--- a/results/momentum_merged_latest.xlsx
+++ b/results/momentum_merged_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D66"/>
+  <dimension ref="A1:D62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AERT</t>
+          <t>CHAD</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -451,19 +451,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ONCO</t>
+          <t>NEON</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ACGLO</t>
+          <t>AEHL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AGEN</t>
+          <t>COSM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -473,1300 +473,1300 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>RDNW</t>
+          <t>AER</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>FJDIU</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AUDC</t>
+          <t>ACRV</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ACU</t>
+          <t>AMKR</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>RFAMU</t>
+          <t>IOVA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>BLNK</t>
+          <t>ADI</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BNKK</t>
+          <t>AUUD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ADAMG</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BPRE</t>
+          <t>AERT</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>BRKRP</t>
+          <t>CAMT</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ADI</t>
+          <t>NTWK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>COLA</t>
+          <t>AGEN</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CHSCO</t>
+          <t>CBRS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ADMA</t>
+          <t>QSI</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CRUS</t>
+          <t>AGPU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GGR</t>
+          <t>COLA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AEMD</t>
+          <t>SDEV</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>DOMH</t>
+          <t>AIIA</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HBIO</t>
+          <t>CRUS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ALVO</t>
+          <t>SXTP</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FAC</t>
+          <t>ALP</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LAFA</t>
+          <t>GCDT</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ALZN</t>
+          <t>TACH</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IQST</t>
+          <t>ARW</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MEDS</t>
+          <t>GNLN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>AMBR</t>
+          <t>XRPN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MWC</t>
+          <t>ASBH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>GRDX</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AMPH</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>OCC</t>
+          <t>KLAC</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NRSN</t>
+          <t>ASST</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AMRX</t>
+          <t>MSS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>QMLS</t>
+          <t>ASYS</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NTWK</t>
+          <t>MWC</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ARQT</t>
+          <t>ATEC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SSYS</t>
+          <t>OCC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PACB</t>
+          <t>ATKR</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>PDC</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SWRD</t>
+          <t>ATLCL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PCAP</t>
+          <t>PLAB</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ATKR</t>
+          <t>ATLCZ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SBMT</t>
+          <t>POM</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ATRC</t>
+          <t>AUC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SDEV</t>
+          <t>RDNW</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AZTA</t>
+          <t>AVAT</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SINT</t>
+          <t>RXT</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AVX</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SONM</t>
+          <t>SHLS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BATRA</t>
+          <t>AXTI</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>WSHP</t>
+          <t>SPHL</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>BCHT</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>BCSS</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>BDSX</t>
-        </is>
-      </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BFRG</t>
+          <t>BMNP</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>BHFAL</t>
+          <t>BNR</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>BPRE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BLFS</t>
+          <t>BTCS</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BMNP</t>
+          <t>BURU</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>BNGO</t>
+          <t>BWIN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BSVN</t>
+          <t>BWMN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BWMN</t>
+          <t>CAI</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CAI</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CBAT</t>
+          <t>CDRO</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CCNEP</t>
+          <t>CEVA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CD</t>
+          <t>CHOW</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>CHSCL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>CHSCO</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CHEC</t>
+          <t>CLGN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CHOW</t>
+          <t>CNET</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLMB</t>
+          <t>CNXN</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CNET</t>
+          <t>COIN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CNTN</t>
+          <t>CPIX</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CNXN</t>
+          <t>CPOP</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CODA</t>
+          <t>CURX</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CPOP</t>
+          <t>DGII</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CRCT</t>
+          <t>DIOD</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CRON</t>
+          <t>DJCO</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>DJT</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CSTL</t>
+          <t>DXPE</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CUB</t>
+          <t>EDHL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CURI</t>
+          <t>EEIQ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CVLT</t>
+          <t>EFSI</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CWD</t>
+          <t>EGBN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>ENGS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DJCO</t>
+          <t>ENTG</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DMAA</t>
+          <t>EPRX</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>DMAC</t>
+          <t>FBLA</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DSGR</t>
+          <t>FEAM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DXPE</t>
+          <t>FLXS</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>FORM</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ECX</t>
+          <t>FSBW</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EDTK</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>EMBC</t>
+          <t>GLND</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>GRI</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>GTBP</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>GYRE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FRNM</t>
+          <t>HBIO</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FSBW</t>
+          <t>HITI</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>FTRE</t>
+          <t>HQI</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>HSDT</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GEGGL</t>
+          <t>IBEX</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GH</t>
+          <t>IBRX</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>IFBD</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>GIW</t>
+          <t>III</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GLSI</t>
+          <t>INAB</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>IOND</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>GRAL</t>
+          <t>IOSP</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GTBP</t>
+          <t>KAZR</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GYRE</t>
+          <t>KLIC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>KMDA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>KMTS</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>IBRX</t>
+          <t>LAUR</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>IMPPP</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>INAB</t>
+          <t>LTRX</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>INOD</t>
+          <t>MATH</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>IOND</t>
+          <t>MCHP</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>IOSP</t>
+          <t>MCHPP</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>IOVA</t>
+          <t>MQ</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>MRAM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>IVVD</t>
+          <t>MTC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>JOYY</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>JRSH</t>
+          <t>MYGN</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>JTAI</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>KAZR</t>
+          <t>NNBR</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>KE</t>
+          <t>NTAP</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>NTNX</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>LGND</t>
+          <t>NTRBW</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>LTRX</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>NVEC</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>MBINM</t>
+          <t>NWGL</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MDWD</t>
+          <t>NXXT</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MIRA</t>
+          <t>OLLI</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MKTW</t>
+          <t>OPRX</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>MLCI</t>
+          <t>ORBS</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MYGN</t>
+          <t>OXBR</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NDSN</t>
+          <t>OXLCZ</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NSTS</t>
+          <t>PAAI</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NTAP</t>
+          <t>PCAP</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>NTNX</t>
+          <t>PGEN</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>NVEC</t>
+          <t>PLXS</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NXXT</t>
+          <t>POWW</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>OCCIN</t>
+          <t>PSHG</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>OLLI</t>
+          <t>PSIG</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ONC</t>
+          <t>PXLW</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ORIC</t>
+          <t>QMCO</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>OXLCI</t>
+          <t>QNBC</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>OXLCM</t>
+          <t>QRVO</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>QTRX</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>PAAI</t>
+          <t>RCMT</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PACH</t>
+          <t>RGS</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>RMTI</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>PDFS</t>
+          <t>RUSHB</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>PFLA</t>
+          <t>RVSB</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PGEN</t>
+          <t>RWAYL</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PHOS</t>
+          <t>RXRX</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>SAFT</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>PLPC</t>
+          <t>SAIL</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>SBMT</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PNTG</t>
+          <t>SGHT</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>PPIH</t>
+          <t>SHMD</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>PPSI</t>
+          <t>SHOP</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PS</t>
+          <t>SIMO</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PSIG</t>
+          <t>SKYA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>QNTM</t>
+          <t>SLAB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>QTRX</t>
+          <t>SLMT</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>QUBT</t>
+          <t>SNPS</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>RCMT</t>
+          <t>SONO</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>RDIB</t>
+          <t>SRZN</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>RDWR</t>
+          <t>SSYS</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>RGEN</t>
+          <t>STRC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>RGS</t>
+          <t>STRF</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>RIGL</t>
+          <t>STRK</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>RILYN</t>
+          <t>SUIG</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>RNW</t>
+          <t>SVCO</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SAIH</t>
+          <t>SVIA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SBC</t>
+          <t>SVIAW</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>SDGR</t>
+          <t>SVRN</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SGHT</t>
+          <t>SWRD</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SIMO</t>
+          <t>TAOX</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SLAB</t>
+          <t>TCPC</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>SMTI</t>
+          <t>TER</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SOPH</t>
+          <t>TITN</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SQFTP</t>
+          <t>TKNO</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>STLN</t>
+          <t>TONX</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>STRC</t>
+          <t>TWAV</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STRF</t>
+          <t>VICR</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>STRK</t>
+          <t>WLTH</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SVRN</t>
+          <t>XCBE</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>SWKHL</t>
+          <t>AMPH</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TAYD</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>TELO</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>TEM</t>
+          <t>RENX</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>TLACU</t>
+          <t>PRTH</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>TMS</t>
+          <t>GRAL</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>TONT</t>
+          <t>YDES</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>TONX</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>TRLV</t>
+          <t>NTRA</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>VAI</t>
+          <t>REFR</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>XXI</t>
+          <t>MXL</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>TJGC</t>
+          <t>DMAC</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>EGHT</t>
+          <t>AIFA</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>OUST</t>
+          <t>AAON</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>IBEX</t>
+          <t>PDFS</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>NTRA</t>
+          <t>GGR</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ARHS</t>
+          <t>CRCT</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>VICR</t>
+          <t>LGND</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
+          <t>SECZ</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
           <t>SILC</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>TNMG</t>
-        </is>
-      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>SHPH</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>ARQQ</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>OESX</t>
+          <t>XXI</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FLXS</t>
+          <t>KBSX</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>SECZ</t>
+          <t>TAYD</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>LSCC</t>
+          <t>HLP</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>QMCO</t>
+          <t>MKTW</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>COHU</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>MRVI</t>
+          <t>OESX</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ALNT</t>
+          <t>WSHP</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>IMOS</t>
+          <t>PS</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MREO</t>
+          <t>JWEL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>DGII</t>
+          <t>ILMN</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FIRY</t>
+          <t>AMRX</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BHFAM</t>
+          <t>COHU</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ARQQ</t>
+          <t>MREO</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>OSUR</t>
+          <t>EMBC</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>GLND</t>
+          <t>MLCI</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>AIXC</t>
+          <t>CLMB</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FEAM</t>
+          <t>MASS</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>MRAM</t>
+          <t>RGEN</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AIFA</t>
+          <t>ARHS</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BATRK</t>
+          <t>LSCC</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SONO</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>FWDI</t>
+          <t>FIRY</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MASS</t>
+          <t>MPWR</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>KBSX</t>
+          <t>STKE</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1776,93 +1776,9 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>STKE</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>KLIC</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>REFR</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>USDEW</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>BNR</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>SVCO</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>MXL</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>SHPH</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>PRTH</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>TKNO</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>SXTP</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>SUIG</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>BLLN</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>FORM</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>EEIQ</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>MRNA</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
+          <t>TJGC</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_merged_latest.xlsx
+++ b/results/momentum_merged_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D81"/>
+  <dimension ref="A1:D77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,1748 +451,1660 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BZFD</t>
+          <t>AAON</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AAON</t>
+          <t>BOT</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AIIA</t>
+          <t>ABSI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ABSI</t>
+          <t>ATOM</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FUFU</t>
+          <t>CURX</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AMBA</t>
+          <t>ABXL</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CHSCO</t>
+          <t>AZUL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ACU</t>
+          <t>DLXY</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GNLN</t>
+          <t>ACLS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ATII</t>
+          <t>BTTC</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CRVO</t>
+          <t>DUKRW</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ADMA</t>
+          <t>ADI</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>HTLM</t>
+          <t>CRD</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AVO</t>
+          <t>FRSH</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ELLA</t>
+          <t>ADMA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>CRNT</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>GCL</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>ADPT</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>RGC</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>CRUS</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>KBSX</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>AEHL</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>FLEX</t>
-        </is>
-      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>DMRC</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AEIS</t>
+          <t>MACI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HWKN</t>
+          <t>AEHR</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GSRF</t>
+          <t>DUOT</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AGEN</t>
+          <t>MDAI</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ICHR</t>
+          <t>AEIS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>INAB</t>
+          <t>EMPD</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AIIR</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>INDV</t>
+          <t>AFRI</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KFII</t>
+          <t>EVCM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>AHG</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>IQMX</t>
+          <t>HBANL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NAUT</t>
+          <t>AIB</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ALMR</t>
+          <t>HYPR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IRMD</t>
+          <t>AIIR</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NSLRL</t>
+          <t>INEO</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ALNT</t>
+          <t>ALAB</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LAB</t>
+          <t>IQMX</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NTWK</t>
+          <t>ALLT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AMPH</t>
+          <t>ITRN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MAZE</t>
+          <t>ALNT</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>OPTX</t>
+          <t>MAZE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AMPL</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDLN</t>
+          <t>MIND</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>OXLCM</t>
+          <t>AMBR</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AMRX</t>
+          <t>NMAD</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MKSI</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PDSB</t>
+          <t>NTRSO</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ANGI</t>
+          <t>AMPH</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NEON</t>
+          <t>POWL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PMTR</t>
+          <t>AMPL</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AOUT</t>
+          <t>QUIK</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>PWRL</t>
+          <t>AMRX</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>RYAAY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ARAY</t>
+          <t>ANDG</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SLMT</t>
+          <t>SNWV</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>PXS</t>
+          <t>ASST</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ARW</t>
+          <t>STRL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>ATKR</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>TLN</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>RELL</t>
-        </is>
-      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ASPS</t>
+          <t>AVAT</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>VERU</t>
+          <t>ZSQR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RXRX</t>
+          <t>AVPT</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ASST</t>
+          <t>AVX</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ZSQR</t>
+          <t>AXTI</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SDEV</t>
+          <t>BATRA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ATKR</t>
+          <t>BBCP</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SOTK</t>
+          <t>BCAL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ATLCL</t>
+          <t>BELFB</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SXTP</t>
+          <t>BMNR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AUUD</t>
+          <t>BNR</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>THEO</t>
+          <t>BOW</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>AVPT</t>
+          <t>BPRE</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>WCCB</t>
+          <t>BSVN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AZTA</t>
+          <t>BTBD</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BCML</t>
+          <t>BZUN</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>BCTX</t>
+          <t>CBAT</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BKHA</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BLRK</t>
+          <t>CDNS</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BNC</t>
+          <t>CELU</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>BPRE</t>
+          <t>CEVA</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BSVN</t>
+          <t>CFFI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BTBD</t>
+          <t>CGNT</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BTTC</t>
+          <t>CGNX</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>BWMN</t>
+          <t>CHAD</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BZUN</t>
+          <t>CHSCL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CAMT</t>
+          <t>CLMB</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>CNXN</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CDNS</t>
+          <t>COHR</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CELU</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>CRAI</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CFFI</t>
+          <t>CRDO</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CHAD</t>
+          <t>CRWD</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CHEF</t>
+          <t>CTKB</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CHSCL</t>
+          <t>CVCO</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CLMB</t>
+          <t>CVLT</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>COHU</t>
+          <t>CWBC</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CORT</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>COSM</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>DIOD</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>CRDO</t>
+          <t>DSGR</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CRSR</t>
+          <t>DSGX</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>DXPE</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>EGBN</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>CSTL</t>
+          <t>EGHT</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CTKB</t>
+          <t>ELMT</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CVLT</t>
+          <t>EMBC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CWBC</t>
+          <t>ENGS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CYRX</t>
+          <t>ENTG</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>EUDA</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DMAC</t>
+          <t>FAST</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>DMRC</t>
+          <t>FBLA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>DOCU</t>
+          <t>FEIM</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DSGR</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>FIRY</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DTST</t>
+          <t>FLEX</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>EEIQ</t>
+          <t>FMAO</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>FOSL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FBLA</t>
+          <t>FPS</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>FEAM</t>
+          <t>FRHC</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>FROG</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FIRY</t>
+          <t>FSBW</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FLGT</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>FNRN</t>
+          <t>FTRE</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>FORM</t>
+          <t>FWDI</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>FRHC</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>GRDX</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FTRE</t>
+          <t>GTLB</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>GDYN</t>
+          <t>HBIO</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>GH</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GRAL</t>
+          <t>HQI</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>GSAT</t>
+          <t>HQWWW</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>GTLB</t>
+          <t>HWKN</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>HBIO</t>
+          <t>IESC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>HIMX</t>
+          <t>INKT</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>IOSP</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>HSTM</t>
+          <t>IRDM</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HTFL</t>
+          <t>JOYY</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>IBRX</t>
+          <t>JWEL</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>IDAI</t>
+          <t>KFII</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>KMRK</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>KMTS</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>IMPPP</t>
+          <t>KOD</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>INCR</t>
+          <t>KOPN</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>INKT</t>
+          <t>LCUT</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>IOSP</t>
+          <t>LECO</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>IOVA</t>
+          <t>LEDS</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>IPGP</t>
+          <t>LGND</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>LIND</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>JAKK</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>JOYY</t>
+          <t>LITS</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>JWEL</t>
+          <t>LKFT</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>KAZR</t>
+          <t>LOPE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>KCHV</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>KFFB</t>
+          <t>LSBK</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>KMTS</t>
+          <t>LSCC</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>KOD</t>
+          <t>LTRX</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>KOSS</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>KRNT</t>
+          <t>MCHP</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>MCHPP</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>LAFA</t>
+          <t>MGNI</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>LAUR</t>
+          <t>MGRC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>LECO</t>
+          <t>MKTX</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LGND</t>
+          <t>MSFT</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>LIND</t>
+          <t>MSGY</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LKFT</t>
+          <t>MTSI</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>LSBK</t>
+          <t>MXL</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>LSCC</t>
+          <t>NATH</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MANE</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>MATH</t>
+          <t>NCPL</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MBINM</t>
+          <t>NDSN</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MCHP</t>
+          <t>NICE</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>NKSH</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>MKTW</t>
+          <t>NOVT</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MLAB</t>
+          <t>NTAP</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>MNTK</t>
+          <t>NTCT</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MPWR</t>
+          <t>NTNX</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>NTRP</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MRVI</t>
+          <t>NTSK</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>NTWK</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MSGM</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>NVEC</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MTSI</t>
+          <t>NXPI</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>OCC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MXL</t>
+          <t>OESX</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NAKA</t>
+          <t>OKTA</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>NATH</t>
+          <t>ONC</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>OPRT</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>NCPL</t>
+          <t>OPRX</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NDRA</t>
+          <t>OPTX</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>NDSN</t>
+          <t>OSPN</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NHPBP</t>
+          <t>OTAI</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>NTCT</t>
+          <t>OUST</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NTNX</t>
+          <t>P</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>NTRA</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NTRP</t>
+          <t>PDFS</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NTSK</t>
+          <t>PKOH</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NUTX</t>
+          <t>PLTR</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>NVAX</t>
+          <t>PLXS</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>PMVP</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>NVEC</t>
+          <t>PPIH</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>OCTV</t>
+          <t>PRCH</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ODD</t>
+          <t>PS</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>PSIG</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>OLLI</t>
+          <t>PSIX</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ON</t>
+          <t>PTC</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>OPRT</t>
+          <t>PUBM</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>OPRX</t>
+          <t>PWP</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>OSPN</t>
+          <t>PXS</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>OSUR</t>
+          <t>QMCO</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>OTAI</t>
+          <t>QSI</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>OXLCZ</t>
+          <t>RBKB</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>RCBC</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>PACB</t>
+          <t>RDVT</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>RDWR</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PAYO</t>
+          <t>RFAI</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>PAYS</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>PDFS</t>
+          <t>RMBS</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PENG</t>
+          <t>RVMD</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PKOH</t>
+          <t>RWAYL</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>PLUN</t>
+          <t>SBC</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>PLXS</t>
+          <t>SBET</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PPIH</t>
+          <t>SCSC</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PPLI</t>
+          <t>SDGR</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>PS</t>
+          <t>SGC</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>SHLS</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>QLYS</t>
+          <t>SHMD</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>QNBC</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>QSEA</t>
+          <t>SILC</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>QTRX</t>
+          <t>SIMO</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>RCEL</t>
+          <t>SITM</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>RCMT</t>
+          <t>SKYA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>RDWR</t>
+          <t>SMMT</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>REFR</t>
+          <t>SMTC</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>RFAI</t>
+          <t>SNPS</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>RILYG</t>
+          <t>SOTK</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>RUSHB</t>
+          <t>SPCX</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>RVSB</t>
+          <t>SPOK</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SAMG</t>
+          <t>SSTI</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SANM</t>
+          <t>STRC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SAX</t>
+          <t>STRD</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>SBC</t>
+          <t>STRK</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SCSC</t>
+          <t>SUIG</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SCYX</t>
+          <t>SUJA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>SDGR</t>
+          <t>SUNB</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>SEER</t>
+          <t>SVCO</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SGC</t>
+          <t>TAOX</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>TEM</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>SIGA</t>
+          <t>TENB</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>SILC</t>
+          <t>TITN</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SIMO</t>
+          <t>TLSA</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SINT</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>SITM</t>
+          <t>TRNI</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>SKHY</t>
+          <t>TRNS</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SLAB</t>
+          <t>USDEW</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SLGL</t>
+          <t>VAI</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>WCCB</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>SPSC</t>
+          <t>WLTH</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SRZN</t>
+          <t>XFLH</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SSYS</t>
+          <t>XMTR</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>STRC</t>
+          <t>XRPN</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>STRD</t>
+          <t>XXI</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STRF</t>
+          <t>KLIC</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>STRK</t>
+          <t>VCTR</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SUIG</t>
+          <t>COHU</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>SUNB</t>
+          <t>CRVO</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SVIA</t>
+          <t>ASYS</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SVRN</t>
+          <t>ICHR</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SWBI</t>
+          <t>NVMI</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>SWKHL</t>
+          <t>SYNA</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>TAOX</t>
+          <t>IBRX</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>TEM</t>
+          <t>ON</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>TENB</t>
+          <t>CBNK</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>TONT</t>
+          <t>MSGM</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>QLYS</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>TRNS</t>
+          <t>KRNT</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>TWAV</t>
+          <t>ODD</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VALU</t>
+          <t>IMMP</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>VIR</t>
+          <t>REBN</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>WLTH</t>
+          <t>III</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>XFLH</t>
+          <t>INAB</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>XMTR</t>
+          <t>BIRD</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>XRPNU</t>
+          <t>SLGL</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>LFCR</t>
+          <t>NAUT</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>SANG</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>DLXY</t>
+          <t>PAHC</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>IMMP</t>
+          <t>RELL</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>NVMI</t>
+          <t>IMOS</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>VICR</t>
+          <t>BTLN</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>BTLN</t>
+          <t>FEAM</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>XRPN</t>
+          <t>PAYS</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>QSI</t>
+          <t>STKE</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>OCG</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>LFCR</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>FOSL</t>
+          <t>RXRX</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>STKE</t>
+          <t>MKSI</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SYNA</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>TJGC</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>ENTG</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>AXTI</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>KLIC</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>SSTI</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>CD</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>QMCO</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>ACLS</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>OCC</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>MASS</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>ASYS</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>MRVL</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>NTAP</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>SANG</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>PMVP</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>REBN</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
+          <t>PACB</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_merged_latest.xlsx
+++ b/results/momentum_merged_latest.xlsx
@@ -1991,134 +1991,134 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>VALU</t>
+          <t>RPGL</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ARTW</t>
+          <t>RGC</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>FVNNU</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>LSAK</t>
+          <t>ATOS</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>IRIX</t>
+          <t>JG</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>BTLN</t>
+          <t>AGBK</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>MWYN</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>FEBO</t>
+          <t>ICG</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ATOS</t>
+          <t>BTSGU</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>SMXT</t>
+          <t>SBC</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BYRN</t>
+          <t>ARTW</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>IDAI</t>
+          <t>FNKO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MWYN</t>
+          <t>CHAD</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>BTSG</t>
+          <t>FEBO</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>LSAK</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BTSGU</t>
+          <t>BTLN</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>RGC</t>
+          <t>FVNNU</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>AGBK</t>
+          <t>VALU</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SBC</t>
+          <t>IDAI</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>RPGL</t>
+          <t>BYRN</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>FNKO</t>
+          <t>BTSG</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ICG</t>
+          <t>RCEL</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>RCEL</t>
+          <t>SMXT</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CHAD</t>
+          <t>IRIX</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>

--- a/results/momentum_merged_latest.xlsx
+++ b/results/momentum_merged_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D78"/>
+  <dimension ref="A1:D71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,17 +441,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AFRI</t>
+          <t>ALISU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ACB</t>
+          <t>AACI</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AERO</t>
+          <t>LVLU</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -463,29 +463,29 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AFRM</t>
+          <t>AMBR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ADMA</t>
+          <t>ACIC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CGNX</t>
+          <t>TBCH</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AZUL</t>
+          <t>AERO</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AMPL</t>
+          <t>AUC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -495,63 +495,63 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CRNT</t>
+          <t>BVFL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DUO</t>
+          <t>BKHAU</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AUC</t>
+          <t>AFRI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AHG</t>
+          <t>ECHO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GFS</t>
+          <t>BMR</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FBYD</t>
+          <t>AGBK</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BKHAU</t>
+          <t>EMPD</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AIFA</t>
+          <t>CHNR</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>HCAT</t>
+          <t>AIRT</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FLEX</t>
+          <t>HWKN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BMR</t>
+          <t>DLXY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -561,1568 +561,1410 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>HRTX</t>
+          <t>INSG</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>INSG</t>
+          <t>ELOG</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BPRE</t>
+          <t>ALRM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>IRMD</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LVLU</t>
+          <t>ENGS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>IRMD</t>
+          <t>AMGN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRBI</t>
+          <t>ITRN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ALRM</t>
+          <t>FVNNU</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NTES</t>
+          <t>AMPH</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ITRN</t>
+          <t>LFS</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRLT</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AMBR</t>
+          <t>AMRX</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>LMB</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>KMRK</t>
+          <t>HLP</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BWIN</t>
+          <t>ANDG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>MYRG</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>QETA</t>
+          <t>ICG</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LFS</t>
+          <t>APA</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BWMN</t>
+          <t>NTES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AMPH</t>
+          <t>IDAI</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SJ</t>
+          <t>APEI</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LMB</t>
+          <t>OFLX</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CAPNU</t>
+          <t>LSAK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>APOG</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SYPR</t>
+          <t>OMCL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NTCT</t>
+          <t>NCPL</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CBRL</t>
+          <t>ASO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ANDG</t>
+          <t>OSW</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NXT</t>
+          <t>OTAI</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CCCT</t>
+          <t>ATEC</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ANGI</t>
+          <t>PWP</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>OCG</t>
+          <t>PEBK</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CFFI</t>
+          <t>AVBC</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>PWRL</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>OMCL</t>
+          <t>QQQX</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CGNT</t>
+          <t>AVPT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>APEI</t>
+          <t>RFAI</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ON</t>
+          <t>BIRD</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CLFD</t>
+          <t>BMNP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>APOG</t>
+          <t>BOW</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>OPTX</t>
+          <t>BPRE</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CLOV</t>
+          <t>BRZE</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>APPN</t>
+          <t>BSET</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PWP</t>
+          <t>BSY</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CMRC</t>
+          <t>BWMN</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ASO</t>
+          <t>BYRN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PWRL</t>
+          <t>CAKE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>CAPNU</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ATEC</t>
+          <t>CBC</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>RDGT</t>
+          <t>CBRL</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ATLCZ</t>
+          <t>CDNS</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TBCH</t>
+          <t>CFFI</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>CGNT</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ATRA</t>
+          <t>CHAD</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FEAM</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AUDC</t>
+          <t>CNXN</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>FLD</t>
+          <t>COPR</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AVPT</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>CPHC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AVTR</t>
+          <t>CRAI</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>GECCI</t>
+          <t>CRCT</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AXIN</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GIBO</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AZTA</t>
+          <t>CUB</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>GOOGM</t>
+          <t>CV</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BGM</t>
+          <t>CWCO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GSAT</t>
+          <t>DCBO</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BLZR</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>DH</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BVFL</t>
+          <t>DLO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>HPK</t>
+          <t>DMLP</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CAKE</t>
+          <t>DSGX</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>HSTM</t>
+          <t>DTST</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CAMT</t>
+          <t>DUOL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IBRX</t>
+          <t>EBAY</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>ECPG</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>IMKTA</t>
+          <t>EFOR</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CELU</t>
+          <t>EFSI</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>INTR</t>
+          <t>EGBN</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CHEF</t>
+          <t>EMBC</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>IPXG</t>
+          <t>ENSC</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CLMB</t>
+          <t>EVCM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JAKK</t>
+          <t>EXEL</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CNXN</t>
+          <t>EXLS</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>EXPO</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CORT</t>
+          <t>FAST</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MEOH</t>
+          <t>FIRY</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>FLXS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>FNKO</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>FOSL</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>FRAF</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>FRD</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NAUT</t>
+          <t>FROG</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CURX</t>
+          <t>FSBW</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NDSN</t>
+          <t>FTRE</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CVLT</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NMAD</t>
+          <t>GECCH</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CWCO</t>
+          <t>GLBE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NTRP</t>
+          <t>GMAB</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NTSK</t>
+          <t>GOOGL</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DGII</t>
+          <t>GOOGM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>NVAX</t>
+          <t>GOOGN</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>GRDX</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NVEC</t>
+          <t>GTLB</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DMAC</t>
+          <t>HAS</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NXPL</t>
+          <t>HBIO</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>DNMX</t>
+          <t>HCKT</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ODD</t>
+          <t>HPK</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>HSTM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ONBPP</t>
+          <t>HURN</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>DTST</t>
+          <t>HYFT</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>OPRT</t>
+          <t>HYNE</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DUOL</t>
+          <t>IBEX</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>OSPN</t>
+          <t>III</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>EFOI</t>
+          <t>INAC</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>OTAI</t>
+          <t>INGN</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>INTR</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PAX</t>
+          <t>IRIX</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>EFSI</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>PDSB</t>
+          <t>JANX</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>EMBC</t>
+          <t>JFU</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PENG</t>
+          <t>JOYY</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>KE</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>PHUN</t>
+          <t>KGEI</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>EUDA</t>
+          <t>KMRK</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PICS</t>
+          <t>KRAQ</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>KRNT</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>KRSA</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PRME</t>
+          <t>LAUR</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FCAP</t>
+          <t>LCUT</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>PSIG</t>
+          <t>LIN</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>LIND</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>QQQX</t>
+          <t>LOPE</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FFR</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>QSI</t>
+          <t>MAT</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>FIRY</t>
+          <t>MKTX</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>RDWR</t>
+          <t>MQ</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>FLYW</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>RELL</t>
+          <t>MSGM</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FOSL</t>
+          <t>MWYN</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>RUSHB</t>
+          <t>NATH</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FROG</t>
+          <t>NDSN</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>RXRX</t>
+          <t>NECB</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FRSH</t>
+          <t>NICE</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SRZN</t>
+          <t>NKSH</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>NMAD</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>STNE</t>
+          <t>NNBR</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>FTRE</t>
+          <t>NSIT</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SYNA</t>
+          <t>NTAP</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>NTGR</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>TENB</t>
+          <t>NTRP</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>NTWK</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>TLSA</t>
+          <t>NWE</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NXPL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VAI</t>
+          <t>OCTV</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>ODD</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>VCTR</t>
+          <t>OLLI</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ZSQR</t>
+          <t>ONBPP</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>GOOGN</t>
+          <t>OPCH</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GRAL</t>
+          <t>OPRT</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GRDX</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>GTLB</t>
+          <t>PAX</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>PBYI</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>HQWWW</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>IBEX</t>
+          <t>PCTY</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>PDSB</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>INGN</t>
+          <t>PENG</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>IOVA</t>
+          <t>PICS</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>PLUS</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>JRSH</t>
+          <t>PNRG</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>KOD</t>
+          <t>PNTG</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>KRNT</t>
+          <t>POCI</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>LAUR</t>
+          <t>PRCH</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LCUT</t>
+          <t>PRDO</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>LFCR</t>
+          <t>PRHI</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>LIND</t>
+          <t>PS</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MACI</t>
+          <t>PSIX</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>PTC</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MASS</t>
+          <t>PUBM</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MAT</t>
+          <t>QLYS</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MBVI</t>
+          <t>RCBC</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>MDLN</t>
+          <t>RCKY</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MKTX</t>
+          <t>RDVT</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MQ</t>
+          <t>RDWR</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>RGS</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>MSGY</t>
+          <t>RMCF</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MYGN</t>
+          <t>RPD</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NATH</t>
+          <t>RVSB</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>NICE</t>
+          <t>RWAYM</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NSIT</t>
+          <t>RYZ</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>NTAP</t>
+          <t>SAFT</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NTGR</t>
+          <t>SAMG</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>NTNX</t>
+          <t>SCHL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NTRA</t>
+          <t>SGC</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>OCTV</t>
+          <t>SIBN</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>SKK</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>OLB</t>
+          <t>SKWD</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>OM</t>
+          <t>SLDE</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>OPCH</t>
+          <t>SMXT</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>OPRX</t>
+          <t>SNPS</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>SOTK</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PAHC</t>
+          <t>SPCX</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>SPSC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>PAYS</t>
+          <t>STDN</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>PBYI</t>
+          <t>STRA</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PCVX</t>
+          <t>STRC</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PDFS</t>
+          <t>SUNB</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>PKOH</t>
+          <t>SVRN</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>PLUS</t>
+          <t>SWKHL</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PRCH</t>
+          <t>TACH</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PRHI</t>
+          <t>TECH</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>PRTH</t>
+          <t>TLN</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>TLSA</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PXS</t>
+          <t>TPCS</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>QLYS</t>
+          <t>TRMB</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>QTEX</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>RCBC</t>
+          <t>UTHR</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>RFAI</t>
+          <t>VAI</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>RIBBU</t>
+          <t>VCTR</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>RLYB</t>
+          <t>VYLR</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>RPD</t>
+          <t>WCCB</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>RRGB</t>
+          <t>BGM</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>RVSB</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>RWAYL</t>
+          <t>SHLS</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>RYZ</t>
+          <t>RELL</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SAV</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SCHL</t>
+          <t>ZSQR</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>SCSC</t>
+          <t>RPGL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>SGC</t>
+          <t>AMPL</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SHLS</t>
+          <t>FRSH</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>TENB</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>SIBN</t>
+          <t>OKTA</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>SLAB</t>
+          <t>TEAM</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SNPS</t>
+          <t>SUJA</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SOTK</t>
+          <t>RCEL</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SSTI</t>
+          <t>JDZG</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>STRC</t>
+          <t>SNWV</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STRK</t>
+          <t>GIBO</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SUJA</t>
+          <t>SWRD</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SUNB</t>
+          <t>RZLT</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>SWKHL</t>
+          <t>NTSK</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SWRD</t>
+          <t>PGNY</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>TEAM</t>
+          <t>KNSA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>TJGC</t>
+          <t>FLYW</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>TLN</t>
+          <t>STNE</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>TPCS</t>
+          <t>MTEX</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>TRMB</t>
+          <t>OLB</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>TRNI</t>
+          <t>AFRM</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>HQWWW</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>UTHR</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>VIR</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>VYLR</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>WCCB</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>XMTR</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>YDES</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>RPGL</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>RGC</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>ATOS</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>JG</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>AGBK</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>MWYN</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>ICG</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>BTSGU</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>SBC</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>ARTW</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>FNKO</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>CHAD</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>FEBO</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>LSAK</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>BTLN</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>FVNNU</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>VALU</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>IDAI</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>BYRN</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>BTSG</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>RCEL</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>SMXT</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>IRIX</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr"/>
-      <c r="D78" t="inlineStr"/>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_merged_latest.xlsx
+++ b/results/momentum_merged_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,29 +441,29 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ALISU</t>
+          <t>AGBK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AACI</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LVLU</t>
+          <t>GFUZ</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ACHC</t>
+          <t>AEP</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AMBR</t>
+          <t>ALISU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -473,1498 +473,1326 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TBCH</t>
+          <t>JYD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AERO</t>
+          <t>BCML</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AUC</t>
+          <t>CHNR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AEHL</t>
+          <t>ADI</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BVFL</t>
+          <t>PFAI</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>BKHAU</t>
+          <t>DLHC</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AFRI</t>
+          <t>DCBO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ECHO</t>
+          <t>AFRM</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BMR</t>
+          <t>SIMA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AGBK</t>
+          <t>EMPD</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EMPD</t>
+          <t>ELOG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CHNR</t>
+          <t>AIRT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AIRT</t>
+          <t>LVLU</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>HWKN</t>
+          <t>ENGS</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DLXY</t>
+          <t>AISP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AISP</t>
+          <t>NTRSO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>INSG</t>
+          <t>ENSC</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ELOG</t>
+          <t>ALRM</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ALRM</t>
+          <t>NXT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IRMD</t>
+          <t>FLYE</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>OSG</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ITRN</t>
+          <t>PEBK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FVNNU</t>
+          <t>AMRX</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AMPH</t>
+          <t>RMCF</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LFS</t>
+          <t>SJ</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>ANDG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AMRX</t>
+          <t>RPGL</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LMB</t>
+          <t>AOUT</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>RSVR</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ANDG</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MYRG</t>
+          <t>SCHL</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ICG</t>
+          <t>APEI</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>SNWV</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NTES</t>
+          <t>ARTW</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IDAI</t>
+          <t>ASO</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>APEI</t>
+          <t>ATKR</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>OFLX</t>
+          <t>AUDC</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LSAK</t>
+          <t>AZTA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>APOG</t>
+          <t>BKHAU</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>OMCL</t>
+          <t>BLKB</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NCPL</t>
+          <t>BMNP</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ASO</t>
+          <t>BOLT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>OSW</t>
+          <t>BORR</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>OTAI</t>
+          <t>BOW</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ATEC</t>
+          <t>BSET</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PWP</t>
+          <t>BSVN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PEBK</t>
+          <t>BSY</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AVBC</t>
+          <t>BVFL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>PWRL</t>
+          <t>BWIN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>QQQX</t>
+          <t>BZUN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AVPT</t>
+          <t>CAKE</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>RFAI</t>
+          <t>CBC</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>BIRD</t>
+          <t>CBRL</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BMNP</t>
+          <t>CCSI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BOW</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BPRE</t>
+          <t>CDNA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>BRZE</t>
+          <t>CFFI</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BSET</t>
+          <t>CGNT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BSY</t>
+          <t>CLMB</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BWMN</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>BYRN</t>
+          <t>CLOV</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CAKE</t>
+          <t>CMRC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CAPNU</t>
+          <t>CNXN</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CBC</t>
+          <t>COKE</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CBRL</t>
+          <t>COR</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CD</t>
+          <t>CORT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CDNS</t>
+          <t>CRAI</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CFFI</t>
+          <t>CRCT</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CGNT</t>
+          <t>CRNC</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CHAD</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CLMT</t>
+          <t>CTAS</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CNXN</t>
+          <t>CVSA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>COPR</t>
+          <t>DAVE</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CPHC</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CRAI</t>
+          <t>DLO</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CRCT</t>
+          <t>DMLP</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>DOCU</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>DSGR</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CUB</t>
+          <t>DSGX</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CV</t>
+          <t>EBAY</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CWCO</t>
+          <t>ECPG</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>EEIQ</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>EFSI</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DLO</t>
+          <t>EGBN</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DMLP</t>
+          <t>EMBC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>EXEL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>DTST</t>
+          <t>EXLS</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DUOL</t>
+          <t>FIVN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>FSBW</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ECPG</t>
+          <t>GDYN</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>GIBO</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>EFSI</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>EGBN</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>EMBC</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ENSC</t>
+          <t>GOOGL</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>EVCM</t>
+          <t>GOOGM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>GOOGN</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>EXLS</t>
+          <t>GTLB</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>HAS</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>HCKT</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FIRY</t>
+          <t>HLP</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FLXS</t>
+          <t>HMR</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>FNKO</t>
+          <t>HOWL</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>FOSL</t>
+          <t>HPK</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FRAF</t>
+          <t>HSTM</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FRD</t>
+          <t>HURN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>FROG</t>
+          <t>IBEX</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>FSBW</t>
+          <t>IBRX</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FTRE</t>
+          <t>ICG</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>III</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>GECCH</t>
+          <t>IMPP</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>GLBE</t>
+          <t>INGN</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>IRMD</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>JANX</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GOOGM</t>
+          <t>JOYY</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GOOGN</t>
+          <t>KBON</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>GRDX</t>
+          <t>KFFB</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>GTLB</t>
+          <t>KGEI</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>KNSA</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>HBIO</t>
+          <t>KROS</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>HCKT</t>
+          <t>KRSA</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>HPK</t>
+          <t>KRT</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>HSTM</t>
+          <t>LAUR</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>HURN</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>HYFT</t>
+          <t>LOCO</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>HYNE</t>
+          <t>LOPE</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>IBEX</t>
+          <t>LYFT</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>MANE</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>INAC</t>
+          <t>MCGA</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>INGN</t>
+          <t>MEOH</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>INTR</t>
+          <t>MESH</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>IRIX</t>
+          <t>MGNI</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>MNRO</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>JANX</t>
+          <t>MQ</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>JFU</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>JOYY</t>
+          <t>MWYN</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>KE</t>
+          <t>NATH</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>KGEI</t>
+          <t>NCPL</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>KMRK</t>
+          <t>NECB</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>KRAQ</t>
+          <t>NKSH</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>KRNT</t>
+          <t>NRDS</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>KRSA</t>
+          <t>NSIT</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>NWE</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>LAUR</t>
+          <t>NXTC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>LCUT</t>
+          <t>ODD</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>OLLI</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>LIND</t>
+          <t>OPLN</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>LOPE</t>
+          <t>OPRX</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>PANL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>MAT</t>
+          <t>PCB</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MKTX</t>
+          <t>PCTY</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MQ</t>
+          <t>PDSB</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>PGNY</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>MSGM</t>
+          <t>PLTR</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MWYN</t>
+          <t>PLUS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NATH</t>
+          <t>PNRG</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NDSN</t>
+          <t>PRAA</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NECB</t>
+          <t>PRDO</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>NICE</t>
+          <t>PSIX</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NKSH</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NMAD</t>
+          <t>PUBM</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NNBR</t>
+          <t>PXS</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>NSIT</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NTAP</t>
+          <t>QDEL</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NTGR</t>
+          <t>QLEP</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NTRP</t>
+          <t>QNBC</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>NTWK</t>
+          <t>QTEX</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NWE</t>
+          <t>RFAI</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NXPL</t>
+          <t>RGC</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>OCTV</t>
+          <t>RIGL</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ODD</t>
+          <t>RVSB</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>OLLI</t>
+          <t>SAFT</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>OM</t>
+          <t>SAMG</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ONBPP</t>
+          <t>SCSC</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>OPCH</t>
+          <t>SLDE</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>OPRT</t>
+          <t>SLSN</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>SMTI</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>PAX</t>
+          <t>SMXT</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PBYI</t>
+          <t>SND</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>SNFCA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>PCTY</t>
+          <t>SPSC</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>PDSB</t>
+          <t>SPT</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PENG</t>
+          <t>SSTI</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PICS</t>
+          <t>STGW</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>PLUS</t>
+          <t>SUJA</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>PNRG</t>
+          <t>SUNB</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PNTG</t>
+          <t>SWKHL</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>POCI</t>
+          <t>SWRD</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>PRCH</t>
+          <t>TBCH</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>PRDO</t>
+          <t>TEAM</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PRHI</t>
+          <t>TENB</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PS</t>
+          <t>TJGC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>PSIX</t>
+          <t>TLN</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>TRI</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PUBM</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>QLYS</t>
+          <t>WCCB</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>RCBC</t>
+          <t>XFLH</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>RCKY</t>
+          <t>ZSQR</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>RDVT</t>
+          <t>AHG</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>RDWR</t>
+          <t>FNKO</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>RGS</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>RMCF</t>
+          <t>BYRN</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>RPD</t>
+          <t>PENG</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>RVSB</t>
+          <t>MAT</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>RWAYM</t>
+          <t>APOG</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>RYZ</t>
+          <t>MRNA</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SAFT</t>
+          <t>JVA</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SAMG</t>
+          <t>HEPS</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SCHL</t>
+          <t>OKTA</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>SGC</t>
+          <t>SKWD</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>BRBI</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SIBN</t>
+          <t>SEZL</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SKK</t>
+          <t>AFYA</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>SKWD</t>
+          <t>JG</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SLDE</t>
+          <t>BMR</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SMXT</t>
+          <t>PAYS</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SNPS</t>
+          <t>JDZG</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>SOTK</t>
+          <t>P</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SPCX</t>
+          <t>RELL</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SPSC</t>
+          <t>SOTK</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>STDN</t>
+          <t>RCEL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>STRA</t>
+          <t>NTSK</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STRC</t>
+          <t>INTR</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SUNB</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SVRN</t>
+          <t>NAUT</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>SWKHL</t>
+          <t>PICS</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TACH</t>
+          <t>AMPL</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>TECH</t>
+          <t>STNE</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>TLN</t>
+          <t>PRHI</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>TLSA</t>
+          <t>IRIX</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TPCS</t>
+          <t>BRZE</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>TRMB</t>
+          <t>OPCH</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>LSAK</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>UTHR</t>
+          <t>PAX</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>VAI</t>
+          <t>PBYI</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>VCTR</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>VYLR</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>WCCB</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>BGM</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>SHLS</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>RELL</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>TW</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>ZSQR</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>RPGL</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>AMPL</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
           <t>FRSH</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>TENB</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>OKTA</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>TEAM</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>SUJA</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>RCEL</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>JDZG</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>SNWV</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>GIBO</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>SWRD</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>RZLT</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>NTSK</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>PGNY</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>KNSA</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>FLYW</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>STNE</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>MTEX</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>OLB</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>AFRM</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>HQWWW</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>PLTR</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr"/>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_merged_latest.xlsx
+++ b/results/momentum_merged_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D63"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AGBK</t>
+          <t>NCPL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -451,1348 +451,1088 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GFUZ</t>
+          <t>AHCO</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>ACHC</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ALISU</t>
+          <t>FNGR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ACIC</t>
+          <t>ADMA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>JYD</t>
+          <t>IIIV</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>BCML</t>
+          <t>AEP</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CHNR</t>
+          <t>IMKTA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ADI</t>
+          <t>AFRI</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PFAI</t>
+          <t>ISPR</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DLHC</t>
+          <t>AFRM</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>LIF</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AFRM</t>
+          <t>AFYA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SIMA</t>
+          <t>TLS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EMPD</t>
+          <t>AGBK</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ELOG</t>
+          <t>AGCC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AIRT</t>
+          <t>AISP</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LVLU</t>
+          <t>ALLT</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>AMGN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AISP</t>
+          <t>AMPL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NTRSO</t>
+          <t>ANDG</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ENSC</t>
+          <t>AOUT</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ALRM</t>
+          <t>APA</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NXT</t>
+          <t>APPN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FLYE</t>
+          <t>ARQT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>ASTH</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>OSG</t>
+          <t>ATEC</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PEBK</t>
+          <t>AUGO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AMRX</t>
+          <t>AVPT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>RMCF</t>
+          <t>AVTR</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SJ</t>
+          <t>AZTA</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ANDG</t>
+          <t>BIIB</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RPGL</t>
+          <t>BMBL</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AOUT</t>
+          <t>BOW</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>RSVR</t>
+          <t>BPRE</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>BSY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SCHL</t>
+          <t>BWIN</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>APEI</t>
+          <t>BZ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SNWV</t>
+          <t>BZUN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ARTW</t>
+          <t>CART</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ASO</t>
+          <t>CBC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ATKR</t>
+          <t>CCEP</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>AUDC</t>
+          <t>CDNA</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AZTA</t>
+          <t>CGNT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BKHAU</t>
+          <t>CHKP</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BLKB</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>BMNP</t>
+          <t>CLOV</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BOLT</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BORR</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BOW</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>BSET</t>
+          <t>CRAI</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BSVN</t>
+          <t>CRNC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BSY</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BVFL</t>
+          <t>CTAS</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>BWIN</t>
+          <t>CVLT</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BZUN</t>
+          <t>CVSA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CAKE</t>
+          <t>DCBO</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CBC</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CBRL</t>
+          <t>DDOG</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CCSI</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CD</t>
+          <t>DLO</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>DOCU</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CFFI</t>
+          <t>DSGR</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CGNT</t>
+          <t>DSGX</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CLMB</t>
+          <t>EBAY</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLMT</t>
+          <t>EDHL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CLOV</t>
+          <t>EFOR</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CMRC</t>
+          <t>EFSI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CNXN</t>
+          <t>ETSY</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>COKE</t>
+          <t>EXEL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>EXLS</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CORT</t>
+          <t>EXPO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CRAI</t>
+          <t>FEAM</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CRCT</t>
+          <t>FIVN</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CRNC</t>
+          <t>FLYW</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>FRPT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>FRSH</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CVSA</t>
+          <t>FTRE</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>DAVE</t>
+          <t>GCL</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>GIW</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>DLO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>DMLP</t>
+          <t>GOOG</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DOCU</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DSGR</t>
+          <t>GOOGM</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>GOOGN</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>GRAL</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ECPG</t>
+          <t>GRDX</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>EEIQ</t>
+          <t>HLP</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>HPK</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>EFSI</t>
+          <t>HURN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>EGBN</t>
+          <t>IBRX</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>EMBC</t>
+          <t>ICFI</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>INGN</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>EXLS</t>
+          <t>INTR</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FIVN</t>
+          <t>IOVA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FSBW</t>
+          <t>IRMD</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GDYN</t>
+          <t>JFU</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>GIBO</t>
+          <t>JOYY</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>JRSH</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>KDP</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>KNSA</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>KOD</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GOOGM</t>
+          <t>KRNT</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GOOGN</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GTLB</t>
+          <t>LAUR</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>LCUT</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>HCKT</t>
+          <t>LGND</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>HMR</t>
+          <t>LVLU</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>HOWL</t>
+          <t>LYFT</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>HPK</t>
+          <t>MANE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>HSTM</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>HURN</t>
+          <t>MATH</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>IBEX</t>
+          <t>MDLN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>IBRX</t>
+          <t>MDXG</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ICG</t>
+          <t>MEDP</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>MKTX</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>IMPP</t>
+          <t>MORN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>INGN</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>IRMD</t>
+          <t>MWYN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>JANX</t>
+          <t>NICE</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>JOYY</t>
+          <t>NIQ</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>KBON</t>
+          <t>NMAD</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>KFFB</t>
+          <t>NVAX</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>KGEI</t>
+          <t>OCTV</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>KNSA</t>
+          <t>OKTA</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>KROS</t>
+          <t>OLLI</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>KRSA</t>
+          <t>OTEX</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>PAX</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>LAUR</t>
+          <t>PCTY</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>LOCO</t>
+          <t>PRHI</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LOPE</t>
+          <t>PRTH</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>LYFT</t>
+          <t>PRVA</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MANE</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MCGA</t>
+          <t>QDEL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>MEOH</t>
+          <t>QNBC</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MESH</t>
+          <t>RCBC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MGNI</t>
+          <t>RGC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MNRO</t>
+          <t>RPD</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>MQ</t>
+          <t>RTSN</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>RZLT</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MWYN</t>
+          <t>SAFT</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>NATH</t>
+          <t>SANG</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NCPL</t>
+          <t>SCHL</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>NECB</t>
+          <t>SEZL</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NKSH</t>
+          <t>SJ</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>NRDS</t>
+          <t>SMXT</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NSIT</t>
+          <t>SND</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NWE</t>
+          <t>SOTK</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NXTC</t>
+          <t>SPT</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ODD</t>
+          <t>SSNC</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>OLLI</t>
+          <t>STNE</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>OPLN</t>
+          <t>SWKHL</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>OPRX</t>
+          <t>SWRD</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>PANL</t>
+          <t>TEAM</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>TRI</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PCTY</t>
+          <t>TRMB</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PDSB</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PGNY</t>
+          <t>VAI</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>VALU</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PLUS</t>
+          <t>WCCB</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PNRG</t>
+          <t>ELOG</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>PRAA</t>
+          <t>ODD</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>PRDO</t>
+          <t>ASO</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PSIX</t>
+          <t>AIXI</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>SUJA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>PUBM</t>
+          <t>RELL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>PXS</t>
+          <t>JYD</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>BOLT</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>QDEL</t>
+          <t>AHG</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>QLEP</t>
+          <t>PDSB</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>QNBC</t>
+          <t>OPLN</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>QTEX</t>
+          <t>KMRK</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>RFAI</t>
+          <t>LIFE</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>RGC</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>RIGL</t>
+          <t>HEPS</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>RVSB</t>
+          <t>BYRN</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SAFT</t>
+          <t>NTSK</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SAMG</t>
+          <t>ZSQR</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>SCSC</t>
+          <t>ACIC</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SLDE</t>
+          <t>BMR</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SLSN</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SMTI</t>
+          <t>LOCO</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>SMXT</t>
+          <t>ENSC</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SND</t>
+          <t>PCRX</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SNFCA</t>
+          <t>BORR</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SPSC</t>
+          <t>PICS</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>SPT</t>
+          <t>OPCH</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SSTI</t>
+          <t>MQ</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>STGW</t>
+          <t>PROF</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SUJA</t>
+          <t>ENGS</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>SUNB</t>
+          <t>JDZG</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SWKHL</t>
+          <t>RPGL</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SWRD</t>
+          <t>FLYE</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>TBCH</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>TEAM</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>TENB</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>TJGC</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>TLN</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>TRI</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>TW</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>WCCB</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>XFLH</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>ZSQR</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>AHG</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>FNKO</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>GCL</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>BYRN</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>PENG</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>MAT</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>APOG</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>MRNA</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>JVA</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>HEPS</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>OKTA</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>SKWD</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>BRBI</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>SEZL</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>AFYA</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>JG</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>BMR</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>PAYS</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>JDZG</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>RELL</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>SOTK</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>RCEL</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>NTSK</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>INTR</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>SHOP</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>NAUT</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>PICS</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>AMPL</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>STNE</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>PRHI</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>IRIX</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>BRZE</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>OPCH</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>LSAK</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>PAX</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>PBYI</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>FRSH</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
+          <t>BLKB</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_merged_latest.xlsx
+++ b/results/momentum_merged_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,139 +441,139 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NCPL</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>ADMA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AHCO</t>
+          <t>AFRM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ACHC</t>
+          <t>AER</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FNGR</t>
+          <t>ACHC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ADMA</t>
+          <t>AFYA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>IIIV</t>
+          <t>ATOS</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>CLWT</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IMKTA</t>
+          <t>AEP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AFRI</t>
+          <t>AHG</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ISPR</t>
+          <t>GOOGM</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AFRM</t>
+          <t>CWCO</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LIF</t>
+          <t>AFRI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AFYA</t>
+          <t>AISP</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TLS</t>
+          <t>JDZG</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AGBK</t>
+          <t>FBYD</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AGCC</t>
+          <t>ALRM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AISP</t>
+          <t>ANGH</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ALLT</t>
+          <t>RPGL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>IIIV</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AMPL</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ANDG</t>
+          <t>APPN</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AOUT</t>
+          <t>RSVR</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>ISPR</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>APPN</t>
+          <t>AOUT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -583,557 +583,557 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ASTH</t>
+          <t>TLS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ATEC</t>
+          <t>RZLT</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>ATLCL</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ARX</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>AUGO</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>AVPT</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>AVTR</t>
-        </is>
-      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>AZTA</t>
+          <t>ASO</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>AVTR</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ATEC</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>BIIB</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>BMBL</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>BOW</t>
-        </is>
-      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>BPRE</t>
+          <t>ATRA</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BSY</t>
+          <t>BLKB</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BWIN</t>
+          <t>AUC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>BMBL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>BZUN</t>
+          <t>AVPT</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CART</t>
+          <t>BMNP</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CBC</t>
+          <t>BLIV</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CCEP</t>
+          <t>BORR</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>BPRE</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CGNT</t>
+          <t>BREZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CHKP</t>
+          <t>BRLT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLMT</t>
+          <t>BYRN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CLOV</t>
+          <t>BSET</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>BZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>BTSG</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>CAKE</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CRAI</t>
+          <t>BTSGU</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CRNC</t>
+          <t>CBC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>BUUU</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>CBFV</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CVLT</t>
+          <t>BWIN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CVSA</t>
+          <t>CBLL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>CBRL</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>CCEP</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DLO</t>
+          <t>CLGN</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>DOCU</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>DSGR</t>
+          <t>COKE</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>CRAC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>EDHL</t>
+          <t>CTAS</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>DH</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EFSI</t>
+          <t>CVSA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ETSY</t>
+          <t>EBAY</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EXLS</t>
+          <t>EFOR</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>DLO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FEAM</t>
+          <t>ENGS</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>FIVN</t>
+          <t>DOCU</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>FLYW</t>
+          <t>EXLS</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FRPT</t>
+          <t>DSGR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FRSH</t>
+          <t>FEAM</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FTRE</t>
+          <t>DSGX</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>FERA</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>ECPG</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GIW</t>
+          <t>FLYE</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>EDHL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>FRPT</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>ETSY</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GOOGM</t>
+          <t>FRSH</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GOOGN</t>
+          <t>EVRG</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>GRAL</t>
+          <t>GIW</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>EXEL</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>FAST</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
           <t>GRDX</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>HLP</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>HPK</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>HURN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IBRX</t>
+          <t>FDBC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>HURN</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>FLYW</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
           <t>ICFI</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>INGN</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>INTR</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IOVA</t>
+          <t>FTRE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IRMD</t>
+          <t>IMKTA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>JFU</t>
+          <t>GAINZ</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>JOYY</t>
+          <t>INGN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>JRSH</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>KDP</t>
+          <t>INTR</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>KNSA</t>
+          <t>GECCI</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>KOD</t>
+          <t>IOVA</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>KRNT</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>IRMD</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>LAUR</t>
+          <t>HLP</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LCUT</t>
+          <t>KDP</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>LGND</t>
+          <t>ICG</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>KRNT</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>LVLU</t>
+          <t>IPXG</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LYFT</t>
+          <t>KRT</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>ISRG</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>LAUR</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
           <t>MANE</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>MAR</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>MATH</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>MDLN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MDXG</t>
+          <t>JRSH</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MEDP</t>
+          <t>MATH</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MKTX</t>
+          <t>KOD</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>MORN</t>
+          <t>MDLN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>KRSA</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>MEOH</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MWYN</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NICE</t>
+          <t>MMSI</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>NIQ</t>
+          <t>LVLU</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>NMAD</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NVAX</t>
+          <t>LYFT</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1145,394 +1145,456 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>OLLI</t>
+          <t>PAX</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>OTEX</t>
+          <t>MCGA</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>PAX</t>
+          <t>PCRX</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PCTY</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>PLGO</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>PRHI</t>
+          <t>MWYN</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>PRTH</t>
+          <t>PNTG</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PRVA</t>
+          <t>NCPL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>PPLC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>QDEL</t>
+          <t>NMFCZ</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>QNBC</t>
+          <t>PRTH</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>RCBC</t>
+          <t>NTWK</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>RGC</t>
+          <t>PRVA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>RPD</t>
+          <t>OKTA</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>RTSN</t>
+          <t>PTC</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>RZLT</t>
+          <t>OLLI</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SAFT</t>
+          <t>QNBC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SANG</t>
+          <t>OTEX</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>SCHL</t>
+          <t>RGCO</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SEZL</t>
+          <t>PACH</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SJ</t>
+          <t>RPD</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SMXT</t>
+          <t>PAHC</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SND</t>
+          <t>RTSN</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SOTK</t>
+          <t>PCTY</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SPT</t>
+          <t>SAFT</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SSNC</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>STNE</t>
+          <t>SCHL</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SWKHL</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SWRD</t>
+          <t>SEZL</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>TEAM</t>
+          <t>PRHI</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>TRI</t>
+          <t>SJ</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>TRMB</t>
+          <t>RCBC</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SLDE</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>VAI</t>
+          <t>RILYG</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VALU</t>
+          <t>SLSN</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>WCCB</t>
+          <t>RPAY</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ELOG</t>
+          <t>SMXT</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ODD</t>
+          <t>RWAYL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ASO</t>
+          <t>SPSC</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AIXI</t>
+          <t>SND</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SUJA</t>
+          <t>SPT</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>RELL</t>
+          <t>SOTK</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>JYD</t>
+          <t>STLD</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BOLT</t>
+          <t>SSNC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>AHG</t>
+          <t>STNE</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>PDSB</t>
+          <t>STGW</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>OPLN</t>
+          <t>SWKHL</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>KMRK</t>
+          <t>SUJA</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>LIFE</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>TJGC</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>HEPS</t>
+          <t>YDES</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BYRN</t>
+          <t>TRI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NTSK</t>
+          <t>ZSQR</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ZSQR</t>
+          <t>VALU</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ACIC</t>
+          <t>CRNC</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BMR</t>
+          <t>AHCO</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>PICS</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>LOCO</t>
+          <t>OPCH</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ENSC</t>
+          <t>APEI</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PCRX</t>
+          <t>DCBO</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BORR</t>
+          <t>ACIC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>PICS</t>
+          <t>KMRK</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>OPCH</t>
+          <t>NIQ</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MQ</t>
+          <t>HEPS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PROF</t>
+          <t>HAS</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>JYD</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>JDZG</t>
+          <t>QDEL</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>RPGL</t>
+          <t>ELOG</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FLYE</t>
+          <t>AIXI</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>BLKB</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>BRBI</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>HSTM</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ENSC</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>GIBO</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LOCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>HPK</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>PDSB</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>SHPH</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>APA</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>EZPW</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_merged_latest.xlsx
+++ b/results/momentum_merged_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AFRM</t>
+          <t>FELE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -463,83 +463,83 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ACHC</t>
+          <t>ACIC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AFYA</t>
+          <t>AFRI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ATOS</t>
+          <t>FLX</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CLWT</t>
+          <t>AHCO</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AHG</t>
+          <t>AIXI</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GOOGM</t>
+          <t>LMAT</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CWCO</t>
+          <t>FBYD</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AFRI</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AISP</t>
+          <t>AMPH</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>JDZG</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FBYD</t>
+          <t>FOIL</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ALRM</t>
+          <t>AEP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ANGH</t>
+          <t>AMPL</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RPGL</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -551,1050 +551,1564 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>AERO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>APPN</t>
+          <t>ANDG</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RSVR</t>
+          <t>PHUN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ISPR</t>
+          <t>MAZE</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AOUT</t>
+          <t>AGYS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ARQT</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TLS</t>
+          <t>PTON</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>RZLT</t>
+          <t>PNRG</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ATLCL</t>
+          <t>AIRT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ARX</t>
+          <t>APEI</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AUGO</t>
+          <t>SOMN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ASO</t>
+          <t>RPC</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AVTR</t>
+          <t>ALLT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ATEC</t>
+          <t>ASTH</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>ALRM</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ATRA</t>
+          <t>ATLCL</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BLKB</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AUC</t>
+          <t>ATRA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BMBL</t>
+          <t>ANGI</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AVPT</t>
+          <t>ATRC</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BMNP</t>
+          <t>AOUT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BLIV</t>
+          <t>AVPT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BORR</t>
+          <t>API</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>BPRE</t>
+          <t>AVTR</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BREZ</t>
+          <t>APPN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BRLT</t>
+          <t>AXIN</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BYRN</t>
+          <t>ARQT</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>BSET</t>
+          <t>AZTA</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>ASBH</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BTSG</t>
+          <t>BEBE</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CAKE</t>
+          <t>ASO</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>BTSGU</t>
+          <t>BMR</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CBC</t>
+          <t>ATEC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BUUU</t>
+          <t>BORR</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CBFV</t>
+          <t>AUPH</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>BWIN</t>
+          <t>BOW</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CBLL</t>
+          <t>BIIB</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CBRL</t>
+          <t>BUUU</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>BL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CCEP</t>
+          <t>BWIN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>BLKB</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CLGN</t>
+          <t>BYRN</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>BRZE</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>COKE</t>
+          <t>BZ</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CRAC</t>
+          <t>BSY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>CBNK</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>BVFL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>CDNA</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CVSA</t>
+          <t>BZUN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>CAKE</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>CHPG</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DLO</t>
+          <t>CART</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>CMRC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DOCU</t>
+          <t>CBC</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EXLS</t>
+          <t>CRAC</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DSGR</t>
+          <t>CBFV</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FEAM</t>
+          <t>DBX</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>CBLL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>FERA</t>
+          <t>DH</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ECPG</t>
+          <t>CBRL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FLYE</t>
+          <t>DLO</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>EDHL</t>
+          <t>CCC</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FRPT</t>
+          <t>DLXY</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ETSY</t>
+          <t>CCEP</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FRSH</t>
+          <t>DMRC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>EVRG</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>GIW</t>
+          <t>EDHL</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>CENT</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>CHKP</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>GRDX</t>
+          <t>ELOG</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FDBC</t>
+          <t>CHRD</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>HURN</t>
+          <t>ENGS</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>FLYW</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ICFI</t>
+          <t>ENSC</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FTRE</t>
+          <t>CNXN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IMKTA</t>
+          <t>EVCM</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GAINZ</t>
+          <t>COKE</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>INGN</t>
+          <t>EXPO</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>INTR</t>
+          <t>FCBC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GECCI</t>
+          <t>CRCT</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>IOVA</t>
+          <t>FIZZ</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>CRNC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>IRMD</t>
+          <t>FRSH</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>CTAS</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>KDP</t>
+          <t>FVNNU</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ICG</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>KRNT</t>
+          <t>FXAC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>IPXG</t>
+          <t>CVLT</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>GCL</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>DAVE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LAUR</t>
+          <t>GEHC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>DCBO</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>MANE</t>
+          <t>GMAB</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>JRSH</t>
+          <t>DHCNL</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MATH</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>KOD</t>
+          <t>DOCU</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>MDLN</t>
+          <t>GRAN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>KRSA</t>
+          <t>DSGR</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MEOH</t>
+          <t>HOWL</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>DSGX</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>MMSI</t>
+          <t>HTFL</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>LVLU</t>
+          <t>EBAY</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>HURN</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>LYFT</t>
+          <t>EMBC</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>OCTV</t>
+          <t>IBEX</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>ETSY</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PAX</t>
+          <t>ICFI</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MCGA</t>
+          <t>EXEL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>PCRX</t>
+          <t>III</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>EXFY</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PLGO</t>
+          <t>IMKTA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MWYN</t>
+          <t>EXLS</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>PNTG</t>
+          <t>INTR</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>NCPL</t>
+          <t>EZPW</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PPLC</t>
+          <t>IOVA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NMFCZ</t>
+          <t>FDBC</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>PRTH</t>
+          <t>JANX</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>NTWK</t>
+          <t>FLYW</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PRVA</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>FNKO</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>LIFE</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>OLLI</t>
+          <t>FRD</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>QNBC</t>
+          <t>LQDT</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>OTEX</t>
+          <t>FTRE</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>RGCO</t>
+          <t>LVLU</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PACH</t>
+          <t>FWRG</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>RPD</t>
+          <t>MACI</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PAHC</t>
+          <t>GAING</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>RTSN</t>
+          <t>MAT</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PCTY</t>
+          <t>GAINZ</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SAFT</t>
+          <t>MDLN</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SCHL</t>
+          <t>MEOH</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>GDRX</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SEZL</t>
+          <t>MORN</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>PRHI</t>
+          <t>GIBO</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>SJ</t>
+          <t>MQ</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>RCBC</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SLDE</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>RILYG</t>
+          <t>GTLB</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>SLSN</t>
+          <t>MSGM</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>RPAY</t>
+          <t>HAS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SMXT</t>
+          <t>MTCH</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>RWAYL</t>
+          <t>HBIO</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>SPSC</t>
+          <t>NIQ</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SND</t>
+          <t>HCKT</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SPT</t>
+          <t>NKSH</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SOTK</t>
+          <t>HLP</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>STLD</t>
+          <t>NTES</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SSNC</t>
+          <t>HNNA</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>STNE</t>
+          <t>NXTC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>STGW</t>
+          <t>HTHT</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>SWKHL</t>
+          <t>OM</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SUJA</t>
+          <t>IBRX</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>OPCH</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>TJGC</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>YDES</t>
+          <t>OPRT</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>TRI</t>
+          <t>IPXG</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ZSQR</t>
+          <t>OPRX</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>VALU</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>CRNC</t>
+          <t>OVBC</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AHCO</t>
+          <t>JAKK</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PICS</t>
+          <t>PAHC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>OPCH</t>
+          <t>JOYY</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>APEI</t>
+          <t>PAX</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>KDP</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ACIC</t>
+          <t>PAYS</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>KMRK</t>
+          <t>KGEI</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NIQ</t>
+          <t>PCVX</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>HEPS</t>
+          <t>KNSA</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>PDSB</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>JYD</t>
+          <t>LAUR</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>QDEL</t>
+          <t>PENG</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ELOG</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AIXI</t>
+          <t>PFXNZ</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>BRBI</t>
+          <t>LOCO</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>HSTM</t>
+          <t>PLGO</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ENSC</t>
+          <t>LOPE</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GIBO</t>
+          <t>PLMR</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ODD</t>
+          <t>LYFT</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LOCO</t>
+          <t>PRDO</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>HPK</t>
+          <t>MANH</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PDSB</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SHPH</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>QQQX</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>EZPW</t>
+          <t>MDLZ</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CART</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
+          <t>RILYG</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>MEDP</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>RTSN</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>MKTX</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>RUSHB</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>MMSI</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>RVSB</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>MWYN</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>SAFT</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>NAVN</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>SAMG</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>NCPL</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>SBAC</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>NRDS</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>SCHL</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>NSIT</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>SEZL</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>NTAP</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>SGC</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>NTWK</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>SHPH</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>OCTV</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>SIBN</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>ODD</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>SJ</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>OLLI</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>SKWD</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>OSW</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>SKYA</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>OTEX</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>SMPL</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>SMTI</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>PBYI</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>SNFCA</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>SOTK</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>PCYO</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>SPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>PNTG</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>SSTI</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>PPLC</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>STRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>PRHI</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>SWKHL</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>PRVA</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>SWRD</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>PTLO</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>TECH</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>RCEL</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>TLN</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>RELY</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>TRMB</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>RGC</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>RPAY</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>VYLR</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>RPD</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>YDES</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>RRGB</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>SLDE</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>SPSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>SSNC</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>STLN</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>STRC</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>STRF</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>TASK</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>TBCH</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>TEAM</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>TRI</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>VSXY</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>WLTH</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>PCRX</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>QDEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>OXSQ</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>SUJA</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>HPK</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>FLYE</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>AHG</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>PICS</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>FRPT</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>ACHC</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>JYD</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>JDZG</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>JZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>SMXT</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>AGBK</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>HSTM</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NVAX</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>KMRK</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>ICG</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>CRVL</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>BRBI</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_merged_latest.xlsx
+++ b/results/momentum_merged_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D77"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,46 +446,46 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ADMA</t>
+          <t>ACHC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FELE</t>
+          <t>ACIW</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AER</t>
+          <t>BHST</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ACIC</t>
+          <t>ACGL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AFRI</t>
+          <t>AFYA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FLX</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AHCO</t>
+          <t>CABR</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>ACIC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -495,29 +495,29 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LMAT</t>
+          <t>MAZE</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FBYD</t>
+          <t>EXC</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AMPH</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>NDLS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -534,1581 +534,1045 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AMPL</t>
+          <t>AMPH</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>GTM</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>IIIV</t>
+          <t>AGBK</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AERO</t>
+          <t>APOG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ANDG</t>
+          <t>IIIV</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PHUN</t>
+          <t>AGCC</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MAZE</t>
+          <t>ASO</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AGYS</t>
+          <t>LNT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>AOUT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PTON</t>
+          <t>ATLCZ</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PNRG</t>
+          <t>OMCL</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AIRT</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>ATOS</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>RPC</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>APEI</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>SOMN</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>RPC</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ALLT</t>
+          <t>ATRC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ASTH</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ALRM</t>
+          <t>AUGO</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ATLCL</t>
+          <t>ARX</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>BCPC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ATRA</t>
+          <t>ASBH</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ANGI</t>
+          <t>BOLT</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ATRC</t>
+          <t>ATKR</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AOUT</t>
+          <t>BORR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AVPT</t>
+          <t>AVTR</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>BRLT</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>AVTR</t>
+          <t>BLKB</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>APPN</t>
+          <t>BWIN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AXIN</t>
+          <t>BLMN</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ARQT</t>
+          <t>CBNK</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>AZTA</t>
+          <t>BOW</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ASBH</t>
+          <t>CDRO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BEBE</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ASO</t>
+          <t>CENTA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>BMR</t>
+          <t>BYRN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ATEC</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BORR</t>
+          <t>BZ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AUPH</t>
+          <t>CRAI</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>BOW</t>
+          <t>BZUN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BUUU</t>
+          <t>CBC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BL</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>BWIN</t>
+          <t>CBRL</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BLKB</t>
+          <t>DBX</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BYRN</t>
+          <t>CCC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BRZE</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>CCEP</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BSY</t>
+          <t>EDHL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CBNK</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BVFL</t>
+          <t>ELOG</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>CENT</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BZUN</t>
+          <t>EVRG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>CHRD</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CAKE</t>
+          <t>EXPO</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CHPG</t>
+          <t>CME</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CART</t>
+          <t>FELE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CMRC</t>
+          <t>COKE</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CBC</t>
+          <t>FRPT</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CRAC</t>
+          <t>COR</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CBFV</t>
+          <t>FSBW</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DBX</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CBLL</t>
+          <t>GAING</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>CSGP</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CBRL</t>
+          <t>GEHC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DLO</t>
+          <t>CTAS</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CCC</t>
+          <t>GGR</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>DLXY</t>
+          <t>DAAQ</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CCEP</t>
+          <t>GMAB</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DMRC</t>
+          <t>DBCA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>GRAN</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>EDHL</t>
+          <t>DDI</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CENT</t>
+          <t>HALO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>DLTR</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CHKP</t>
+          <t>HCKT</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ELOG</t>
+          <t>DMLP</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CHRD</t>
+          <t>ICFI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>DUKU</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
           <t>ENGS</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>CME</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>ENSC</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CNXN</t>
+          <t>INBKZ</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>EVCM</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>COKE</t>
+          <t>INGN</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>EXLS</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>IRMD</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>FANG</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>JBDI</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>FCBC</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>CRCT</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>FIZZ</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CRNC</t>
+          <t>JCSE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FRSH</t>
+          <t>FDBC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>JYD</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>FVNNU</t>
+          <t>FIZZ</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FXAC</t>
+          <t>FOSL</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CVLT</t>
+          <t>LIFE</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>FRHC</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DAVE</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GEHC</t>
+          <t>FVNNU</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>LOPE</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>GCL</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DHCNL</t>
+          <t>LQDT</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>HAS</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DOCU</t>
+          <t>LVLU</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>GRAN</t>
+          <t>HPK</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DSGR</t>
+          <t>MATH</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>HOWL</t>
+          <t>HSTM</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>MRSH</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>HTFL</t>
+          <t>HTHT</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>MSGM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>HURN</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>EMBC</t>
+          <t>NKSH</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>IBEX</t>
+          <t>JG</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ETSY</t>
+          <t>NWE</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ICFI</t>
+          <t>KDP</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>OLB</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>KGEI</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>EXFY</t>
+          <t>OLLI</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>IMKTA</t>
+          <t>LIND</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>EXLS</t>
+          <t>OPLN</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>INTR</t>
+          <t>LOCO</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>EZPW</t>
+          <t>OSW</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>IOVA</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>FDBC</t>
+          <t>PAHC</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>JANX</t>
+          <t>MDLZ</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>FLYW</t>
+          <t>PCTY</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>MEDP</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>FNKO</t>
+          <t>PDSB</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LIFE</t>
+          <t>MEOH</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>FRD</t>
+          <t>PEBK</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>LQDT</t>
+          <t>MKTX</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>FTRE</t>
+          <t>PLGO</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LVLU</t>
+          <t>MWYN</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>FWRG</t>
+          <t>RGCO</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MACI</t>
+          <t>NATH</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>GAING</t>
+          <t>RILYG</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>MAT</t>
+          <t>NAVN</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>GAINZ</t>
+          <t>RTSN</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MDLN</t>
+          <t>NCPL</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>RWAYM</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>MEOH</t>
+          <t>PLMR</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>GDRX</t>
+          <t>SAFT</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MORN</t>
+          <t>PPLC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GIBO</t>
+          <t>SBAC</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>MQ</t>
+          <t>PTLO</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>SGRY</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>RGC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>GTLB</t>
+          <t>SJ</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>MSGM</t>
+          <t>RYZ</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>SKWD</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MTCH</t>
+          <t>SGC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>HBIO</t>
+          <t>SMPL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NIQ</t>
+          <t>SLDE</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>HCKT</t>
+          <t>SMXT</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NKSH</t>
+          <t>SOMN</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>SPSC</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NTES</t>
+          <t>STLD</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>HNNA</t>
+          <t>STRA</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NXTC</t>
+          <t>TECH</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>HTHT</t>
+          <t>SWKHL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>OM</t>
+          <t>TRI</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>IBRX</t>
+          <t>SWRD</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>OPCH</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>TCRT</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>OPRT</t>
+          <t>TDAY</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>IPXG</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>OPRX</t>
+          <t>UTHR</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>VSXY</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>OVBC</t>
+          <t>VYLR</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>JAKK</t>
+          <t>XFLH</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PAHC</t>
+          <t>DCBO</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>JOYY</t>
+          <t>ODD</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>PAX</t>
+          <t>FWRG</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>KDP</t>
+          <t>PRVA</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PAYS</t>
+          <t>DSGX</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>KGEI</t>
+          <t>TBCH</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>PCVX</t>
+          <t>PCRX</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>KNSA</t>
+          <t>ARQT</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PDSB</t>
+          <t>ICG</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>LAUR</t>
+          <t>SSEAU</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>PENG</t>
+          <t>HLP</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>BMBL</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PFXNZ</t>
+          <t>JZ</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>LOCO</t>
+          <t>SKYA</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>PLGO</t>
+          <t>JDZG</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>LOPE</t>
+          <t>ETSY</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PLMR</t>
+          <t>EMBC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>LYFT</t>
+          <t>GIBO</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>PRDO</t>
+          <t>AHG</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MANH</t>
+          <t>OTEX</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PYPL</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>MAR</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>QQQX</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>MDLZ</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>RILYG</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>MEDP</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>RTSN</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>MKTX</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>RUSHB</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>MMSI</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>RVSB</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>MWYN</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>SAFT</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>NAVN</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>SAMG</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>NCPL</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>SBAC</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>NRDS</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>SCHL</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>NSIT</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>SEZL</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>NTAP</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>SGC</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>NTWK</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>SHPH</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>OCTV</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>SIBN</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>ODD</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>SJ</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>OLLI</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>SKWD</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>OSW</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>SKYA</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>OTEX</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>SMPL</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>SMTI</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>PBYI</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>SNFCA</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>PCTY</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>SOTK</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>PCYO</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>SPT</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>PNTG</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>SSTI</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>PPLC</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>STRA</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>PRHI</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>SWKHL</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>PRVA</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>SWRD</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>PTLO</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>TECH</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>RCEL</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>TLN</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>RELY</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>TRMB</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>RGC</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>TW</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>RPAY</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>VYLR</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>RPD</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>YDES</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>RRGB</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>SHOP</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>SLDE</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>SPSC</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>SSNC</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>STLN</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>STRC</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>STRF</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>TASK</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>TBCH</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>TEAM</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>TRI</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>VSXY</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>WLTH</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>PCRX</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>QDEL</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>OXSQ</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>SUJA</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>HPK</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>FLYE</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>AHG</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>PICS</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>FRPT</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>JG</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>ACHC</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>JYD</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>JDZG</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>JZ</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>SMXT</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>AGBK</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>HSTM</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>NVAX</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>KMRK</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>ICG</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>CRVL</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>BRBI</t>
-        </is>
-      </c>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_merged_latest.xlsx
+++ b/results/momentum_merged_latest.xlsx
@@ -1458,68 +1458,68 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>FWRG</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ODD</t>
+          <t>PCRX</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>FWRG</t>
+          <t>ETSY</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PRVA</t>
+          <t>OTEX</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>GIBO</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>TBCH</t>
+          <t>AHG</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>PCRX</t>
+          <t>DCBO</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ARQT</t>
+          <t>DSGX</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ICG</t>
+          <t>TBCH</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SSEAU</t>
+          <t>SKYA</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>EMBC</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BMBL</t>
+          <t>SSEAU</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1529,46 +1529,46 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SKYA</t>
+          <t>PRVA</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>JDZG</t>
+          <t>ARQT</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ETSY</t>
+          <t>BMBL</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>EMBC</t>
+          <t>ICG</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>GIBO</t>
+          <t>ODD</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>AHG</t>
+          <t>HLP</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>OTEX</t>
+          <t>EBAY</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>JDZG</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>

--- a/results/momentum_merged_latest.xlsx
+++ b/results/momentum_merged_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,281 +441,281 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AERO</t>
+          <t>BRZE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ACIC</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BKYI</t>
+          <t>AMSF</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>BIII</t>
+          <t>JCSE</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ADMA</t>
+          <t>ACGL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CABR</t>
+          <t>ASTH</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CFFI</t>
+          <t>ACHC</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AFYA</t>
+          <t>CASY</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CASY</t>
+          <t>ACIC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>COCO</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ALLT</t>
+          <t>ACIW</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>COCO</t>
+          <t>DAKT</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ALRM</t>
+          <t>GTM</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CV</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NATH</t>
+          <t>IOTR</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ANDG</t>
+          <t>ADUS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DAKT</t>
+          <t>ISPR</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RGC</t>
+          <t>AFYA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>JZ</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EXE</t>
+          <t>AGYS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>VAI</t>
+          <t>LMAT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>APEI</t>
+          <t>ALRM</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FOIL</t>
+          <t>LZ</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>APOG</t>
+          <t>AMPH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>AMPL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>INTJ</t>
+          <t>MGPI</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ARHS</t>
+          <t>ANDG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IOTR</t>
+          <t>MLKN</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ARQT</t>
+          <t>ANGI</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>JDZG</t>
+          <t>ODFL</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ARX</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>OFIX</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ARXS</t>
+          <t>APEI</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>OMCL</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ASBH</t>
+          <t>APPF</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NDLS</t>
+          <t>OSW</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ATLCL</t>
+          <t>APPN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ODFL</t>
+          <t>PDD</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ATLCZ</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>OMCL</t>
+          <t>PGNY</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ATLO</t>
+          <t>ARHS</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>OSG</t>
+          <t>PLAY</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AUDC</t>
+          <t>ARQT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PGNY</t>
+          <t>PODD</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BCML</t>
+          <t>ARXS</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>PWRL</t>
+          <t>PPLC</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BLKB</t>
+          <t>ASO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SCHL</t>
+          <t>QDEL</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BLMN</t>
+          <t>ATLCZ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -727,882 +727,1230 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BMBL</t>
+          <t>ATLO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BPRN</t>
+          <t>STFS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BSET</t>
+          <t>ATRC</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>BSVN</t>
+          <t>TDAY</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BWIN</t>
+          <t>AUPH</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BWMN</t>
+          <t>TRIP</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BYRN</t>
+          <t>AVPT</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>BZUN</t>
+          <t>AZN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CBNK</t>
+          <t>BIIB</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CBRL</t>
+          <t>BL</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>BLKB</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>COKE</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>COLM</t>
+          <t>BRBR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>BRCB</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>BRLT</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CPHC</t>
+          <t>BSET</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CPOP</t>
+          <t>BSP</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CRAI</t>
+          <t>BSY</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>BTSG</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CSX</t>
+          <t>BVFL</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CVSA</t>
+          <t>BWIN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DAVE</t>
+          <t>BWMN</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>BZ</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>CAI</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DMRC</t>
+          <t>CAKE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DSGR</t>
+          <t>CAQ</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>CART</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>CBLL</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>EXLS</t>
+          <t>CBNK</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>CCEP</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>EZPW</t>
+          <t>CDNA</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FACT</t>
+          <t>CDW</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>CENT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FCBC</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FDBC</t>
+          <t>CFFI</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>FLYE</t>
+          <t>CHA</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FMAO</t>
+          <t>CHAD</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FOSL</t>
+          <t>CHKP</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>FRPT</t>
+          <t>CHRD</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>FTRE</t>
+          <t>CHYM</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GAINI</t>
+          <t>CINF</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GRDX</t>
+          <t>COKE</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>HALO</t>
+          <t>COR</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>HOWL</t>
+          <t>CRAI</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>HPK</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>HWKN</t>
+          <t>CSGP</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IBEX</t>
+          <t>CTAS</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>IIIV</t>
+          <t>CV</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>INGN</t>
+          <t>CVSA</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>DBX</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>INTR</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>IOSP</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>IPXG</t>
+          <t>DLO</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>DLTR</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>JCSE</t>
+          <t>DMRC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>JOYY</t>
+          <t>DOCU</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>JRSH</t>
+          <t>DOX</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>JYD</t>
+          <t>DSGX</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>KMRK</t>
+          <t>DSP</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>KOD</t>
+          <t>EBAY</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LAUR</t>
+          <t>EDHL</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>LIFE</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>EFSI</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>LOGI</t>
+          <t>EMBC</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LOPE</t>
+          <t>ENGS</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>ENSC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MAZE</t>
+          <t>ERIE</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MEOH</t>
+          <t>ETSY</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>MMSI</t>
+          <t>EVCM</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MNST</t>
+          <t>EXEL</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MTCH</t>
+          <t>EXLS</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NAUT</t>
+          <t>EXPE</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NAVN</t>
+          <t>EXPO</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>NKSH</t>
+          <t>FANG</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NSIT</t>
+          <t>FCBC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>NTRSO</t>
+          <t>FIZZ</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NTWK</t>
+          <t>FRSH</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>NXPL</t>
+          <t>FTDR</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>OFRM</t>
+          <t>FTRE</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>OLB</t>
+          <t>FWRG</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>OM</t>
+          <t>GCT</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>OPLN</t>
+          <t>GDRX</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>OTEX</t>
+          <t>GEGGL</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>OXLCZ</t>
+          <t>GEHC</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>PAHC</t>
+          <t>GMAB</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PCRX</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PEBK</t>
+          <t>GTLB</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>PICS</t>
+          <t>HALO</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>PLUS</t>
+          <t>HAS</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PRCH</t>
+          <t>HCKT</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PRDO</t>
+          <t>HELE</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PRME</t>
+          <t>HLP</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>HTHT</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PXS</t>
+          <t>HUIZ</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>QNBC</t>
+          <t>HWKN</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>RGCO</t>
+          <t>IBEX</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>RNW</t>
+          <t>ICFI</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>RPC</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>RPD</t>
+          <t>IIIV</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>RTSN</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>RVSB</t>
+          <t>INTR</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>RYZ</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SAIC</t>
+          <t>IOSP</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SAIH</t>
+          <t>IPAR</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>SAMG</t>
+          <t>ISRG</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SCSC</t>
+          <t>JAKK</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SGC</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SKWD</t>
+          <t>JOYY</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>SKYA</t>
+          <t>JVA</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SLDE</t>
+          <t>KDP</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SMXT</t>
+          <t>KGEI</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SPT</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>SSNC</t>
+          <t>KMTS</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STLD</t>
+          <t>KNSA</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>STNE</t>
+          <t>KOD</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SUJA</t>
+          <t>LAUR</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>SUNB</t>
+          <t>LFCR</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>TCRT</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>TILE</t>
+          <t>LKFT</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>TRNZ</t>
+          <t>LOGI</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>MANH</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>VSXY</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>YSWY</t>
+          <t>MAZE</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>PCTY</t>
+          <t>MDLZ</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>FWRG</t>
+          <t>MEDP</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PLMR</t>
+          <t>MEOH</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>OLLI</t>
+          <t>MMSI</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MWYN</t>
+          <t>MNDY</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>EDHL</t>
+          <t>MNRO</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>MNST</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>KDP</t>
+          <t>MORN</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>CHRD</t>
+          <t>MRSH</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ICG</t>
+          <t>MTCH</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>MWYN</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ASO</t>
+          <t>NATH</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>AOUT</t>
+          <t>NAVN</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SMPL</t>
+          <t>NCNO</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>NDAQ</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FIZZ</t>
+          <t>NIQ</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>TRI</t>
+          <t>NRDS</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CSGP</t>
+          <t>NTRSO</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>TBCH</t>
+          <t>NWE</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>PTLO</t>
+          <t>NWS</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NWSA</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CCEP</t>
+          <t>ODD</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NCPL</t>
+          <t>OFRM</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>OFS</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ODD</t>
+          <t>OLLI</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PFAI</t>
+          <t>ONC</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ETSY</t>
+          <t>OPCH</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>ORIQ</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>PRVA</t>
+          <t>ORLY</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>JZ</t>
+          <t>OTEX</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MGPI</t>
+          <t>OXLCM</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CAKE</t>
+          <t>PCTY</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LYFT</t>
-        </is>
-      </c>
+          <t>PEGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>PICS</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>PLGO</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>PRCH</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>PRDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>PRVA</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>PTC</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>PTLO</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>PTON</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>PYPL</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>QNBC</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>RCEL</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>REAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>REGN</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>RELY</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ROP</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>ROST</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>RPAY</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>RPC</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>RPRX</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>RRGB</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>RTSN</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>RVSB</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>SAIC</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>SGRY</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>SHOO</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>SIBN</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>SKWD</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>SKYA</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>SLDE</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>SNFCA</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>SPSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>SPT</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>SSNC</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>SSTI</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>STNE</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>STRA</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>SYNA</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>SZZL</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>TEAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>TRI</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>TRMB</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>UTHR</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>VAI</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>XZO</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>YSWY</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>BLMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>CBRL</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>DCBO</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>BYRN</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>TBCH</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>JDZG</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>MXCT</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>JBDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>IDXX</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>RGC</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>BMBL</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>TCRT</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>JYD</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>HPK</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_merged_latest.xlsx
+++ b/results/momentum_merged_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D70"/>
+  <dimension ref="A1:D71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,39 +441,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BRZE</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>AER</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AMSF</t>
+          <t>ACHC</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>JCSE</t>
+          <t>ATAT</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ACGL</t>
+          <t>ACIW</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ASTH</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ACHC</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -485,1472 +485,1490 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ACIC</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>COCO</t>
+          <t>CHDN</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ACIW</t>
+          <t>ADUS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DAKT</t>
+          <t>CROX</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>AEP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GTM</t>
+          <t>CSX</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>AGYS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>IOTR</t>
+          <t>ENSG</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ADUS</t>
+          <t>ALRM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ISPR</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AFYA</t>
+          <t>AMPL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>JZ</t>
+          <t>FLX</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AGYS</t>
+          <t>ANDG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LMAT</t>
+          <t>FSV</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ALRM</t>
+          <t>APEI</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>JDZG</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AMPH</t>
+          <t>APOG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>KWY</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AMPL</t>
+          <t>APPF</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MGPI</t>
+          <t>LNT</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ANDG</t>
+          <t>APPN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MLKN</t>
+          <t>ODFL</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ANGI</t>
+          <t>ARHS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ODFL</t>
+          <t>OFIX</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>ARLP</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OFIX</t>
+          <t>OXSQ</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>APEI</t>
+          <t>ARQT</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>OMCL</t>
+          <t>PECO</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>APPF</t>
+          <t>ASBH</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>OSW</t>
+          <t>PWRL</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>APPN</t>
+          <t>ASO</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>QDEL</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>ATEC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PGNY</t>
+          <t>SOLS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ARHS</t>
+          <t>ATRC</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>PLAY</t>
+          <t>STFS</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ARQT</t>
+          <t>AUDC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PODD</t>
+          <t>TCMD</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ARXS</t>
+          <t>AUPH</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>PPLC</t>
+          <t>AVPT</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ASO</t>
+          <t>AVTR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>QDEL</t>
+          <t>BCML</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ATLCZ</t>
+          <t>BL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SOLS</t>
+          <t>BLKB</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ATLO</t>
+          <t>BRBR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>STFS</t>
+          <t>BSVN</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ATRC</t>
+          <t>BSY</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>TDAY</t>
+          <t>BTSG</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AUPH</t>
+          <t>BVS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TRIP</t>
+          <t>BWIN</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AVPT</t>
+          <t>BZ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>BZUN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>CAI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BL</t>
+          <t>CAKE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BLKB</t>
+          <t>CART</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>CBC</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BRBR</t>
+          <t>CBLL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BRCB</t>
+          <t>CBRL</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BRLT</t>
+          <t>CDNA</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>BSET</t>
+          <t>CDW</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BSP</t>
+          <t>CDZI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BSY</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BTSG</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>BVFL</t>
+          <t>CHAD</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BWIN</t>
+          <t>CHRD</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BWMN</t>
+          <t>CHYM</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>CINF</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CAI</t>
+          <t>CMRC</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CAKE</t>
+          <t>CRAI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CAQ</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CART</t>
+          <t>CSGP</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CBLL</t>
+          <t>CTSH</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CBNK</t>
+          <t>CV</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CCEP</t>
+          <t>CVLT</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>DAKT</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>DAVE</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CENT</t>
+          <t>DBX</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>DCBO</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CFFI</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>DLO</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CHAD</t>
+          <t>DLTR</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CHKP</t>
+          <t>DMRC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CHRD</t>
+          <t>DOCU</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CHYM</t>
+          <t>DSGR</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CINF</t>
+          <t>DSGX</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>DSP</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>COKE</t>
+          <t>EBAY</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>EFSI</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>EMBC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CRAI</t>
+          <t>ENGS</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>ERIE</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>CSGP</t>
+          <t>ETSY</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>EVRG</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>EXEL</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CV</t>
+          <t>EXFY</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>CVSA</t>
+          <t>EXLS</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DBX</t>
+          <t>EXPO</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>EZPW</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>FAST</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>DLO</t>
+          <t>FRSH</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DLTR</t>
+          <t>FTDR</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DMRC</t>
+          <t>FTRE</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>DOCU</t>
+          <t>GABC</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>DOX</t>
+          <t>GDRX</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>GDYN</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DSP</t>
+          <t>GMAB</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>GRDX</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>EDHL</t>
+          <t>GTLB</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>GTM</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>EFSI</t>
+          <t>HALO</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>EMBC</t>
+          <t>HAS</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>HOWL</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ENSC</t>
+          <t>HPK</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ERIE</t>
+          <t>HSTM</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ETSY</t>
+          <t>HTFL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>EVCM</t>
+          <t>HURN</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EXLS</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>EXPE</t>
+          <t>IGAC</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>III</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>FANG</t>
+          <t>IIIV</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FCBC</t>
+          <t>INGN</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FIZZ</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>FRSH</t>
+          <t>INTU</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>FTDR</t>
+          <t>IOSP</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FTRE</t>
+          <t>IOVA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FWRG</t>
+          <t>IPAR</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>IRMD</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>GDRX</t>
+          <t>JAKK</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GEGGL</t>
+          <t>JCAP</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GEHC</t>
+          <t>KOD</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>LIFE</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GTLB</t>
+          <t>LIND</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>HALO</t>
+          <t>LKFT</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>LOCO</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HCKT</t>
+          <t>LOGI</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>HELE</t>
+          <t>LQDT</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>HTHT</t>
+          <t>MANH</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>HUIZ</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HWKN</t>
+          <t>MAZE</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>IBEX</t>
+          <t>MEDP</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ICFI</t>
+          <t>MEOH</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>MMSI</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>IIIV</t>
+          <t>MNDY</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>MNRO</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>INTR</t>
+          <t>MORN</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>MQ</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>IOSP</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>IPAR</t>
+          <t>MRSH</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>NATH</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>JAKK</t>
+          <t>NAUT</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>NAVN</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>JOYY</t>
+          <t>NCNO</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>JVA</t>
+          <t>NCPL</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>KDP</t>
+          <t>NDAQ</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>KGEI</t>
+          <t>NIQ</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>NSIT</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>KMTS</t>
+          <t>NTSK</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>KNSA</t>
+          <t>NTWK</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>KOD</t>
+          <t>NWE</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>LAUR</t>
+          <t>NWS</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LFCR</t>
+          <t>NXPL</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>OCTV</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>LKFT</t>
+          <t>ODD</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>LOGI</t>
+          <t>OFRM</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>MANH</t>
+          <t>OLB</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>ONC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MAZE</t>
+          <t>OPLN</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MDLZ</t>
+          <t>OPRT</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>MEDP</t>
+          <t>OPRX</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MEOH</t>
+          <t>OTAI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>MMSI</t>
+          <t>OTEX</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MNDY</t>
+          <t>PAA</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>MNRO</t>
+          <t>PAGP</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MNST</t>
+          <t>PAHC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>MORN</t>
+          <t>PAYS</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>PCTY</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>MRSH</t>
+          <t>PMTS</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MTCH</t>
+          <t>PODD</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>MWYN</t>
+          <t>PRCH</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>NATH</t>
+          <t>PRGS</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NAVN</t>
+          <t>PRME</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>NCNO</t>
+          <t>PRVA</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>PSIX</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>NIQ</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NRDS</t>
+          <t>PTLE</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>NTRSO</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NWE</t>
+          <t>QNBC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>NWS</t>
+          <t>RCEL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>RCKY</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ODD</t>
+          <t>REAL</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>OFRM</t>
+          <t>REF</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>OFS</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>OLLI</t>
+          <t>RELY</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ONC</t>
+          <t>RGC</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>OPCH</t>
+          <t>RGCO</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ORIQ</t>
+          <t>ROOT</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ORLY</t>
+          <t>ROST</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>OTEX</t>
+          <t>RPC</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>OXLCM</t>
+          <t>RPRX</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>PCTY</t>
+          <t>RTSN</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>PEGA</t>
+          <t>RVSB</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PICS</t>
+          <t>RYZ</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PLGO</t>
+          <t>SAIC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>PRCH</t>
+          <t>SBAC</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>PRDO</t>
+          <t>SEZL</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PRVA</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>SIBN</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>PTLO</t>
+          <t>SIGI</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>PTON</t>
+          <t>SJ</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>SKIN</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>QNBC</t>
+          <t>SKYA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>RCEL</t>
+          <t>SLN</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>REAL</t>
+          <t>SMPL</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>SNFCA</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>RELY</t>
+          <t>SPSC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ROP</t>
+          <t>SPT</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ROST</t>
+          <t>SSTI</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>RPAY</t>
+          <t>SUNB</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>RPC</t>
+          <t>SYNA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>RPRX</t>
+          <t>TASK</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>RRGB</t>
+          <t>TCRT</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>RTSN</t>
+          <t>TEAM</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>RVSB</t>
+          <t>TENB</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SAIC</t>
+          <t>TLN</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>SGRY</t>
+          <t>TRI</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SHOO</t>
+          <t>TRMB</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SIBN</t>
+          <t>UTHR</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>SKWD</t>
+          <t>VYLR</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SKYA</t>
+          <t>WLTH</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SLDE</t>
+          <t>WSBCO</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SNFCA</t>
+          <t>XZO</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>SPSC</t>
+          <t>YMAT</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SPT</t>
+          <t>BYRN</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SSNC</t>
+          <t>AMCR</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SSTI</t>
+          <t>TBCH</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>STNE</t>
+          <t>HUIZ</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STRA</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SYNA</t>
+          <t>BMBL</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>SZZL</t>
+          <t>ROP</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>TEAM</t>
+          <t>ADMA</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>TRI</t>
+          <t>EDHL</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>TRMB</t>
+          <t>ERIC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>IRLA</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>UTHR</t>
+          <t>JYD</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>VAI</t>
+          <t>EVER</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>XZO</t>
+          <t>MTC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>YSWY</t>
+          <t>BRCB</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>BLMN</t>
+          <t>SLDE</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CBRL</t>
+          <t>CNXC</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>JBDI</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>COKE</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>BYRN</t>
+          <t>PAYX</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>TBCH</t>
+          <t>FIZZ</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>JDZG</t>
+          <t>JRVR</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MXCT</t>
+          <t>MNST</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>JBDI</t>
+          <t>DH</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>EXPE</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>IDXX</t>
+          <t>ICG</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>RGC</t>
+          <t>NRDS</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>BMBL</t>
+          <t>MXCT</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>TCRT</t>
+          <t>SSNC</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>JYD</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>HPK</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
+          <t>HCM</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>HLP</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>WTW</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_merged_latest.xlsx
+++ b/results/momentum_merged_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,34 +441,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AER</t>
+          <t>AMSF</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ACHC</t>
+          <t>ACIW</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ATAT</t>
+          <t>CASY</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ACIW</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>CSX</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -478,7 +478,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CASY</t>
+          <t>FLX</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>GIII</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CROX</t>
+          <t>GPGI</t>
         </is>
       </c>
     </row>
@@ -512,1463 +512,1573 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CSX</t>
+          <t>IOTR</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AGYS</t>
+          <t>AFYA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ENSG</t>
+          <t>KLTR</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ALRM</t>
+          <t>AGIO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>LCNB</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AMPL</t>
+          <t>AGYS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FLX</t>
+          <t>LIF</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ANDG</t>
+          <t>ALLT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FSV</t>
+          <t>MGPI</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>APEI</t>
+          <t>ALRM</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>JDZG</t>
+          <t>NXGL</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>APOG</t>
+          <t>AMCR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KWY</t>
+          <t>ODFL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>APPF</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LNT</t>
+          <t>OSG</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>APPN</t>
+          <t>AMPH</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ODFL</t>
+          <t>PODD</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ARHS</t>
+          <t>AMPL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>OFIX</t>
+          <t>POOL</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ARLP</t>
+          <t>ANDG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OXSQ</t>
+          <t>REYN</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ARQT</t>
+          <t>ANIK</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>PECO</t>
+          <t>STFS</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ASBH</t>
+          <t>AOUT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PWRL</t>
+          <t>TRIP</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ASO</t>
+          <t>APEI</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>QDEL</t>
+          <t>APOG</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ATEC</t>
+          <t>APPN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SOLS</t>
+          <t>ARHS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ATRC</t>
+          <t>ATLO</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>STFS</t>
+          <t>AUPH</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AUDC</t>
+          <t>AVPT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TCMD</t>
+          <t>AVTR</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AUPH</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>AVPT</t>
+          <t>BANF</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AVTR</t>
+          <t>BCML</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BCML</t>
+          <t>BFST</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>BIIB</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>BL</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>BLKB</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BRBR</t>
+          <t>BLKB</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BSVN</t>
+          <t>BOW</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BSY</t>
+          <t>BPRN</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>BTSG</t>
+          <t>BR</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BVS</t>
+          <t>BRCB</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BWIN</t>
+          <t>BRZE</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>BSET</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>BZUN</t>
+          <t>BSVN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CAI</t>
+          <t>BSY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CAKE</t>
+          <t>BVS</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CART</t>
+          <t>BWIN</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CBC</t>
+          <t>BZUN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CBLL</t>
+          <t>CART</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>CBC</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CBNK</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>CBRL</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>CDNA</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>CDW</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CDZI</t>
+          <t>CCNE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>CENTA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>CERT</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>CHA</t>
-        </is>
-      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CHAD</t>
+          <t>CFFI</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CHRD</t>
+          <t>CGNT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CHYM</t>
+          <t>CHAD</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>CHKP</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
           <t>CINF</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>CMRC</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CRAI</t>
+          <t>CLAR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CSGP</t>
+          <t>CNXC</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>COST</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CV</t>
+          <t>CPIX</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CVLT</t>
+          <t>CRAI</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>DAKT</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>DAVE</t>
+          <t>CSGP</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DBX</t>
+          <t>CTAS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>CVLT</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>DLO</t>
+          <t>CVSA</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DLTR</t>
+          <t>CYRX</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DMRC</t>
+          <t>DAVE</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DOCU</t>
+          <t>DBX</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>DSGR</t>
+          <t>DCBO</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DSP</t>
+          <t>DMAC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>DMLP</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>EFSI</t>
+          <t>DOCU</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EMBC</t>
+          <t>DOX</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>DSGR</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ERIE</t>
+          <t>DSGX</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ETSY</t>
+          <t>DSP</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>EVRG</t>
+          <t>DUKU</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>EXFY</t>
+          <t>EGBN</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>EXLS</t>
+          <t>EMBC</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>ENGS</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EZPW</t>
+          <t>ENSC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>ERIE</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>FRSH</t>
+          <t>ESLT</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FTDR</t>
+          <t>ETSY</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FTRE</t>
+          <t>EVAX</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GABC</t>
+          <t>EVER</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>GDRX</t>
+          <t>EVRG</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GDYN</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>EXE</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>GRDX</t>
+          <t>EXEL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>GTLB</t>
+          <t>EXLS</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>GTM</t>
+          <t>EXPO</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>HALO</t>
+          <t>FIZZ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>FLYW</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>HOWL</t>
+          <t>FNKO</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>HPK</t>
+          <t>FNLC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>HSTM</t>
+          <t>FRSH</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>HTFL</t>
+          <t>FSV</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>HURN</t>
+          <t>FTDR</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>FTRE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>GDRX</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>IGAC</t>
+          <t>GDYN</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>GMAB</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>IIIV</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>INGN</t>
+          <t>GRDX</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>GTLB</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>GTM</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>IOSP</t>
+          <t>HAS</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>IOVA</t>
+          <t>HBNC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>IPAR</t>
+          <t>HCKT</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>IRMD</t>
+          <t>HCM</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>JAKK</t>
+          <t>HPK</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JCAP</t>
+          <t>HQY</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>KOD</t>
+          <t>HSTM</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LIFE</t>
+          <t>HTFL</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>HURN</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>LIND</t>
+          <t>IBEX</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>LKFT</t>
+          <t>ICFI</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LOCO</t>
+          <t>ICLR</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>LOGI</t>
+          <t>IDXX</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>LQDT</t>
+          <t>III</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>IIIV</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>MANH</t>
+          <t>INGN</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MAZE</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MEDP</t>
+          <t>IRMD</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>MEOH</t>
+          <t>IRON</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MMSI</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MNDY</t>
+          <t>JRSH</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MNRO</t>
+          <t>KDP</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>MORN</t>
+          <t>KGEI</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MQ</t>
+          <t>KIDS</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>KINS</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MRSH</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NATH</t>
+          <t>KRT</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>NAUT</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NAVN</t>
+          <t>LIND</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NCNO</t>
+          <t>LKFT</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NCPL</t>
+          <t>LMAT</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>LNT</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NIQ</t>
+          <t>LOPE</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NSIT</t>
+          <t>LQDT</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NTSK</t>
+          <t>LZ</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>NTWK</t>
+          <t>MANE</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NWE</t>
+          <t>MANH</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NWS</t>
+          <t>MAT</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NXPL</t>
+          <t>MICC</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>OCTV</t>
+          <t>MKTX</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ODD</t>
+          <t>MMSI</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>OFRM</t>
+          <t>MNDY</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>OLB</t>
+          <t>MNST</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ONC</t>
+          <t>MORN</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>OPLN</t>
+          <t>MQ</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>OPRT</t>
+          <t>MRSH</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>OPRX</t>
+          <t>MXCT</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>OTAI</t>
+          <t>MYGN</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>OTEX</t>
+          <t>MZTI</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>PAA</t>
+          <t>NATH</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>PAGP</t>
+          <t>NAUT</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PAHC</t>
+          <t>NAVN</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PAYS</t>
+          <t>NCNO</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>PCTY</t>
+          <t>NCPL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>PMTS</t>
+          <t>NDAQ</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PODD</t>
+          <t>NECB</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PRCH</t>
+          <t>NRDS</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>PRGS</t>
+          <t>NTRSO</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>PRME</t>
+          <t>NTSK</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PRVA</t>
+          <t>NTWK</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PSIX</t>
+          <t>NWE</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>NWS</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>PTLE</t>
+          <t>NWSA</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>OCCIM</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>QNBC</t>
+          <t>OFS</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>RCEL</t>
+          <t>OMCL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>RCKY</t>
+          <t>OPRT</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>REAL</t>
+          <t>ORIC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>REF</t>
+          <t>OSPN</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>OSW</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>RELY</t>
+          <t>OTAI</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>RGC</t>
+          <t>OTEX</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>RGCO</t>
+          <t>OTTR</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ROOT</t>
+          <t>OVBC</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ROST</t>
+          <t>PAGP</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>RPC</t>
+          <t>PAHC</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>RPRX</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>RTSN</t>
+          <t>PBYI</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>RVSB</t>
+          <t>PCRX</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>RYZ</t>
+          <t>PCTY</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SAIC</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SBAC</t>
+          <t>PGNY</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>SEZL</t>
+          <t>PLGO</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>PLMR</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SIBN</t>
+          <t>PLUS</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SIGI</t>
+          <t>PMTS</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>SJ</t>
+          <t>POWW</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SKIN</t>
+          <t>PRGS</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SKYA</t>
+          <t>PRTH</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SLN</t>
+          <t>PRVA</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>SMPL</t>
+          <t>PTEN</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SNFCA</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SPSC</t>
+          <t>QDEL</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SPT</t>
+          <t>QNBC</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>SSTI</t>
+          <t>RCEL</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SUNB</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SYNA</t>
+          <t>ROKU</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>TASK</t>
+          <t>ROOT</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>TCRT</t>
+          <t>ROP</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>TEAM</t>
+          <t>RPAY</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>TENB</t>
+          <t>RPC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>TLN</t>
+          <t>RPD</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>TRI</t>
+          <t>RPRX</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TRMB</t>
+          <t>RUSHB</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>RYZ</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>UTHR</t>
+          <t>SAIC</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VYLR</t>
+          <t>SBUX</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>WLTH</t>
+          <t>SCHL</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>WSBCO</t>
+          <t>SEIC</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>XZO</t>
+          <t>SIBN</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>YMAT</t>
+          <t>SIGI</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BYRN</t>
+          <t>SLDE</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AMCR</t>
+          <t>SLN</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>TBCH</t>
+          <t>SMXT</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>HUIZ</t>
+          <t>SPSC</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>SPT</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BMBL</t>
+          <t>SSNC</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ROP</t>
+          <t>STGW</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ADMA</t>
+          <t>STLN</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>EDHL</t>
+          <t>SYNA</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ERIC</t>
+          <t>TASK</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>IRLA</t>
+          <t>TCPC</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>JYD</t>
+          <t>TCRT</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>EVER</t>
+          <t>TEAM</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MTC</t>
+          <t>TENB</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>BRCB</t>
+          <t>TRI</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>SLDE</t>
+          <t>TRMB</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CNXC</t>
+          <t>TRXB</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>JBDI</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>COKE</t>
+          <t>UTHR</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>VAI</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>FIZZ</t>
+          <t>VSXY</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>JRVR</t>
+          <t>WLTH</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MNST</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>XZO</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>EXPE</t>
+          <t>YSWY</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ICG</t>
+          <t>BTOC</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>NRDS</t>
+          <t>TBCH</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>MXCT</t>
+          <t>DMRC</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SSNC</t>
+          <t>PEPG</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>ICG</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>MAZE</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LYFT</t>
+          <t>CDZI</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>OPK</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>WTW</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
+          <t>BMBL</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>BLMN</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LOGI</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>NRIX</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>JDZG</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>INDP</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>KPLT</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>ENTX</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>ONC</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>RGC</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>SKYA</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>ARQT</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>SKIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>RTSN</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>ASO</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>OLED</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>HUIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>JRVR</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>DH</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_merged_latest.xlsx
+++ b/results/momentum_merged_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D76"/>
+  <dimension ref="A1:D94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,1639 +446,2039 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AMSF</t>
+          <t>ACGL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ACIW</t>
+          <t>CASY</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CASY</t>
+          <t>AGNT</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>ACIW</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>ACIC</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>CSX</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>ADP</t>
-        </is>
-      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FLX</t>
+          <t>AMSF</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GIII</t>
+          <t>ADUS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ADUS</t>
+          <t>ENSG</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>GPGI</t>
+          <t>BRBR</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IOTR</t>
+          <t>AGIO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AFYA</t>
+          <t>FRPT</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>KLTR</t>
+          <t>CHNR</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LCNB</t>
+          <t>AGYS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AGYS</t>
+          <t>GIII</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LIF</t>
+          <t>DPZ</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ALLT</t>
+          <t>AEP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MGPI</t>
+          <t>ANIK</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ALRM</t>
+          <t>GPGI</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NXGL</t>
+          <t>FLX</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AMCR</t>
+          <t>ALRM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ODFL</t>
+          <t>APEI</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>HONA</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>OSG</t>
+          <t>JDZG</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AMPH</t>
+          <t>AMCR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PODD</t>
+          <t>APOG</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AMPL</t>
+          <t>IPAR</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>KLTR</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ANDG</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>REYN</t>
+          <t>ARLP</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ANIK</t>
+          <t>KWY</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>STFS</t>
+          <t>LIF</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AOUT</t>
+          <t>AMPL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TRIP</t>
+          <t>ASBP</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>APEI</t>
+          <t>ODFL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>APOG</t>
+          <t>MGPI</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>APPN</t>
+          <t>ANDG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ARHS</t>
+          <t>ATLCZ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ATLO</t>
+          <t>PECO</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>AUPH</t>
+          <t>NXGL</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AVPT</t>
+          <t>ANGI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AVTR</t>
+          <t>ATOS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>BANF</t>
+          <t>PODD</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BCML</t>
+          <t>APPN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BFST</t>
+          <t>AUPH</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>PTEN</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>BL</t>
+          <t>REYN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BLKB</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BOW</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BPRN</t>
+          <t>TILE</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>SHOE</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BRCB</t>
+          <t>ARHS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BRZE</t>
+          <t>BOW</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BSET</t>
+          <t>STFS</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>BSVN</t>
+          <t>ASBH</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BSY</t>
+          <t>BREZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BVS</t>
+          <t>TCMD</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BWIN</t>
+          <t>ASO</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>BZUN</t>
+          <t>BRZE</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CART</t>
+          <t>TRIB</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CBC</t>
+          <t>ATLCL</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CBNK</t>
+          <t>BSET</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CBRL</t>
+          <t>TRIP</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CCNE</t>
+          <t>ATLO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CENTA</t>
+          <t>BSP</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>AVBC</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CFFI</t>
+          <t>BUUU</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CGNT</t>
+          <t>AVPT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CHAD</t>
+          <t>BVFL</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CHKP</t>
+          <t>BANF</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CINF</t>
+          <t>BWIN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CLAR</t>
+          <t>BCAL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>BYRN</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CNXC</t>
+          <t>BCML</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>BZUN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CPIX</t>
+          <t>BCPC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CRAI</t>
+          <t>CART</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>BFST</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CSGP</t>
+          <t>CBC</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>BIIB</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>CBNK</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CVLT</t>
+          <t>BL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CVSA</t>
+          <t>CBRL</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CYRX</t>
+          <t>BLKB</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DAVE</t>
+          <t>CDZI</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DBX</t>
+          <t>BPRN</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>CENT</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DMAC</t>
+          <t>CFFI</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DMLP</t>
+          <t>BRCB</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>DOCU</t>
+          <t>CHDN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DOX</t>
+          <t>BSVN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DSGR</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>BSY</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>DSP</t>
+          <t>COKE</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DUKU</t>
+          <t>BVS</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>COLM</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>EGBN</t>
+          <t>CBFV</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>EMBC</t>
+          <t>CPIX</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>CCEP</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ENSC</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ERIE</t>
+          <t>CCNE</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ESLT</t>
+          <t>CVSA</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ETSY</t>
+          <t>CCNEP</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>EVAX</t>
+          <t>DCBO</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>EVER</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>EVRG</t>
+          <t>DDI</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>CENTA</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EXE</t>
+          <t>DGICA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>CHCO</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>EXLS</t>
+          <t>DHCNL</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>CHKP</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FIZZ</t>
+          <t>DIBS</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>FLYW</t>
+          <t>CINF</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>FNKO</t>
+          <t>DOX</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>FNLC</t>
+          <t>CLAR</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FRSH</t>
+          <t>DRDB</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>FSV</t>
+          <t>CNXC</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>FTDR</t>
+          <t>DSGX</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FTRE</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GDRX</t>
+          <t>DSP</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>GDYN</t>
+          <t>CRAC</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>EPSN</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>CRAI</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GRDX</t>
+          <t>ERIE</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GTLB</t>
+          <t>CSGP</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>GTM</t>
+          <t>ETSY</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>CTAS</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>HBNC</t>
+          <t>EXE</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>HCKT</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>EXEL</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>HPK</t>
+          <t>CVLT</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>HQY</t>
+          <t>EYE</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>HSTM</t>
+          <t>CWST</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>HTFL</t>
+          <t>FAST</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HURN</t>
+          <t>DAKT</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>IBEX</t>
+          <t>FIZZ</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ICFI</t>
+          <t>DAVE</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>FLYW</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>IDXX</t>
+          <t>DBX</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>FNKO</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>IIIV</t>
+          <t>DLTR</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>INGN</t>
+          <t>FNLC</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>DMAA</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>FOX</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>IRMD</t>
+          <t>DOCU</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>IRON</t>
+          <t>FRSH</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>DSGR</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>JRSH</t>
+          <t>FVN</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>KDP</t>
+          <t>DUKU</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>KGEI</t>
+          <t>GABC</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>KIDS</t>
+          <t>ECCU</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>KINS</t>
+          <t>GDRX</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>EDHL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>GEHC</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>LIND</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>LKFT</t>
+          <t>EFSI</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LMAT</t>
+          <t>GP</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>LNT</t>
+          <t>EGBN</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>LOPE</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>LQDT</t>
+          <t>EMBC</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>HSTM</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MANE</t>
+          <t>ENGS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MANH</t>
+          <t>HUIZ</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MAT</t>
+          <t>EVCM</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>MICC</t>
+          <t>IDXX</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MKTX</t>
+          <t>EVER</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MMSI</t>
+          <t>IIIV</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MNDY</t>
+          <t>EVRG</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>MNST</t>
+          <t>IRON</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MORN</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MQ</t>
+          <t>JRSH</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MRSH</t>
+          <t>EXLS</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>MXCT</t>
+          <t>JVA</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MYGN</t>
+          <t>EXPO</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>MZTI</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NATH</t>
+          <t>FDBC</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NAUT</t>
+          <t>KRT</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>NAVN</t>
+          <t>FERAU</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NCNO</t>
+          <t>KTWO</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NCPL</t>
+          <t>FMAO</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>LIVN</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>NECB</t>
+          <t>FORR</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NRDS</t>
+          <t>LMAT</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>NTRSO</t>
+          <t>FOXA</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NTSK</t>
+          <t>LQDT</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>NTWK</t>
+          <t>FRBA</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NWE</t>
+          <t>LYFT</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>NWS</t>
+          <t>FSV</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>MANE</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>OCCIM</t>
+          <t>FTDR</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>OFS</t>
+          <t>MANH</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>OMCL</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>OPRT</t>
+          <t>MICC</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ORIC</t>
+          <t>GDYN</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>OSPN</t>
+          <t>MNST</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>OSW</t>
+          <t>GMAB</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>OTAI</t>
+          <t>MQ</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>OTEX</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>OTTR</t>
+          <t>NKSH</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>OVBC</t>
+          <t>GRDX</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>PAGP</t>
+          <t>NSIT</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>PAHC</t>
+          <t>GTM</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>NWE</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>PBYI</t>
+          <t>HAS</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>PCRX</t>
+          <t>NWS</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PCTY</t>
+          <t>HBNC</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>OCCIM</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>PGNY</t>
+          <t>HCKT</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>PLGO</t>
+          <t>OFIX</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PLMR</t>
+          <t>HLP</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PLUS</t>
+          <t>OPLN</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>PMTS</t>
+          <t>HQY</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>POWW</t>
+          <t>OSW</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PRGS</t>
+          <t>HURN</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PRTH</t>
+          <t>OTAI</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>PRVA</t>
+          <t>HWKN</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>PTEN</t>
+          <t>OTTR</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>HYNE</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>QDEL</t>
+          <t>PAGP</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>QNBC</t>
+          <t>IBEX</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>RCEL</t>
+          <t>PEGA</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>ICFI</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ROKU</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ROOT</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ROP</t>
+          <t>PEPG</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>RPAY</t>
+          <t>III</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>RPC</t>
+          <t>PGNY</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>RPD</t>
+          <t>INGN</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>RPRX</t>
+          <t>PLUS</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>RUSHB</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>RYZ</t>
+          <t>PNTG</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SAIC</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>PPLC</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SCHL</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SEIC</t>
+          <t>PRDO</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SIBN</t>
+          <t>JAKK</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>SIGI</t>
+          <t>PRGS</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SLDE</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SLN</t>
+          <t>PTON</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SMXT</t>
+          <t>KDP</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>SPSC</t>
+          <t>PYPL</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SPT</t>
+          <t>KIDS</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SSNC</t>
+          <t>RGCO</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>STGW</t>
+          <t>KINS</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>STLN</t>
+          <t>ROOT</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SYNA</t>
+          <t>KMTS</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>TASK</t>
+          <t>RPC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>TCPC</t>
+          <t>LCNB</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>TCRT</t>
+          <t>RPRX</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>TEAM</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>TENB</t>
+          <t>RWAYI</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>TRI</t>
+          <t>LKFT</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>TRMB</t>
+          <t>RWAYL</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>TRXB</t>
+          <t>LNT</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SAMG</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>UTHR</t>
+          <t>LOGI</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VAI</t>
+          <t>SBUX</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>VSXY</t>
+          <t>LOPE</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>WLTH</t>
+          <t>SCHL</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>LSBK</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>XZO</t>
+          <t>SIBN</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>YSWY</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BTOC</t>
+          <t>SOMN</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>TBCH</t>
+          <t>MDLZ</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>DMRC</t>
+          <t>STGW</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PEPG</t>
+          <t>MKTX</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ICG</t>
+          <t>STLN</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MAZE</t>
+          <t>MMSI</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>CDZI</t>
+          <t>TASK</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>OPK</t>
+          <t>MNDY</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>BMBL</t>
+          <t>TBCH</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>BLMN</t>
+          <t>MORN</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LOGI</t>
+          <t>TCPC</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>NRIX</t>
+          <t>MRSH</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>JDZG</t>
+          <t>TCRT</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>INDP</t>
+          <t>MTC</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>KPLT</t>
+          <t>TENB</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ENTX</t>
+          <t>MWYN</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ONC</t>
+          <t>TRAD</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>MYGN</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>RGC</t>
+          <t>TRAX</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>MZTI</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SKYA</t>
+          <t>TRXB</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ARQT</t>
+          <t>NAVN</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>SKIN</t>
+          <t>VAI</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>RTSN</t>
+          <t>NCNO</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ASO</t>
+          <t>WLTH</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>NCPL</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>HUIZ</t>
+          <t>NDAQ</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>NECB</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>NRDS</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>NTSK</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NTWK</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>NWSA</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>OLED</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>OMCL</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>ORLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>OSPN</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>OTEX</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>OVBC</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>PAA</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>PAHC</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>PAYX</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>PBYI</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>PLBC</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>PLGO</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>PLMR</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>POWW</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>QNBC</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>RCEL</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>RCKY</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>REF</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>REGN</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>ROKU</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>ROP</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>RPAY</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>RPD</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>SAIC</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>SBC</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>SBFG</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>SDHIU</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>SEIC</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>SEZL</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>SGRY</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>SIGI</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>SKWD</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>SLDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>SMPL</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>SPSC</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>SPT</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>SSNC</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>SUNB</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>TONT</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>TRI</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>TRMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>TRS</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>UTHR</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>WTW</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>XZO</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>YSWY</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
           <t>JRVR</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>DH</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr"/>
-      <c r="D76" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>BMBL</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>AVTR</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>MXCT</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>HALO</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>INDP</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>HPK</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>ARQT</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>ORIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>BLMN</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>OPK</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>SKYA</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>MAZE</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>ENTX</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>ICG</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>PTLE</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>KPLT</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>SKIN</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>RTSN</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>FTRE</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_merged_latest.xlsx
+++ b/results/momentum_merged_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D94"/>
+  <dimension ref="A1:D80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,100 +441,100 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>AGBK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ACGL</t>
+          <t>ABLV</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CASY</t>
+          <t>BHST</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AGNT</t>
+          <t>AQB</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ACIW</t>
+          <t>AGYS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ACIC</t>
+          <t>ADAMI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CSX</t>
+          <t>BVC</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AMSF</t>
+          <t>ASR</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>AIIR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ADUS</t>
+          <t>ADMA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ENSG</t>
+          <t>COCO</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>BRBR</t>
+          <t>CELH</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>AIXI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>AFYA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FRPT</t>
+          <t>EJH</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CHNR</t>
+          <t>LFS</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>ALRM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AGYS</t>
+          <t>AHG</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -544,41 +544,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>DPZ</t>
+          <t>NXPI</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>AMPL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ANIK</t>
+          <t>AMRO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GPGI</t>
+          <t>GRFS</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FLX</t>
+          <t>OSG</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ALRM</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>APEI</t>
+          <t>ANIK</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -588,107 +588,107 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>JDZG</t>
+          <t>PLBY</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AMCR</t>
+          <t>APPN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>APOG</t>
+          <t>ATLCZ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>IPAR</t>
+          <t>KWY</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>KLTR</t>
+          <t>PODD</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ARLP</t>
+          <t>AVPT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>KWY</t>
+          <t>MIDD</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LIF</t>
+          <t>PTEN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AMPL</t>
+          <t>ARHS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ASBP</t>
+          <t>AVTR</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ODFL</t>
+          <t>PECO</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MGPI</t>
+          <t>RGC</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ANDG</t>
+          <t>ARLP</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ATLCZ</t>
+          <t>BETR</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PECO</t>
+          <t>PEPG</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NXGL</t>
+          <t>SOLS</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ANGI</t>
+          <t>ARX</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ATOS</t>
+          <t>BMBL</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -698,134 +698,134 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>PODD</t>
+          <t>TCMD</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>APPN</t>
+          <t>AVBC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AUPH</t>
+          <t>BRZE</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PTEN</t>
+          <t>SBAC</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>REYN</t>
+          <t>BCPC</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BVFL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>BDCI</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TILE</t>
+          <t>BWIN</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SHOE</t>
+          <t>BL</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ARHS</t>
+          <t>BZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BOW</t>
+          <t>BOLT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>STFS</t>
+          <t>CASY</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ASBH</t>
+          <t>BOTJ</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BREZ</t>
+          <t>CBC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TCMD</t>
+          <t>BPRN</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ASO</t>
+          <t>CBRL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>BRZE</t>
+          <t>BRBI</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TRIB</t>
+          <t>CDZI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ATLCL</t>
+          <t>BRCB</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>CENT</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>BSET</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>TRIP</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ATLO</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BSP</t>
+          <t>BSY</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AVBC</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -837,931 +837,931 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AVPT</t>
+          <t>CHAD</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BVFL</t>
+          <t>CART</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BANF</t>
+          <t>COFS</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>BWIN</t>
+          <t>CBFV</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BCAL</t>
+          <t>CPIX</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BYRN</t>
+          <t>CBNK</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BCML</t>
+          <t>CWST</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>BZUN</t>
+          <t>CCNE</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BCPC</t>
+          <t>DCBO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CART</t>
+          <t>CCSI</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BFST</t>
+          <t>DIBS</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CBC</t>
+          <t>CD</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>DMAC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CBNK</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BL</t>
+          <t>DOCU</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CBRL</t>
+          <t>CENTA</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BLKB</t>
+          <t>DRDB</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CDZI</t>
+          <t>CGNT</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BPRN</t>
+          <t>DSP</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CENT</t>
+          <t>CHKP</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>EBAY</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CFFI</t>
+          <t>CHRD</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BRCB</t>
+          <t>ENGS</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>COKE</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BSVN</t>
+          <t>ENTX</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>CTAS</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BSY</t>
+          <t>EXE</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>COKE</t>
+          <t>CVLT</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BVS</t>
+          <t>EXPO</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>COLM</t>
+          <t>CVSA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CBFV</t>
+          <t>FANG</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>CPIX</t>
+          <t>CZFS</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CCEP</t>
+          <t>FNLC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>CZNC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CCNE</t>
+          <t>FRSH</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>CVSA</t>
+          <t>DAKT</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CCNEP</t>
+          <t>FUNC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>DBX</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>GAING</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>DCOM</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CENTA</t>
+          <t>GAINI</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DGICA</t>
+          <t>DHCNL</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CHCO</t>
+          <t>GAINZ</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>DHCNL</t>
+          <t>EDHL</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CHKP</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DIBS</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CINF</t>
+          <t>GEHC</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>DOX</t>
+          <t>EFSI</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CLAR</t>
+          <t>GTLB</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DRDB</t>
+          <t>EGBN</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CNXC</t>
+          <t>GTM</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>EPSN</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>HALO</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DSP</t>
+          <t>ERIC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CRAC</t>
+          <t>HAS</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>EPSN</t>
+          <t>ETS</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CRAI</t>
+          <t>HEPS</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ERIE</t>
+          <t>FCNCA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CSGP</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ETSY</t>
+          <t>FDBC</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>HOWL</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>EXE</t>
+          <t>FLYW</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>HPK</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>FMAO</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CVLT</t>
+          <t>HUIZ</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>EYE</t>
+          <t>FORR</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CWST</t>
+          <t>ICG</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>FRBA</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DAKT</t>
+          <t>INGN</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FIZZ</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>DAVE</t>
+          <t>IOSP</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>FLYW</t>
+          <t>GDYN</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DBX</t>
+          <t>IOVA</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FNKO</t>
+          <t>GLBE</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>DLTR</t>
+          <t>IPXG</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>FNLC</t>
+          <t>GMAB</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DMAA</t>
+          <t>IRON</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FOX</t>
+          <t>GRDX</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>DOCU</t>
+          <t>JCSE</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>FRSH</t>
+          <t>HBNC</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DSGR</t>
+          <t>JOYY</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FVN</t>
+          <t>HCSG</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>DUKU</t>
+          <t>JYD</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>GABC</t>
+          <t>HLP</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ECCU</t>
+          <t>KMTS</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GDRX</t>
+          <t>HQY</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>EDHL</t>
+          <t>LIFE</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>GEHC</t>
+          <t>HSTM</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>LQDT</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>HTFL</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>EFSI</t>
+          <t>MANE</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>GP</t>
+          <t>HURN</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>EGBN</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>HYNE</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>EMBC</t>
+          <t>MAZE</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>HSTM</t>
+          <t>IBEX</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>MBRX</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>HUIZ</t>
+          <t>ICFI</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>EVCM</t>
+          <t>MEDP</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>IDXX</t>
+          <t>III</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>EVER</t>
+          <t>MMTX</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>IIIV</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>EVRG</t>
+          <t>MTCH</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>IRON</t>
+          <t>INTR</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>JRSH</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>EXLS</t>
+          <t>MYGN</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>JVA</t>
+          <t>JAKK</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>NAVN</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FDBC</t>
+          <t>NPAC</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>KGEI</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FERAU</t>
+          <t>NRIX</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>KTWO</t>
+          <t>LCNB</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>FMAO</t>
+          <t>NWFL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LIVN</t>
+          <t>LGND</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>FORR</t>
+          <t>ONBPP</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>LMAT</t>
+          <t>LKFT</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>FOXA</t>
+          <t>ONC</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LQDT</t>
+          <t>MGYR</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>FRBA</t>
+          <t>OTAI</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>LYFT</t>
+          <t>MKTX</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FSV</t>
+          <t>OTLY</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>MANE</t>
+          <t>MORN</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FTDR</t>
+          <t>OXLCZ</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MANH</t>
+          <t>MWYN</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>PAX</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>MICC</t>
+          <t>NATH</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>GDYN</t>
+          <t>PCRX</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MNST</t>
+          <t>NAUT</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>PICS</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>MQ</t>
+          <t>NBTB</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>PMTS</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NKSH</t>
+          <t>NICE</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GRDX</t>
+          <t>PRCH</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NSIT</t>
+          <t>NIQ</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>GTM</t>
+          <t>PRGS</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NWE</t>
+          <t>NSIT</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NWS</t>
+          <t>NSSC</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>HBNC</t>
+          <t>PTLE</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>OCCIM</t>
+          <t>NTRSO</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>HCKT</t>
+          <t>RCEL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>OFIX</t>
+          <t>NTSK</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>REBN</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>OPLN</t>
+          <t>NTWK</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>HQY</t>
+          <t>RELY</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>OSW</t>
+          <t>NWE</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>HURN</t>
+          <t>REVB</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>OTAI</t>
+          <t>OABI</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>HWKN</t>
+          <t>RIGL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>OTTR</t>
+          <t>OCTV</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>HYNE</t>
+          <t>RVSB</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PAGP</t>
+          <t>OMCL</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>IBEX</t>
+          <t>RWAYI</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>PEGA</t>
+          <t>ORIC</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ICFI</t>
+          <t>SAFT</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>OSPN</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>SAIC</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>PEPG</t>
+          <t>OTEX</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PGNY</t>
+          <t>OVBC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>INGN</t>
+          <t>SKYA</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>PLUS</t>
+          <t>PAA</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>SPSC</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PNTG</t>
+          <t>PAGP</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>TBCH</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>PPLC</t>
+          <t>POWW</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>TEAM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1771,714 +1771,410 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>JAKK</t>
+          <t>TRAX</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>PRGS</t>
+          <t>PRME</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PTON</t>
+          <t>PSIG</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>KDP</t>
+          <t>UTHR</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>QLYS</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>KIDS</t>
+          <t>VSXY</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>RGCO</t>
+          <t>QNBC</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>KINS</t>
+          <t>YSWY</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ROOT</t>
+          <t>REAL</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>KMTS</t>
+          <t>REF</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>RPC</t>
+          <t>ROP</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>LCNB</t>
+          <t>RPAY</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>RPRX</t>
+          <t>RPD</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>RPRX</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>RWAYI</t>
+          <t>SBFG</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>LKFT</t>
+          <t>SIGI</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>RWAYL</t>
+          <t>SLDE</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>LNT</t>
+          <t>SWKHL</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SAMG</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>LOGI</t>
+          <t>TENB</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>TLS</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>LOPE</t>
+          <t>JDZG</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SCHL</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>LSBK</t>
+          <t>FTRE</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>SIBN</t>
+          <t>CAPS</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SOMN</t>
+          <t>TRI</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MDLZ</t>
+          <t>STFS</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>STGW</t>
+          <t>DGICB</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MKTX</t>
+          <t>KPLT</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>STLN</t>
+          <t>FTDR</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MMSI</t>
+          <t>AEYE</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>TASK</t>
+          <t>KINS</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MNDY</t>
+          <t>OPRX</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>TBCH</t>
+          <t>FISV</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MORN</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>TCPC</t>
+          <t>OMH</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MRSH</t>
+          <t>MNDY</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>TCRT</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MTC</t>
+          <t>CNXC</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>TENB</t>
+          <t>ALGN</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MWYN</t>
+          <t>SVIAW</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>TRAD</t>
+          <t>MANH</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MYGN</t>
+          <t>EVAX</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>TRAX</t>
+          <t>PGNY</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>MZTI</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>TRXB</t>
+          <t>SLN</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>NAVN</t>
+          <t>MTEX</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VAI</t>
+          <t>BMGL</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>NCNO</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>WLTH</t>
+          <t>MMSI</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>NCPL</t>
+          <t>RPC</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>OLED</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>NECB</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>NRDS</t>
+          <t>AGIO</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>NTSK</t>
+          <t>JRVR</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NTWK</t>
+          <t>CSGP</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>NRDS</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>OMCL</t>
+          <t>MRSH</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ORLY</t>
+          <t>SLE</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>OSPN</t>
+          <t>INDP</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>OTEX</t>
+          <t>ERIE</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>OVBC</t>
+          <t>BLKB</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>PAA</t>
+          <t>AMCR</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>PAHC</t>
+          <t>EXYN</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>GP</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>PBYI</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>OPK</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>EXLS</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
           <t>PCTY</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>PLBC</t>
-        </is>
-      </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>PLGO</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>PLMR</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>POWW</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>QNBC</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>RCEL</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>RCKY</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>REF</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>REGN</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>ROKU</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>ROP</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>RPAY</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>RPD</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>SAIC</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>SBC</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>SBFG</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>SDHIU</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>SEIC</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>SEZL</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>SGRY</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>SIGI</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>SKWD</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>SLDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>SMPL</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>SPSC</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
           <t>SPT</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>SSNC</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>SUNB</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>TONT</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>TRI</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>TRMB</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>TRS</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>TW</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>UTHR</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>WTW</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>XZO</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>YSWY</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>ETS</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>JRVR</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>BMBL</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>AVTR</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>MXCT</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>HALO</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>INDP</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>HPK</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>ARQT</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>ORIC</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>BLMN</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>OPK</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>SKYA</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>MAZE</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>ENTX</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>ICG</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>PTLE</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>KPLT</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>SKIN</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>RTSN</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>FTRE</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_merged_latest.xlsx
+++ b/results/momentum_merged_latest.xlsx
@@ -830,7 +830,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>BUUU</t>
+          <t>CART</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CART</t>
+          <t>CBFV</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CBFV</t>
+          <t>CBNK</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CBNK</t>
+          <t>CCNE</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CCNE</t>
+          <t>CCSI</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CCSI</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CD</t>
+          <t>CDW</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>CENTA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CENTA</t>
+          <t>CGNT</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CGNT</t>
+          <t>CHKP</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CHKP</t>
+          <t>CHRD</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CHRD</t>
+          <t>COKE</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>COKE</t>
+          <t>CTAS</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>CVLT</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>CVLT</t>
+          <t>CVSA</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CVSA</t>
+          <t>CZFS</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>CZFS</t>
+          <t>CZNC</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CZNC</t>
+          <t>DAKT</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>DAKT</t>
+          <t>DBX</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DBX</t>
+          <t>DCOM</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>DCOM</t>
+          <t>DHCNL</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DHCNL</t>
+          <t>EDHL</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>EDHL</t>
+          <t>EFOR</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>EFSI</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>EFSI</t>
+          <t>EGBN</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>EGBN</t>
+          <t>EPSN</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>EPSN</t>
+          <t>ERIC</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ERIC</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>FCNCA</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FCNCA</t>
+          <t>FDBC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>FDBC</t>
+          <t>FLYW</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FLYW</t>
+          <t>FMAO</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>FMAO</t>
+          <t>FORR</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FORR</t>
+          <t>FRBA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>FRBA</t>
+          <t>GCL</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>GDYN</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>GDYN</t>
+          <t>GLBE</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GLBE</t>
+          <t>GMAB</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>GRDX</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GRDX</t>
+          <t>HBNC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>HBNC</t>
+          <t>HCSG</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>HCSG</t>
+          <t>HLP</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>HQY</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>HQY</t>
+          <t>HSTM</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>HSTM</t>
+          <t>HTFL</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>HTFL</t>
+          <t>HURN</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>HURN</t>
+          <t>HYNE</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>HYNE</t>
+          <t>IBEX</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>IBEX</t>
+          <t>ICFI</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ICFI</t>
+          <t>III</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>INTA</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>INTR</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>INTR</t>
+          <t>ISRG</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>JAKK</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>JAKK</t>
+          <t>JKHY</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>KGEI</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>KGEI</t>
+          <t>LCNB</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>LCNB</t>
+          <t>LGND</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LGND</t>
+          <t>LKFT</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>LKFT</t>
+          <t>MGYR</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>MGYR</t>
+          <t>MKTX</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>MKTX</t>
+          <t>MORN</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>MORN</t>
+          <t>MWYN</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MWYN</t>
+          <t>NATH</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NATH</t>
+          <t>NAUT</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NAUT</t>
+          <t>NBTB</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NBTB</t>
+          <t>NICE</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NICE</t>
+          <t>NIQ</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NIQ</t>
+          <t>NSIT</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NSIT</t>
+          <t>NSSC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NSSC</t>
+          <t>NTRSO</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NTRSO</t>
+          <t>NTSK</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NTSK</t>
+          <t>NTWK</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NTWK</t>
+          <t>NWE</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NWE</t>
+          <t>OABI</t>
         </is>
       </c>
     </row>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>OABI</t>
+          <t>OCTV</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>OCTV</t>
+          <t>OMCL</t>
         </is>
       </c>
     </row>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>OMCL</t>
+          <t>ORIC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ORIC</t>
+          <t>OSPN</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>OSPN</t>
+          <t>OTEX</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>OTEX</t>
+          <t>OVBC</t>
         </is>
       </c>
     </row>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>OVBC</t>
+          <t>PAA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>PAA</t>
+          <t>PAGP</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PAGP</t>
+          <t>POWW</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>POWW</t>
+          <t>PRDO</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PRDO</t>
+          <t>PRME</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>PRME</t>
+          <t>PSIG</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PSIG</t>
+          <t>QLYS</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>QLYS</t>
+          <t>QNBC</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>QNBC</t>
+          <t>REAL</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1820,361 +1820,357 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>REAL</t>
+          <t>REF</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>REF</t>
+          <t>ROP</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ROP</t>
+          <t>RPAY</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>RPAY</t>
+          <t>RPD</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>RPD</t>
+          <t>RPRX</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>RPRX</t>
+          <t>SBFG</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SBFG</t>
+          <t>SIGI</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>SIGI</t>
+          <t>SLDE</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>SLDE</t>
+          <t>SWKHL</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SWKHL</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>TENB</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>TENB</t>
+          <t>TLS</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>TLS</t>
+          <t>BLKB</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>JDZG</t>
+          <t>CAPS</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>AMCR</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
+          <t>NRDS</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
           <t>FTRE</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>CAPS</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>MNDY</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>TRI</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>STFS</t>
+          <t>FTDR</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>DGICB</t>
+          <t>OPK</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>KPLT</t>
+          <t>JRVR</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>FTDR</t>
+          <t>RPC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AEYE</t>
+          <t>PGNY</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>KINS</t>
+          <t>ALGN</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>OPRX</t>
+          <t>MMSI</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>FISV</t>
+          <t>MTEX</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>TRI</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>OMH</t>
+          <t>DGICB</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MNDY</t>
+          <t>AEYE</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CNXC</t>
+          <t>PCTY</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ALGN</t>
+          <t>SPT</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SVIAW</t>
+          <t>MANH</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>MANH</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>EVAX</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>PGNY</t>
+          <t>OMH</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>EXLS</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SLN</t>
+          <t>BMGL</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MTEX</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>BMGL</t>
+          <t>ERIE</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>OPRX</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>MMSI</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>RPC</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>SLE</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>JRVR</t>
+          <t>INDP</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>CSGP</t>
+          <t>OLED</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>NRDS</t>
+          <t>SVIAW</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>STFS</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>MRSH</t>
+          <t>JDZG</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>SLE</t>
+          <t>GP</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>INDP</t>
+          <t>AGIO</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ERIE</t>
+          <t>KPLT</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>BLKB</t>
+          <t>EXYN</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>AMCR</t>
+          <t>FISV</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>EXYN</t>
+          <t>SLN</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>GP</t>
+          <t>CNXC</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>CSGP</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>OPK</t>
+          <t>INTU</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>EXLS</t>
+          <t>MRSH</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>PCTY</t>
+          <t>EVAX</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>INTU</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>SPT</t>
-        </is>
-      </c>
+          <t>KINS</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_merged_latest.xlsx
+++ b/results/momentum_merged_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D80"/>
+  <dimension ref="A1:D103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AGBK</t>
+          <t>BRLT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -451,1726 +451,2224 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BHST</t>
+          <t>RENT</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AQB</t>
+          <t>ALKS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AGYS</t>
+          <t>FNWD</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ADAMI</t>
+          <t>ACNB</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BVC</t>
+          <t>AQB</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ASR</t>
+          <t>FORTY</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AIIR</t>
+          <t>ADAMI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>ARXS</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SGRY</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>ADMA</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>COCO</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>CELH</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AIXI</t>
+          <t>BDTX</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AFYA</t>
+          <t>XNCR</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>EJH</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LFS</t>
+          <t>BHST</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ALRM</t>
+          <t>ADUS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AHG</t>
+          <t>BVC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GIII</t>
+          <t>AEP</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NXPI</t>
+          <t>CLBT</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AMPL</t>
+          <t>AER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AMRO</t>
+          <t>CTSO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GRFS</t>
+          <t>AGIO</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>OSG</t>
+          <t>DORM</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>AGYS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ANIK</t>
+          <t>FELE</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>HONA</t>
+          <t>AISP</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PLBY</t>
+          <t>FLX</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>APPN</t>
+          <t>ALGN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ATLCZ</t>
+          <t>GRFS</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>KWY</t>
+          <t>ALLT</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>PODD</t>
+          <t>HLMN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>ALRM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AVPT</t>
+          <t>HONA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MIDD</t>
+          <t>AMAL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>PTEN</t>
+          <t>HTZ</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ARHS</t>
+          <t>AMCR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AVTR</t>
+          <t>KLRA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>PECO</t>
+          <t>AMRO</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>RGC</t>
+          <t>KXIN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ARLP</t>
+          <t>AMRX</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BETR</t>
+          <t>LIF</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PEPG</t>
+          <t>AMSF</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SOLS</t>
+          <t>NXPI</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ARX</t>
+          <t>ANDG</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BMBL</t>
+          <t>NYAX</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>API</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>TCMD</t>
+          <t>OMH</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AVBC</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BRZE</t>
+          <t>OSG</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SBAC</t>
+          <t>ARLP</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>BCPC</t>
+          <t>OSW</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BVFL</t>
+          <t>ARX</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BDCI</t>
+          <t>PECO</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BWIN</t>
+          <t>ASND</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>BL</t>
+          <t>PMA</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>ASST</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BOLT</t>
+          <t>PSMT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CASY</t>
+          <t>ATGL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>BOTJ</t>
+          <t>PTEN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CBC</t>
+          <t>ATRC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BPRN</t>
+          <t>PWRL</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CBRL</t>
+          <t>AUDC</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>BRBI</t>
+          <t>SBAC</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CDZI</t>
+          <t>AVBC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BRCB</t>
+          <t>SNWV</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CENT</t>
+          <t>AVPT</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>BSET</t>
+          <t>SOLS</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>BBSI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BSY</t>
+          <t>STAA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>BCAL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CART</t>
+          <t>TNGX</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CHAD</t>
+          <t>BCPC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CBFV</t>
+          <t>TREE</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>COFS</t>
+          <t>BOLT</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CBNK</t>
+          <t>BOTJ</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CPIX</t>
+          <t>BOW</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CCNE</t>
+          <t>BPRN</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CWST</t>
+          <t>BSET</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CCSI</t>
+          <t>BSIN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>BSRR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CD</t>
+          <t>BSY</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>DIBS</t>
+          <t>BUSE</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>BVS</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DMAC</t>
+          <t>BWFG</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CENTA</t>
+          <t>BWMN</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>DOCU</t>
+          <t>BZ</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CGNT</t>
+          <t>BZUN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DRDB</t>
+          <t>CAC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CHKP</t>
+          <t>CAI</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DSP</t>
+          <t>CAPS</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CHRD</t>
+          <t>CATY</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>CBC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>COKE</t>
+          <t>CBNK</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>CBU</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>CCBG</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ENTX</t>
+          <t>CCNE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CVLT</t>
+          <t>CCSI</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>EXE</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>CVSA</t>
+          <t>CDNA</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>CENT</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CZFS</t>
+          <t>CENTA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FANG</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>CZNC</t>
+          <t>CFFI</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FNLC</t>
+          <t>CGNT</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DAKT</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FRSH</t>
+          <t>CHAD</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>DBX</t>
+          <t>CHCO</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FUNC</t>
+          <t>CHKP</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DCOM</t>
+          <t>CIVB</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GAING</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>DHCNL</t>
+          <t>CNOB</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GAINI</t>
+          <t>CNXC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EDHL</t>
+          <t>COFS</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>GAINZ</t>
+          <t>CRAI</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>CRON</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>CRSR</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>EFSI</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>GEHC</t>
+          <t>CTAS</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>EGBN</t>
+          <t>CTSH</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>GTLB</t>
+          <t>CV</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>EPSN</t>
+          <t>CVLT</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GTM</t>
+          <t>CZFS</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ERIC</t>
+          <t>CZNC</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>HALO</t>
+          <t>DAKT</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>DCBO</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>DCOM</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>FCNCA</t>
+          <t>DIBS</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>HEPS</t>
+          <t>DLTR</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FDBC</t>
+          <t>DMAC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>HON</t>
+          <t>DMLP</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>FLYW</t>
+          <t>DMRC</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>HOWL</t>
+          <t>DSGX</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FMAO</t>
+          <t>EBAY</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>HPK</t>
+          <t>EBC</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>FORR</t>
+          <t>EFSI</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>HUIZ</t>
+          <t>ELMT</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FRBA</t>
+          <t>ENGS</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ICG</t>
+          <t>ENSG</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>ENTX</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>INGN</t>
+          <t>ERIC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GDYN</t>
+          <t>ESLA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>IOSP</t>
+          <t>ESLT</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>GLBE</t>
+          <t>ESQ</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>IOVA</t>
+          <t>EVCM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>EVRG</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>IPXG</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>GRDX</t>
+          <t>EXLS</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>IRON</t>
+          <t>EXPO</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HBNC</t>
+          <t>EXYN</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>JCSE</t>
+          <t>FBIZ</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>HCSG</t>
+          <t>FCBC</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>JOYY</t>
+          <t>FCNCA</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>FDBC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>JYD</t>
+          <t>FFBC</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>HQY</t>
+          <t>FISI</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>KMTS</t>
+          <t>FITB</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>HSTM</t>
+          <t>FIVN</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>LIFE</t>
+          <t>FMAO</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>HTFL</t>
+          <t>FMBH</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>LQDT</t>
+          <t>FMNB</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>HURN</t>
+          <t>FNKO</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MANE</t>
+          <t>FNLC</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>HYNE</t>
+          <t>FRAF</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>FRBA</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>IBEX</t>
+          <t>FSSL</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MAZE</t>
+          <t>FTRE</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ICFI</t>
+          <t>FUNC</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MBRX</t>
+          <t>GABC</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>GAING</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MEDP</t>
+          <t>GAINI</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>GAINZ</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MMTX</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>INTR</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MTCH</t>
+          <t>GDYN</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>GEHC</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>GIBO</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>JAKK</t>
+          <t>GIII</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MYGN</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>GLBE</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>NAVN</t>
+          <t>GMAB</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>KGEI</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NPAC</t>
+          <t>GP</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LCNB</t>
+          <t>GTLB</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>NRIX</t>
+          <t>HAFC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>LGND</t>
+          <t>HALO</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NWFL</t>
+          <t>HAS</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LKFT</t>
+          <t>HBNC</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ONBPP</t>
+          <t>HCKT</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>MGYR</t>
+          <t>HIFS</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ONC</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>MKTX</t>
+          <t>HPK</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>OTAI</t>
+          <t>HSTM</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>MORN</t>
+          <t>HTFL</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>OTLY</t>
+          <t>HTHT</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>MWYN</t>
+          <t>HURN</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>OXLCZ</t>
+          <t>HWKN</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NATH</t>
+          <t>HYNE</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>PAX</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NAUT</t>
+          <t>IBCP</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PCRX</t>
+          <t>IBEX</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NBTB</t>
+          <t>ICFI</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>PICS</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NICE</t>
+          <t>IDXX</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PMTS</t>
+          <t>III</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NIQ</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>PRCH</t>
+          <t>INDB</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NSIT</t>
+          <t>INDP</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>PRGS</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NSSC</t>
+          <t>IOSP</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>IRLA</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NTRSO</t>
+          <t>IRON</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PTLE</t>
+          <t>IRTC</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NTSK</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>RCEL</t>
+          <t>JAKK</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NTWK</t>
+          <t>JCAP</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>REBN</t>
+          <t>JCSE</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NWE</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>RELY</t>
+          <t>JMSB</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>OABI</t>
+          <t>JOYY</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>REVB</t>
+          <t>JYD</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>OCTV</t>
+          <t>KIDS</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>RIGL</t>
+          <t>KMTS</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>OMCL</t>
+          <t>KPLT</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>RVSB</t>
+          <t>LCNB</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ORIC</t>
+          <t>LFCR</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>RWAYI</t>
+          <t>LFST</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>OSPN</t>
+          <t>LIFE</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SAFT</t>
+          <t>LIND</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>OTEX</t>
+          <t>LKFT</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SAIC</t>
+          <t>LMRI</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>OVBC</t>
+          <t>LNT</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>LQDT</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PAA</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SKYA</t>
+          <t>MANE</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>PAGP</t>
+          <t>MBRX</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SPSC</t>
+          <t>MCBS</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>POWW</t>
+          <t>MEDP</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>TBCH</t>
+          <t>MEOH</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>PRDO</t>
+          <t>MGRC</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TEAM</t>
+          <t>MITK</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PRME</t>
+          <t>MKTX</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>TRAX</t>
+          <t>MMSI</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>PSIG</t>
+          <t>MQ</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>MTC</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>QLYS</t>
+          <t>MTEX</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>UTHR</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>QNBC</t>
+          <t>MXCT</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>VSXY</t>
+          <t>MYGN</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>REAL</t>
+          <t>NBTB</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>YSWY</t>
+          <t>NCNO</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>REF</t>
+          <t>NDAQ</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ROP</t>
+          <t>NICE</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>RPAY</t>
+          <t>NSIT</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>RPD</t>
+          <t>NSSC</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>RPRX</t>
+          <t>NTRA</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SBFG</t>
+          <t>NTRSO</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SIGI</t>
+          <t>NTSK</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>SLDE</t>
+          <t>NWBI</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>SWKHL</t>
+          <t>NWE</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>NWFL</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TENB</t>
+          <t>OCTV</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>TLS</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>BLKB</t>
+          <t>ONC</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CAPS</t>
+          <t>OPRT</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>AMCR</t>
+          <t>OPRX</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>NRDS</t>
+          <t>ORRF</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>FTRE</t>
+          <t>OSPN</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MNDY</t>
+          <t>OYSE</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>PAA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>FTDR</t>
+          <t>PAGP</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>OPK</t>
+          <t>PBFS</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>JRVR</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>RPC</t>
+          <t>PCRX</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>PGNY</t>
+          <t>PEGA</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ALGN</t>
+          <t>PFBC</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MMSI</t>
+          <t>PLBC</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MTEX</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>TRI</t>
+          <t>PLUS</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>DGICB</t>
+          <t>PMTS</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AEYE</t>
+          <t>PNFP</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>PNTG</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>PCTY</t>
+          <t>POM</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>SPT</t>
+          <t>POWW</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MANH</t>
+          <t>PRCH</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>PRGS</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>OMH</t>
+          <t>QCRH</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>EXLS</t>
+          <t>QDEL</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>BMGL</t>
+          <t>QLYS</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>QNBC</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ERIE</t>
+          <t>RCBC</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>OPRX</t>
+          <t>REF</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>RELY</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>RGS</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>SLE</t>
+          <t>RIGL</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>ROKU</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>ROP</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>INDP</t>
+          <t>RPD</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>RPRX</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SVIAW</t>
+          <t>RUSHB</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>STFS</t>
+          <t>RVSB</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>JDZG</t>
+          <t>RYZ</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>GP</t>
+          <t>SAIC</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>SBCF</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>KPLT</t>
+          <t>SBFG</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>EXYN</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>FISV</t>
+          <t>SCSC</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SLN</t>
+          <t>SEPN</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CNXC</t>
+          <t>SEZL</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>CSGP</t>
+          <t>SFNC</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>SGP</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MRSH</t>
+          <t>SIBN</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EVAX</t>
+          <t>SIGI</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
+          <t>SKYA</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>SLDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>SLN</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>SONO</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>SPT</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>SRCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>SSNC</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>STBA</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>STLD</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>STLN</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>SUNB</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>SWKHL</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>SYNA</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>SYRE</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>TACT</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>TCMD</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>TENB</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>TILE</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>TLS</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>TRI</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>TRMB</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>TRS</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>VSXY</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>WAFU</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>WLTH</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>WSBCO</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>YMAT</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>YSWY</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>OZK</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>ACIW</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>OPK</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>XLAB</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>INTA</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>ARHS</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>EFOR</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>AVTR</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>EMBC</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>TBCH</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ASBH</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>BMGL</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>DOX</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>FTDR</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>MORN</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>APPN</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>ASRV</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>BIIB</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>MANH</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>HON</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>STFS</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>TRAX</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>EPSN</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>AGNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>FRSH</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>PBYI</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>POOL</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>HQY</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>NTWK</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>AMPL</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>CWST</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>GRDX</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>MNDY</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>NIQ</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>DOCU</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>CDLR</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>BL</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>AVAH</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>REVB</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>BRZE</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>CDZI</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>DBX</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>SGHT</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>BETR</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>RPC</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>INGN</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>SLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
           <t>KINS</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>DGICB</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>BLKB</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>COO</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>BRCB</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>OTEX</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>JJSF</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>CINF</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>ICG</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>UTHR</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>HCSG</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>CVBF</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>CDW</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_merged_latest.xlsx
+++ b/results/momentum_merged_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D103"/>
+  <dimension ref="A1:D83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,2234 +441,1794 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BRLT</t>
+          <t>AEYE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ABLV</t>
+          <t>ACT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>RENT</t>
+          <t>ALGN</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ALKS</t>
+          <t>BOW</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FNWD</t>
+          <t>ACU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ACNB</t>
+          <t>AMSF</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AQB</t>
+          <t>JCSE</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FORTY</t>
+          <t>ADP</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ADAMI</t>
+          <t>BGSI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ARXS</t>
+          <t>KELYB</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SGRY</t>
+          <t>AEP</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ADMA</t>
+          <t>BMGL</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BDTX</t>
+          <t>POM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>XNCR</t>
+          <t>AER</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>CARR</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>BHST</t>
+          <t>AGIO</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ADUS</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BVC</t>
+          <t>ALLT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>CCB</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CLBT</t>
+          <t>AMAL</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AER</t>
+          <t>CTSO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CTSO</t>
+          <t>AMPL</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>DHCNI</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>DORM</t>
+          <t>AMRO</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AGYS</t>
+          <t>EJH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FELE</t>
+          <t>AMRX</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AISP</t>
+          <t>ELUT</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FLX</t>
+          <t>ANIK</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ALGN</t>
+          <t>FLX</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GRFS</t>
+          <t>APPN</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ALLT</t>
+          <t>IMCR</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>HLMN</t>
+          <t>ARHS</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ALRM</t>
+          <t>JDZG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HONA</t>
+          <t>ARLP</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AMAL</t>
+          <t>KLRA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HTZ</t>
+          <t>ARQT</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AMCR</t>
+          <t>LIF</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>KLRA</t>
+          <t>ARXS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AMRO</t>
+          <t>NXPI</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>KXIN</t>
+          <t>ASTL</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AMRX</t>
+          <t>NYAX</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LIF</t>
+          <t>ATLCL</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AMSF</t>
+          <t>OIO</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NXPI</t>
+          <t>AUDC</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ANDG</t>
+          <t>OKYO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NYAX</t>
+          <t>AUPH</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>OSW</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>OMH</t>
+          <t>AVAH</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>PWRL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>OSG</t>
+          <t>AVBH</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ARLP</t>
+          <t>RSVR</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>OSW</t>
+          <t>BANR</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ARX</t>
+          <t>SOLS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PECO</t>
+          <t>BCAL</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ASND</t>
+          <t>STAA</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>PMA</t>
+          <t>BETR</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ASST</t>
+          <t>TCBK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PSMT</t>
+          <t>BL</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ATGL</t>
+          <t>TREE</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>PTEN</t>
+          <t>BLKB</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ATRC</t>
+          <t>VMRK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PWRL</t>
+          <t>BOTJ</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AUDC</t>
+          <t>BPRN</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SBAC</t>
+          <t>BRCB</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AVBC</t>
+          <t>BRZE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SNWV</t>
+          <t>BSET</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AVPT</t>
+          <t>BSIN</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SOLS</t>
+          <t>BSRR</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BBSI</t>
+          <t>BSVN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>STAA</t>
+          <t>BUSE</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BCAL</t>
+          <t>BVC</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>TNGX</t>
+          <t>BVS</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BCPC</t>
+          <t>BWFG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TREE</t>
+          <t>BWMN</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BOLT</t>
+          <t>CASS</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>BOTJ</t>
+          <t>CATY</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BOW</t>
+          <t>CCID</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BPRN</t>
+          <t>CCSI</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BSET</t>
+          <t>CDNA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>BSIN</t>
+          <t>CDW</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BSRR</t>
+          <t>CFFI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BSY</t>
+          <t>CGNT</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BUSE</t>
+          <t>CHDN</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>BVS</t>
+          <t>CINF</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BWFG</t>
+          <t>CNXC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BWMN</t>
+          <t>CRSR</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>CSX</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>BZUN</t>
+          <t>CTKB</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CAC</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CAI</t>
+          <t>CVBF</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CAPS</t>
+          <t>CVLT</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CATY</t>
+          <t>CYRX</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CBC</t>
+          <t>CZFS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CBNK</t>
+          <t>DAKT</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CBU</t>
+          <t>DBX</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CCBG</t>
+          <t>DCBO</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CCNE</t>
+          <t>DLTR</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CCSI</t>
+          <t>DMRC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CD</t>
+          <t>DOCU</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>DOX</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CENT</t>
+          <t>DSP</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CENTA</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>ERIC</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>CFFI</t>
+          <t>ESQ</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CGNT</t>
+          <t>EWBC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>EXE</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CHAD</t>
+          <t>EXLS</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>CHCO</t>
+          <t>EXYN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CHKP</t>
+          <t>FBIZ</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CIVB</t>
+          <t>FCBM</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>FCNCA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CNOB</t>
+          <t>FFBC</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CNXC</t>
+          <t>FITB</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>COFS</t>
+          <t>FMAO</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CRAI</t>
+          <t>FMBH</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CRON</t>
+          <t>FNKO</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CRSR</t>
+          <t>FRME</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>FSSL</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>FTDR</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>FTRE</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CV</t>
+          <t>FUNC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CVLT</t>
+          <t>FVNNU</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CZFS</t>
+          <t>GAINI</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CZNC</t>
+          <t>GCBC</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DAKT</t>
+          <t>GDRX</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>GDYN</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>DCOM</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>DIBS</t>
+          <t>GRDX</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DLTR</t>
+          <t>GRFS</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DMAC</t>
+          <t>GSBC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>DMLP</t>
+          <t>GTM</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>DMRC</t>
+          <t>HAFC</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>HBT</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>HCKT</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>EBC</t>
+          <t>HCSG</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>EFSI</t>
+          <t>HLP</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ELMT</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ENSG</t>
+          <t>HQY</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ENTX</t>
+          <t>HTFL</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ERIC</t>
+          <t>HWBK</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ESLA</t>
+          <t>HWKN</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ESLT</t>
+          <t>IBEX</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ESQ</t>
+          <t>ICLR</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>EVCM</t>
+          <t>III</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>EVRG</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>IMC</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>EXLS</t>
+          <t>IMKTA</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>INDB</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>EXYN</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FBIZ</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>FCBC</t>
+          <t>IOSP</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>FCNCA</t>
+          <t>IOVA</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FDBC</t>
+          <t>IRON</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FFBC</t>
+          <t>JBDI</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>FISI</t>
+          <t>JOUT</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FITB</t>
+          <t>JYD</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>FIVN</t>
+          <t>KELYA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FMAO</t>
+          <t>KIDS</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>FMBH</t>
+          <t>KINS</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>FMNB</t>
+          <t>KMRK</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>FNKO</t>
+          <t>KMTS</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>FNLC</t>
+          <t>KPLT</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>FRAF</t>
+          <t>KRNT</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FRBA</t>
+          <t>KRRO</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>FSSL</t>
+          <t>LCNB</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FTRE</t>
+          <t>LGND</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>FUNC</t>
+          <t>LIND</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>GABC</t>
+          <t>LMAT</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GAING</t>
+          <t>LNT</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GAINI</t>
+          <t>LOGI</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>GAINZ</t>
+          <t>LQDT</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>LSBK</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>MANH</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GDYN</t>
+          <t>MAZE</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>GEHC</t>
+          <t>MBWM</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>GIBO</t>
+          <t>MGRC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GIII</t>
+          <t>MIDD</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>MLKN</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>GLBE</t>
+          <t>MOBI</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>MQ</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>MTC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GP</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>GTLB</t>
+          <t>MXCT</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>HAFC</t>
+          <t>MYGN</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>HALO</t>
+          <t>NBBK</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>NBTB</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>HBNC</t>
+          <t>NECB</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>HCKT</t>
+          <t>NMFCZ</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>HIFS</t>
+          <t>NRIX</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>NSSC</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>HPK</t>
+          <t>NTRSO</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>HSTM</t>
+          <t>NTWK</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>HTFL</t>
+          <t>NWE</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>HTHT</t>
+          <t>NWFL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>HURN</t>
+          <t>OBT</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>HWKN</t>
+          <t>OFIX</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>HYNE</t>
+          <t>OPCH</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>OPRT</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>IBCP</t>
+          <t>OPRX</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>IBEX</t>
+          <t>OTAI</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ICFI</t>
+          <t>OTEX</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>OVBC</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>IDXX</t>
+          <t>PBYI</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>PDLB</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>INDB</t>
+          <t>PFIS</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>INDP</t>
+          <t>PFXNZ</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>PHAR</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>IOSP</t>
+          <t>PLGO</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>IRLA</t>
+          <t>PLUS</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>IRON</t>
+          <t>PNFP</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>IRTC</t>
+          <t>PNTG</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>JAKK</t>
+          <t>PRGS</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>JCAP</t>
+          <t>PRME</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>JCSE</t>
+          <t>QCRH</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>QSI</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>JMSB</t>
+          <t>RBB</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>JOYY</t>
+          <t>RCBC</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>JYD</t>
+          <t>RCEL</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>KIDS</t>
+          <t>RDWR</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>KMTS</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>KPLT</t>
+          <t>RGS</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>LCNB</t>
+          <t>RILYG</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>LFCR</t>
+          <t>ROKU</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>LFST</t>
+          <t>RPAY</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LIFE</t>
+          <t>RPC</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>LIND</t>
+          <t>RPRX</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>LKFT</t>
+          <t>RRBI</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>LMRI</t>
+          <t>RVSB</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LNT</t>
+          <t>RYZ</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>LQDT</t>
+          <t>SAFT</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>SAGT</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MANE</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>MBRX</t>
+          <t>SBFG</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MCBS</t>
+          <t>SCHL</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MEDP</t>
+          <t>SEZL</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MEOH</t>
+          <t>SFNC</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>MGRC</t>
+          <t>SGP</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MITK</t>
+          <t>SIBN</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MKTX</t>
+          <t>SNFCA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>MMSI</t>
+          <t>SPSC</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>MQ</t>
+          <t>SPT</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MTC</t>
+          <t>SRCE</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MTEX</t>
+          <t>STBA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>STRC</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>MXCT</t>
+          <t>SUNB</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MYGN</t>
+          <t>SWIM</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NBTB</t>
+          <t>SYNA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>NCNO</t>
+          <t>SYRE</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>TACT</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>NICE</t>
+          <t>TASK</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NSIT</t>
+          <t>TCX</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>NSSC</t>
+          <t>THFF</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NTRA</t>
+          <t>TILE</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>NTRSO</t>
+          <t>TOP</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NTSK</t>
+          <t>TOWN</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>NWBI</t>
+          <t>TRAX</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NWE</t>
+          <t>TRI</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>NWFL</t>
+          <t>TRMB</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>OCTV</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>TROO</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ONC</t>
+          <t>TRS</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>OPRT</t>
+          <t>WCCB</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>OPRX</t>
+          <t>WLTH</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ORRF</t>
+          <t>XNCR</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>OSPN</t>
+          <t>HAS</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>OYSE</t>
+          <t>ALRM</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PAA</t>
+          <t>POWW</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>PAGP</t>
+          <t>EPSN</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>PBFS</t>
+          <t>OZK</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>FIVN</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PCRX</t>
+          <t>ESLA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>PEGA</t>
+          <t>CENT</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>PFBC</t>
+          <t>ROP</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PLBC</t>
+          <t>FIBK</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>COLB</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>PLUS</t>
+          <t>SIGI</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>PMTS</t>
+          <t>CHKP</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>PNFP</t>
+          <t>QLYS</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PNTG</t>
+          <t>ATGL</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>POM</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>POWW</t>
+          <t>GMAB</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>PRCH</t>
+          <t>SEPN</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PRGS</t>
+          <t>KXIN</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>CHMG</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>QCRH</t>
+          <t>AVPT</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>QDEL</t>
+          <t>CDZI</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>QLYS</t>
+          <t>INVE</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>QNBC</t>
+          <t>BBT</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>RCBC</t>
+          <t>SGRY</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>REF</t>
+          <t>ELMT</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>RELY</t>
+          <t>OCTV</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>RGS</t>
+          <t>OMH</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>RIGL</t>
+          <t>SLN</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ROKU</t>
+          <t>JAKK</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ROP</t>
+          <t>TLS</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>RPD</t>
+          <t>RENT</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>RPRX</t>
+          <t>DIBS</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>RUSHB</t>
+          <t>INDP</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>RVSB</t>
+          <t>EMBC</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>RYZ</t>
+          <t>NTSK</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>SAIC</t>
+          <t>RPD</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SBCF</t>
+          <t>INGN</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SBFG</t>
+          <t>YSWY</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>CENTA</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>SCSC</t>
+          <t>CLAR</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SEPN</t>
+          <t>TENB</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SEZL</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SFNC</t>
+          <t>ENGS</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>SGP</t>
+          <t>PLSE</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SIBN</t>
+          <t>NDAQ</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SIGI</t>
+          <t>MGRT</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>SKYA</t>
+          <t>MEDP</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>SLDE</t>
+          <t>HURN</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SLN</t>
+          <t>FNLC</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SONO</t>
+          <t>LFST</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SPT</t>
+          <t>IRTC</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>SRCE</t>
+          <t>ATRC</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SSNC</t>
+          <t>ORRF</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>STBA</t>
+          <t>NSIT</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>STLD</t>
+          <t>OSPN</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>STLN</t>
+          <t>MANE</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SUNB</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>SWKHL</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>SYNA</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>SYRE</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>TACT</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>TCMD</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>TENB</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>TILE</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>TLS</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>TRI</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>TRMB</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>TRS</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>TW</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>VSXY</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>WAFU</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>WLTH</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>WSBCO</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>YMAT</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>YSWY</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>OZK</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>PCTY</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>ACIW</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>OPK</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>XLAB</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>INTA</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>ARHS</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>EFOR</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>AVTR</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>EMBC</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>TBCH</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>ASBH</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>BMGL</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>DOX</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>FTDR</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>MORN</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>APPN</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>ASRV</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>BIIB</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>MANH</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>HON</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>STFS</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>TRAX</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>EPSN</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>AGNT</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>FRSH</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>PBYI</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>POOL</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>HQY</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>NTWK</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>AMPL</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>CWST</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>GRDX</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>MNDY</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>NIQ</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>DOCU</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>CDLR</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>BL</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>AVAH</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>REVB</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>BRZE</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>CDZI</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>DBX</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>SGHT</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>BETR</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>RPC</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>INGN</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>FA</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>SLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>KINS</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>DGICB</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>BLKB</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>COO</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>BRCB</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>OTEX</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>JJSF</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>CINF</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>ICG</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>UTHR</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>HCSG</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>CVBF</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>CDW</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr"/>
-      <c r="C103" t="inlineStr"/>
-      <c r="D103" t="inlineStr"/>
+          <t>SAIC</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_merged_latest.xlsx
+++ b/results/momentum_merged_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D83"/>
+  <dimension ref="A1:D90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,1794 +441,1952 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AEYE</t>
+          <t>AXIN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ACT</t>
+          <t>ACGL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>BKYI</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>ALGN</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>BOW</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ACU</t>
+          <t>BRLT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AMSF</t>
+          <t>ACNB</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>JCSE</t>
+          <t>BANR</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>CLAR</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BGSI</t>
+          <t>ACT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KELYB</t>
+          <t>BBSI</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>GMAB</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>BMGL</t>
+          <t>ADAMI</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>POM</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AER</t>
+          <t>JVA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CARR</t>
+          <t>ADMA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>CCB</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>KIDS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ALLT</t>
+          <t>ADUS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CCB</t>
+          <t>CIGI</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AMAL</t>
+          <t>PACB</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CTSO</t>
+          <t>AER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AMPL</t>
+          <t>CNDT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DHCNI</t>
+          <t>POM</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>AMRO</t>
+          <t>AEYE</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EJH</t>
+          <t>CTSO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AMRX</t>
+          <t>PRME</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ELUT</t>
+          <t>AFRI</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ANIK</t>
+          <t>CVSA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FLX</t>
+          <t>SDHIU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>APPN</t>
+          <t>AGIO</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>IMCR</t>
+          <t>DGNX</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ARHS</t>
+          <t>AGYS</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>JDZG</t>
+          <t>DHCNI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ARLP</t>
+          <t>ALKS</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>KLRA</t>
+          <t>ELUT</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ARQT</t>
+          <t>ALLT</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LIF</t>
+          <t>FCCO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ARXS</t>
+          <t>ALRS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NXPI</t>
+          <t>FTW</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ASTL</t>
+          <t>AMAL</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NYAX</t>
+          <t>HLMN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ATLCL</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>OIO</t>
+          <t>HONA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>AUDC</t>
+          <t>AMPL</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>OKYO</t>
+          <t>JDZG</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AUPH</t>
+          <t>ANIK</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>OSW</t>
+          <t>KLTR</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>AVAH</t>
+          <t>AOUT</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PWRL</t>
+          <t>KRMD</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AVBH</t>
+          <t>API</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>RSVR</t>
+          <t>LBRX</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>BANR</t>
+          <t>AQB</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SOLS</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BCAL</t>
+          <t>ARHS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>STAA</t>
+          <t>NWBI</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>BETR</t>
+          <t>ARLP</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TCBK</t>
+          <t>OIO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BL</t>
+          <t>AROW</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TREE</t>
+          <t>PCSA</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>BLKB</t>
+          <t>ARQT</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>VMRK</t>
+          <t>PEBO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BOTJ</t>
+          <t>ARX</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BPRN</t>
+          <t>PECO</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>BRCB</t>
+          <t>ARXS</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BRZE</t>
+          <t>SNES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BSET</t>
+          <t>ASND</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BSIN</t>
+          <t>SNY</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>BSRR</t>
+          <t>ASRV</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BSVN</t>
+          <t>TCMD</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BUSE</t>
+          <t>ASTL</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BVC</t>
+          <t>ATEC</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>BVS</t>
+          <t>ATER</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BWFG</t>
+          <t>ATRC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BWMN</t>
+          <t>AUPH</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CASS</t>
+          <t>AVBH</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CATY</t>
+          <t>AVPT</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CCID</t>
+          <t>AZTA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CCSI</t>
+          <t>BBT</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>BDCI</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>BIIB</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CFFI</t>
+          <t>BL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CGNT</t>
+          <t>BLLN</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>BLZR</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CINF</t>
+          <t>BPRN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CNXC</t>
+          <t>BSET</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CRSR</t>
+          <t>BSIN</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CSX</t>
+          <t>BSP</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CTKB</t>
+          <t>BSRR</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>BWFG</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CVBF</t>
+          <t>BWMN</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CVLT</t>
+          <t>BZ</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CYRX</t>
+          <t>CAI</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CZFS</t>
+          <t>CART</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DAKT</t>
+          <t>CATY</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DBX</t>
+          <t>CBC</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>CBNK</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DLTR</t>
+          <t>CBRL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DMRC</t>
+          <t>CCBG</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>DOCU</t>
+          <t>CCID</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>DOX</t>
+          <t>CCSI</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DSP</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>CDNA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ERIC</t>
+          <t>CENT</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ESQ</t>
+          <t>CENTA</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>EWBC</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EXE</t>
+          <t>CFFI</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>EXLS</t>
+          <t>CHMG</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>EXYN</t>
+          <t>CIVB</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FBIZ</t>
+          <t>CLBT</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FCBM</t>
+          <t>COFS</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FCNCA</t>
+          <t>COLB</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>FFBC</t>
+          <t>CPSS</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>FITB</t>
+          <t>CTAS</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FMAO</t>
+          <t>CTKB</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FMBH</t>
+          <t>CV</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>FNKO</t>
+          <t>CWST</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>FRME</t>
+          <t>CYRX</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FSSL</t>
+          <t>DAKT</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>FTDR</t>
+          <t>DBX</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>FTRE</t>
+          <t>DCOM</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>FUNC</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FVNNU</t>
+          <t>DHCNL</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GAINI</t>
+          <t>DMAC</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>GCBC</t>
+          <t>DMRC</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GDRX</t>
+          <t>DSP</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GDYN</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>EGBN</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>GRDX</t>
+          <t>ELMT</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>GRFS</t>
+          <t>EPSN</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GSBC</t>
+          <t>ETSY</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GTM</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>HAFC</t>
+          <t>EXEL</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>HBT</t>
+          <t>FA</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>HCKT</t>
+          <t>FBNC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>HCSG</t>
+          <t>FCAP</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>FCBM</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>HON</t>
+          <t>FCNCA</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>FFBC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>HQY</t>
+          <t>FITB</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>HTFL</t>
+          <t>FIVE</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HWBK</t>
+          <t>FIVN</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>HWKN</t>
+          <t>FLYW</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>IBEX</t>
+          <t>FMAO</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>FMBH</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>FMNB</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>FNLC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>IMC</t>
+          <t>FRAF</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>IMKTA</t>
+          <t>FRBA</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>INDB</t>
+          <t>FROG</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>FSBC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>FTRE</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>IOSP</t>
+          <t>FULT</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>IOVA</t>
+          <t>FVN</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>IRON</t>
+          <t>FVNNU</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>JBDI</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>JOUT</t>
+          <t>GEHC</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>JYD</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>KELYA</t>
+          <t>GRAL</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>KIDS</t>
+          <t>GSBC</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>KINS</t>
+          <t>GTLB</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>KMRK</t>
+          <t>HAFC</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>KMTS</t>
+          <t>HALO</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>KPLT</t>
+          <t>HAS</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>KRNT</t>
+          <t>HCKT</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>KRRO</t>
+          <t>HCSG</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>LCNB</t>
+          <t>HLP</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>LGND</t>
+          <t>HMR</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LIND</t>
+          <t>HON</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>LMAT</t>
+          <t>HSTM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LNT</t>
+          <t>HTFL</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>LOGI</t>
+          <t>HURN</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LQDT</t>
+          <t>IA</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>LSBK</t>
+          <t>IBEX</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MANH</t>
+          <t>ICFI</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MAZE</t>
+          <t>ICG</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>MBWM</t>
+          <t>ICLR</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MGRC</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MIDD</t>
+          <t>INDB</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MLKN</t>
+          <t>INDP</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>MOBI</t>
+          <t>INGN</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MQ</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>MTC</t>
+          <t>IOVA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>IRON</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>MXCT</t>
+          <t>IRTC</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MYGN</t>
+          <t>ISBA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NBBK</t>
+          <t>JAKK</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NBTB</t>
+          <t>JJSF</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NECB</t>
+          <t>JKHY</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>NMFCZ</t>
+          <t>JMSB</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NRIX</t>
+          <t>JYD</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>NSSC</t>
+          <t>KARO</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NTRSO</t>
+          <t>KELYA</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>NTWK</t>
+          <t>KMRK</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NWE</t>
+          <t>KMTS</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>NWFL</t>
+          <t>KOD</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>OBT</t>
+          <t>KPLT</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>OFIX</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>OPCH</t>
+          <t>KYIV</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>OPRT</t>
+          <t>LCNB</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>OPRX</t>
+          <t>LEGN</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>OTAI</t>
+          <t>LFST</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>OTEX</t>
+          <t>LGND</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>OVBC</t>
+          <t>LIFE</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>PBYI</t>
+          <t>LIVN</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PDLB</t>
+          <t>LKFT</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>LMRI</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>PFIS</t>
+          <t>LQDT</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>PFXNZ</t>
+          <t>LSBK</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>PHAR</t>
+          <t>MANE</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PLGO</t>
+          <t>MANH</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>PLUS</t>
+          <t>MBWM</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>PNFP</t>
+          <t>MCBS</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PNTG</t>
+          <t>MEDP</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>MGPI</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>PRGS</t>
+          <t>MGRT</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>PRME</t>
+          <t>MOBI</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>QCRH</t>
+          <t>MSBI</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>QSI</t>
+          <t>MWYN</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>RBB</t>
+          <t>MXCT</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>RCBC</t>
+          <t>MYGN</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>RCEL</t>
+          <t>NAUT</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>RDWR</t>
+          <t>NBN</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>NBTB</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>RGS</t>
+          <t>NDAQ</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>RILYG</t>
+          <t>NECB</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ROKU</t>
+          <t>NICE</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>RPAY</t>
+          <t>NMIH</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>RPC</t>
+          <t>NRC</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>RPRX</t>
+          <t>NRIX</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>RRBI</t>
+          <t>NSIT</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>RVSB</t>
+          <t>NTNX</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>RYZ</t>
+          <t>NTRA</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SAFT</t>
+          <t>NTSK</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SAGT</t>
+          <t>OCTV</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>OFIX</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>SBFG</t>
+          <t>OM</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SCHL</t>
+          <t>OMCL</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SEZL</t>
+          <t>ONC</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SFNC</t>
+          <t>OPCH</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>SGP</t>
+          <t>OPRX</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SIBN</t>
+          <t>OSW</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SNFCA</t>
+          <t>OTEX</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SPSC</t>
+          <t>OVBC</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>SPT</t>
+          <t>OZK</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SRCE</t>
+          <t>PDLB</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>STBA</t>
+          <t>PHAR</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>STRC</t>
+          <t>PLSE</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>SUNB</t>
+          <t>PNRG</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SWIM</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SYNA</t>
+          <t>POWW</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>SYRE</t>
+          <t>PPLC</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>TACT</t>
+          <t>PRCH</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>TASK</t>
+          <t>PRCT</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>TCX</t>
+          <t>PRGS</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>THFF</t>
+          <t>PRTH</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>TILE</t>
+          <t>PSIG</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>TOP</t>
+          <t>PTEN</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>TOWN</t>
+          <t>QCRH</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>TRAX</t>
+          <t>QDEL</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>TRI</t>
+          <t>QLYS</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>TRMB</t>
+          <t>QNBC</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>QSI</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>TROO</t>
+          <t>RCEL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>TRS</t>
+          <t>RDVT</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>WCCB</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>WLTH</t>
+          <t>RMBI</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>XNCR</t>
+          <t>RPD</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>RRBI</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ALRM</t>
+          <t>RWAYI</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>POWW</t>
+          <t>SAFT</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>EPSN</t>
+          <t>SBAC</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>OZK</t>
+          <t>SBUX</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>FIVN</t>
+          <t>SEPN</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ESLA</t>
+          <t>SEZL</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CENT</t>
+          <t>SGHT</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ROP</t>
+          <t>SGMT</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>FIBK</t>
+          <t>SGP</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>COLB</t>
+          <t>SHOE</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SIGI</t>
+          <t>SHPH</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>CHKP</t>
+          <t>SIBN</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>QLYS</t>
+          <t>SKYA</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ATGL</t>
+          <t>SLDE</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>SPSC</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>SRZN</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SEPN</t>
+          <t>STAA</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>KXIN</t>
+          <t>STAK</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CHMG</t>
+          <t>STRC</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>AVPT</t>
+          <t>SUNB</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CDZI</t>
+          <t>SWIM</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>INVE</t>
+          <t>SWKS</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>BBT</t>
+          <t>SWRD</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>SGRY</t>
+          <t>SYRE</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ELMT</t>
+          <t>TECH</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>OCTV</t>
+          <t>TENB</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>OMH</t>
+          <t>TLS</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>SLN</t>
+          <t>TRAX</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>JAKK</t>
+          <t>TRMB</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>TLS</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>RENT</t>
+          <t>TROO</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>DIBS</t>
+          <t>TW</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>INDP</t>
+          <t>UTHR</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EMBC</t>
+          <t>VALU</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>NTSK</t>
+          <t>WCCB</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>RPD</t>
+          <t>XNCR</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>INGN</t>
+          <t>XZO</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
+          <t>YORW</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
           <t>YSWY</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>CENTA</t>
-        </is>
-      </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>CLAR</t>
+          <t>AR</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>TENB</t>
+          <t>BETR</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>XFOR</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>MGRC</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>PLSE</t>
+          <t>ALRM</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>CZNC</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>MGRT</t>
+          <t>ROP</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MEDP</t>
+          <t>BMGL</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>HURN</t>
+          <t>SLN</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>FNLC</t>
+          <t>RENT</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>LFST</t>
+          <t>OSPN</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>IRTC</t>
+          <t>SGRY</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ATRC</t>
+          <t>RDWR</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ORRF</t>
+          <t>SAIC</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>NSIT</t>
+          <t>ABVC</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>OSPN</t>
+          <t>ESLA</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>MANE</t>
+          <t>TACT</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SAIC</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr"/>
-      <c r="C83" t="inlineStr"/>
-      <c r="D83" t="inlineStr"/>
+          <t>CHKP</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>SAIL</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>BRCB</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NTWK</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>NWFL</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>ATGL</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>GIBO</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>DOO</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>CGNT</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>ESQ</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>CINF</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>BRZE</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>NWE</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>KXIN</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>DIBS</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>TNDM</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>AMRX</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>CDZI</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>KRRO</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>GRDX</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>CBFV</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>RPRX</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>PYPD</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>ENGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>CSX</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>NSSC</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>IMC</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>SAGT</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>SIGI</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>OLED</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_merged_latest.xlsx
+++ b/results/momentum_merged_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,17 +441,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AXIN</t>
+          <t>BSBK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ACGL</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BKYI</t>
+          <t>PCSA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -463,1930 +463,2906 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BRLT</t>
+          <t>CART</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ACNB</t>
+          <t>ABLV</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BANR</t>
+          <t>ASR</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CLAR</t>
+          <t>CEPO</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ACT</t>
+          <t>ABSI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BBSI</t>
+          <t>BANR</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>COAG</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ADAMI</t>
+          <t>ACGL</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>BBIO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JVA</t>
+          <t>DHCNI</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ADMA</t>
+          <t>ACIC</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CCB</t>
+          <t>BBSI</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KIDS</t>
+          <t>FRAF</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ADUS</t>
+          <t>ACIW</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CIGI</t>
+          <t>BCBP</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PACB</t>
+          <t>FVNNU</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AER</t>
+          <t>ACNB</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CNDT</t>
+          <t>BGSI</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>POM</t>
+          <t>MAYS</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>AEYE</t>
+          <t>ACT</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CTSO</t>
+          <t>BKU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PRME</t>
+          <t>MFIC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AFRI</t>
+          <t>ACU</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CVSA</t>
+          <t>BOTJ</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SDHIU</t>
+          <t>NUWE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>ADMA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DGNX</t>
+          <t>CARG</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>AGYS</t>
+          <t>PTLE</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DHCNI</t>
+          <t>ADUS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ALKS</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ELUT</t>
+          <t>QNBC</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ALLT</t>
+          <t>AER</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FCCO</t>
+          <t>CHDN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ALRS</t>
+          <t>STFS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FTW</t>
+          <t>AEYE</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AMAL</t>
+          <t>CIGI</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HLMN</t>
+          <t>AFRI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>CLBT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>HONA</t>
+          <t>ALKS</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>AMPL</t>
+          <t>COLL</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>JDZG</t>
+          <t>ALLT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ANIK</t>
+          <t>COO</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>KLTR</t>
+          <t>ALMR</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>AOUT</t>
+          <t>CPRT</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>KRMD</t>
+          <t>ALRM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>DORM</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LBRX</t>
+          <t>ALRS</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>AQB</t>
+          <t>EVER</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>AMAL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ARHS</t>
+          <t>EXE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NWBI</t>
+          <t>AMCR</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ARLP</t>
+          <t>EXYN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>OIO</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AROW</t>
+          <t>FHB</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PCSA</t>
+          <t>ANDG</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ARQT</t>
+          <t>FISV</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PEBO</t>
+          <t>ANIK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ARX</t>
+          <t>FLWS</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PECO</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ARXS</t>
+          <t>GIII</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SNES</t>
+          <t>APOG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ASND</t>
+          <t>HBAN</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SNY</t>
+          <t>AQB</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ASRV</t>
+          <t>HLMN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TCMD</t>
+          <t>ARHS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ASTL</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ATEC</t>
+          <t>ARLP</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ATER</t>
+          <t>IDN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ATRC</t>
+          <t>AROW</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AUPH</t>
+          <t>IVA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AVBH</t>
+          <t>ARQT</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>AVPT</t>
+          <t>JMSB</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AZTA</t>
+          <t>ASND</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BBT</t>
+          <t>JRVR</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BDCI</t>
+          <t>ASO</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>KLRA</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BL</t>
+          <t>ASTL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BLLN</t>
+          <t>KRMD</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BLZR</t>
+          <t>ATEC</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>BPRN</t>
+          <t>KXIN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BSET</t>
+          <t>ATLCL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BSIN</t>
+          <t>LIF</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BSP</t>
+          <t>ATLCZ</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>BSRR</t>
+          <t>LMAT</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BWFG</t>
+          <t>ATR</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BWMN</t>
+          <t>LWAY</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>ATRC</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CAI</t>
+          <t>MVBF</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CART</t>
+          <t>AUDC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CATY</t>
+          <t>NXST</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CBC</t>
+          <t>AVAH</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CBNK</t>
+          <t>OSIS</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CBRL</t>
+          <t>AVBC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CCBG</t>
+          <t>PATK</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CCID</t>
+          <t>AVBH</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>CCSI</t>
+          <t>PECO</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CD</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>PLAY</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CENT</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>CENTA</t>
+          <t>PLUR</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>AZTA</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CFFI</t>
+          <t>PRPL</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CHMG</t>
+          <t>BANF</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>CIVB</t>
+          <t>QNST</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CLBT</t>
+          <t>BBT</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>COFS</t>
+          <t>RARE</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>COLB</t>
+          <t>BETR</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CPSS</t>
+          <t>RBB</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>BFST</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CTKB</t>
+          <t>RSVR</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CV</t>
+          <t>BHRB</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CWST</t>
+          <t>SIRI</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CYRX</t>
+          <t>BLLN</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DAKT</t>
+          <t>SMBC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DBX</t>
+          <t>BMRC</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>DCOM</t>
+          <t>SNES</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>BOBS</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DHCNL</t>
+          <t>SYBT</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DMAC</t>
+          <t>BOW</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>DMRC</t>
+          <t>TCBK</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DSP</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>TCBS</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>EGBN</t>
+          <t>BRLT</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ELMT</t>
+          <t>TOWN</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>EPSN</t>
+          <t>BSET</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ETSY</t>
+          <t>TREE</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>BSP</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>XFOR</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>FA</t>
+          <t>BSVN</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FBNC</t>
+          <t>XLAB</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FCAP</t>
+          <t>BUUU</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>FCBM</t>
+          <t>YORW</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>FCNCA</t>
+          <t>BVS</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FFBC</t>
+          <t>BWFG</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>FITB</t>
+          <t>BWIN</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>FIVE</t>
+          <t>CAC</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>FIVN</t>
+          <t>CAI</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FLYW</t>
+          <t>CARL</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>FMAO</t>
+          <t>CATY</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>FMBH</t>
+          <t>CBC</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>FMNB</t>
+          <t>CBK</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FNLC</t>
+          <t>CBNK</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>FRAF</t>
+          <t>CBRL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>FRBA</t>
+          <t>CBU</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>FROG</t>
+          <t>CCBG</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FSBC</t>
+          <t>CCNE</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FTRE</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>FULT</t>
+          <t>CDW</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>FVN</t>
+          <t>CDZI</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FVNNU</t>
+          <t>CFBK</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>CFFI</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>GEHC</t>
+          <t>CFR</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>CGNT</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GRAL</t>
+          <t>CHCO</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GSBC</t>
+          <t>CHKP</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>GTLB</t>
+          <t>CHMG</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>HAFC</t>
+          <t>CHRD</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>HALO</t>
+          <t>CINF</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>CING</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>HCKT</t>
+          <t>CIVB</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>HCSG</t>
+          <t>CLAR</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>CLMB</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>HMR</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>HON</t>
+          <t>COFS</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>HSTM</t>
+          <t>COKE</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>HTFL</t>
+          <t>COLB</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>HURN</t>
+          <t>COLM</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>CRAI</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>IBEX</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ICFI</t>
+          <t>CSX</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ICG</t>
+          <t>CTAS</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>CTKB</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>CV</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>INDB</t>
+          <t>CYPH</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>INDP</t>
+          <t>CZFS</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>INGN</t>
+          <t>CZNC</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>CZWI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>IOVA</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>IRON</t>
+          <t>DGICA</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>IRTC</t>
+          <t>DHCNL</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ISBA</t>
+          <t>DLTR</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>JAKK</t>
+          <t>DOO</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>JJSF</t>
+          <t>DOX</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>DTIL</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>JMSB</t>
+          <t>DUKU</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>JYD</t>
+          <t>DYOR</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>KARO</t>
+          <t>EBAY</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>KELYA</t>
+          <t>EBC</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>KMRK</t>
+          <t>EDHL</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>KMTS</t>
+          <t>EFSI</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>KOD</t>
+          <t>EGBN</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>KPLT</t>
+          <t>EGHT</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>ELMT</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>KYIV</t>
+          <t>EMBC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>LCNB</t>
+          <t>ENTX</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LEGN</t>
+          <t>ENVX</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>LFST</t>
+          <t>EPSN</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>LGND</t>
+          <t>ERIC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>LIFE</t>
+          <t>ERIE</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LIVN</t>
+          <t>ESLT</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>LKFT</t>
+          <t>ESQ</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>LMRI</t>
+          <t>EWBC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>LQDT</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LSBK</t>
+          <t>EXPO</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MANE</t>
+          <t>FA</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MANH</t>
+          <t>FANG</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MBWM</t>
+          <t>FAST</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>MCBS</t>
+          <t>FBIZ</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MEDP</t>
+          <t>FBLA</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MGPI</t>
+          <t>FCAP</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MGRT</t>
+          <t>FCBM</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>MOBI</t>
+          <t>FCCO</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MSBI</t>
+          <t>FCNCA</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MWYN</t>
+          <t>FDBC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MXCT</t>
+          <t>FFBC</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>MYGN</t>
+          <t>FGBI</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>NAUT</t>
+          <t>FIBK</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NBN</t>
+          <t>FISI</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>NBTB</t>
+          <t>FITB</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>FIVE</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>NECB</t>
+          <t>FLYW</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NICE</t>
+          <t>FMAO</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>NMIH</t>
+          <t>FMBH</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NRC</t>
+          <t>FMNB</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>NRIX</t>
+          <t>FNKO</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NSIT</t>
+          <t>FNLC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>NTNX</t>
+          <t>FNWD</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NTRA</t>
+          <t>FRBA</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>NTSK</t>
+          <t>FRD</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>OCTV</t>
+          <t>FRHC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>OFIX</t>
+          <t>FRME</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>OM</t>
+          <t>FRMEP</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>OMCL</t>
+          <t>FSBC</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ONC</t>
+          <t>FSSL</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>OPCH</t>
+          <t>FSV</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>OPRX</t>
+          <t>FTDR</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>OSW</t>
+          <t>FULT</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>OTEX</t>
+          <t>FUNC</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>OVBC</t>
+          <t>FVN</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>OZK</t>
+          <t>GCT</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>PDLB</t>
+          <t>GDRX</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PHAR</t>
+          <t>GEHC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>PLSE</t>
+          <t>GH</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>PNRG</t>
+          <t>GILD</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>GLBE</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>POWW</t>
+          <t>GRAL</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>PPLC</t>
+          <t>GSBC</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>PRCH</t>
+          <t>HAFC</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PRCT</t>
+          <t>HALO</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PRGS</t>
+          <t>HBIO</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>PRTH</t>
+          <t>HBNC</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>PSIG</t>
+          <t>HBT</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PTEN</t>
+          <t>HCSG</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>QCRH</t>
+          <t>HELE</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>QDEL</t>
+          <t>HIFS</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>QLYS</t>
+          <t>HON</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>QNBC</t>
+          <t>HOWL</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>QSI</t>
+          <t>HQY</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>RCEL</t>
+          <t>HTFL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>RDVT</t>
+          <t>HTHT</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>HURN</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>RMBI</t>
+          <t>HWBK</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>RPD</t>
+          <t>HYNE</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>RRBI</t>
+          <t>IA</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>RWAYI</t>
+          <t>IBCP</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SAFT</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SBAC</t>
+          <t>ICUI</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>IDXX</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SEPN</t>
+          <t>IMC</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SEZL</t>
+          <t>INDB</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SGHT</t>
+          <t>INDP</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>SGMT</t>
+          <t>INGN</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SGP</t>
+          <t>INTG</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SHOE</t>
+          <t>IOSP</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SHPH</t>
+          <t>IRON</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>SIBN</t>
+          <t>IRTC</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SKYA</t>
+          <t>ISBA</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SLDE</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>SPSC</t>
+          <t>JAKK</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>SRZN</t>
+          <t>JJSF</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STAA</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>STAK</t>
+          <t>JVA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>STRC</t>
+          <t>KARO</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>SUNB</t>
+          <t>KDP</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SWIM</t>
+          <t>KIDS</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SWKS</t>
+          <t>KINS</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>SWRD</t>
+          <t>KLTR</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>SYRE</t>
+          <t>KMTS</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>TECH</t>
+          <t>KNSA</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>TENB</t>
+          <t>KOD</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>TLS</t>
+          <t>KPLT</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>TRAX</t>
+          <t>KRNT</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>TRMB</t>
+          <t>KROS</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>KRRO</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>TROO</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>KVHI</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>UTHR</t>
+          <t>KYIV</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>VALU</t>
+          <t>LARK</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>WCCB</t>
+          <t>LBRX</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>XNCR</t>
+          <t>LECO</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>XZO</t>
+          <t>LFST</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>YORW</t>
+          <t>LIFE</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>YSWY</t>
+          <t>LIND</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>LIVN</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BETR</t>
+          <t>LKFN</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>XFOR</t>
+          <t>LKFT</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MGRC</t>
+          <t>LLYVA</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ALRM</t>
+          <t>LLYVK</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CZNC</t>
+          <t>LMRI</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ROP</t>
+          <t>LNT</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>BMGL</t>
+          <t>LOVE</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>SLN</t>
+          <t>LQDT</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>RENT</t>
+          <t>LSBK</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>OSPN</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SGRY</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>RDWR</t>
+          <t>MANE</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SAIC</t>
+          <t>MANH</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ABVC</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ESLA</t>
+          <t>MAZE</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>TACT</t>
+          <t>MBWM</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CHKP</t>
+          <t>MCBS</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>MEOH</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>BRCB</t>
+          <t>MGPI</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NTWK</t>
+          <t>MGRC</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>NWFL</t>
+          <t>MGRT</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ATGL</t>
+          <t>MIDD</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>GIBO</t>
+          <t>MNST</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>DOO</t>
+          <t>MORN</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>CGNT</t>
+          <t>MRSH</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ESQ</t>
+          <t>MSBI</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>CINF</t>
+          <t>MSEX</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>BRZE</t>
+          <t>MTEX</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>NWE</t>
+          <t>MXCT</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>KXIN</t>
+          <t>MYFW</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>DIBS</t>
+          <t>MZTI</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>TNDM</t>
+          <t>NAVN</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AMRX</t>
+          <t>NBBK</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CDZI</t>
+          <t>NBN</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>KRRO</t>
+          <t>NBTX</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>GRDX</t>
+          <t>NDAQ</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CBFV</t>
+          <t>NECB</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>RPRX</t>
+          <t>NICE</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>PYPD</t>
+          <t>NMIH</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>NOVT</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CSX</t>
+          <t>NPAC</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>NSSC</t>
+          <t>NRC</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>IMC</t>
+          <t>NRDS</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>SAGT</t>
+          <t>NRIX</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
+          <t>NSIT</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>NSSC</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>NTCT</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NTGR</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>NTNX</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>NTRA</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>NUTX</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NWBI</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>NXPI</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>OBT</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>OFIX</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>OFS</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>OKTA</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>OMAB</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>OMCL</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>ONC</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>OPK</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>OPLN</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>OPRT</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>OPRX</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>ORKA</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>ORRF</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>OSG</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>OSPN</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>OSUR</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>OSW</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>OTAI</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>OTTR</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>OVBC</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>OVLY</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>OXLCO</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>OXLCZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>OZK</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>PAA</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>PACB</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>PAGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>PDLB</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>PDSB</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>PEBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>PFBC</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>PFIS</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>PGNY</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>PGY</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>PLBC</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>PLBY</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>PLGO</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>PLMR</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>PLSE</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>PLUS</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>PNFP</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>PNTG</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>PODD</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>POOL</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>POWW</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>PPLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>PRCT</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>PRME</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>PRVA</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>PSIG</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>PTON</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>QDEL</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>QLYS</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>QSI</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>RCBC</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>RCEL</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>REAL</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>REF</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>REGN</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>RELY</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>REYN</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>RGCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>RIGL</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>RLAY</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>RMBI</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>ROIV</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>ROOT</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>RPAY</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>RPC</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>RRBI</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>RYZ</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>SBAC</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>SBFG</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>SBUX</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>SCHL</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>SEPN</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>SEZL</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>SFNC</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>SFST</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>SGHT</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>SGP</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>SHOE</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>SHPH</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>SIBN</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
           <t>SIGI</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>OLED</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>SLAB</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>SNFCA</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>SNY</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>SOMN</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>SPFI</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>SPTX</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>SRCE</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>SRZN</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>SSTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>STAA</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>STBA</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>STLD</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>STRC</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>SUNB</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>SWIM</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>SWRD</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>TACO</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>TACT</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>TBCH</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>TCMD</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>TENB</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>TFSL</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>TGTX</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>THFF</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>TILE</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>TMCI</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>TNDM</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>TRAX</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>TRMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>TRMD</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>UTHR</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>VSXY</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>WCCB</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>YMAT</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>ATGL</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>BMGL</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>GIBO</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>NTSK</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>MEDP</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>BRCB</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>DIBS</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>MOBI</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>CERT</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>ENGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>MRVI</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>PNRG</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>PHAR</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>JLHL</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>BSIN</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>PYPD</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>BOLT</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>JYD</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>EFOI</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>NOVTU</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>ANIX</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>GMAB</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>AIOK</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>PTEN</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>HLP</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>SAIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>RENT</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>RIBBU</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>ATER</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>SWKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>TLS</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>DGII</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>SGRY</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>INM</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>HAS</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>MYGN</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>NTWK</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>SLN</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>AVPT</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>SAGT</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>RDWR</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>ITRI</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>LEGN</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>BRZE</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>AMRX</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>RICK</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>GNSS</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>AIFA</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>BVC</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>BSRR</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_merged_latest.xlsx
+++ b/results/momentum_merged_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D134"/>
+  <dimension ref="A1:D113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,29 +441,29 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BSBK</t>
+          <t>CDNA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>ABCL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>PCSA</t>
+          <t>BRKRP</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ALGN</t>
+          <t>AHRT</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CART</t>
+          <t>CHOW</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -473,2896 +473,2426 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ASR</t>
+          <t>HBNB</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CEPO</t>
+          <t>BANR</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ABSI</t>
+          <t>FBIZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BANR</t>
+          <t>ACGL</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>COAG</t>
+          <t>BBSI</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ACGL</t>
+          <t>GDYN</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BBIO</t>
+          <t>ACIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DHCNI</t>
+          <t>BCBP</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ACIC</t>
+          <t>MEOH</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>BBSI</t>
+          <t>ACIW</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FRAF</t>
+          <t>BGSI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ACIW</t>
+          <t>NSLRL</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BCBP</t>
+          <t>ACNB</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FVNNU</t>
+          <t>BOKF</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ACNB</t>
+          <t>OSPN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BGSI</t>
+          <t>ACU</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MAYS</t>
+          <t>CASY</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ACT</t>
+          <t>REGN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BKU</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MFIC</t>
+          <t>CHDN</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ACU</t>
+          <t>SHOE</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>BOTJ</t>
+          <t>ADPT</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NUWE</t>
+          <t>CLRO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ADMA</t>
+          <t>SNY</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CARG</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>PTLE</t>
+          <t>COLL</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>TOMZ</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>ADUS</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>CASH</t>
-        </is>
-      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>QNBC</t>
+          <t>COO</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>AER</t>
+          <t>AEP</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>CRNT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>STFS</t>
+          <t>AFRI</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AEYE</t>
+          <t>CWST</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CIGI</t>
+          <t>AGYS</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AFRI</t>
+          <t>DPZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CLBT</t>
+          <t>ALKS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ALKS</t>
+          <t>EJH</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>COLL</t>
+          <t>ALLT</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ALLT</t>
+          <t>ESTA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>COO</t>
+          <t>ALRS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ALMR</t>
+          <t>EVER</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CPRT</t>
+          <t>AMGN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ALRM</t>
+          <t>EXTR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DORM</t>
+          <t>AMRX</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ALRS</t>
+          <t>FISV</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EVER</t>
+          <t>ANIK</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AMAL</t>
+          <t>HBAN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EXE</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AMCR</t>
+          <t>IDN</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>EXYN</t>
+          <t>API</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>IMCR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FHB</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ANDG</t>
+          <t>INSG</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>FISV</t>
+          <t>AROW</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ANIK</t>
+          <t>KWY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FLWS</t>
+          <t>ARQT</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>LMAT</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>GIII</t>
+          <t>ARX</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>APOG</t>
+          <t>LWAY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HBAN</t>
+          <t>ASBH</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AQB</t>
+          <t>MGEE</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>HLMN</t>
+          <t>ASND</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ARHS</t>
+          <t>NBIX</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>ATLCL</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ARLP</t>
+          <t>NBN</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>IDN</t>
+          <t>ATLCZ</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AROW</t>
+          <t>NXST</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>IVA</t>
+          <t>ATR</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ARQT</t>
+          <t>NYAX</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>JMSB</t>
+          <t>AUDC</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ASND</t>
+          <t>OFIX</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>JRVR</t>
+          <t>AUPH</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ASO</t>
+          <t>PATK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>KLRA</t>
+          <t>AVBC</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ASTL</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>KRMD</t>
+          <t>AVBH</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ATEC</t>
+          <t>PECO</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>KXIN</t>
+          <t>AWR</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ATLCL</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LIF</t>
+          <t>AXGN</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ATLCZ</t>
+          <t>PLUR</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LMAT</t>
+          <t>AZN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ATR</t>
+          <t>PRTA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LWAY</t>
+          <t>BBCP</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ATRC</t>
+          <t>QQQX</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>MVBF</t>
+          <t>BBIO</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AUDC</t>
+          <t>RARE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NXST</t>
+          <t>BFST</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AVAH</t>
+          <t>RDCM</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>OSIS</t>
+          <t>BHRB</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AVBC</t>
+          <t>SIRI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PATK</t>
+          <t>BIIB</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AVBH</t>
+          <t>SMBC</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>PECO</t>
+          <t>BL</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>SOLS</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PLAY</t>
+          <t>BLKB</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>TCBK</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>PLUR</t>
+          <t>BMGL</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AZTA</t>
+          <t>TCX</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PRPL</t>
+          <t>BMRC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BANF</t>
+          <t>VMRK</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>QNST</t>
+          <t>BOOM</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BBT</t>
+          <t>YORW</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>RARE</t>
+          <t>BOW</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>BETR</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>RBB</t>
+          <t>BSBK</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BFST</t>
+          <t>BSIN</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>RSVR</t>
+          <t>BSP</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BHRB</t>
+          <t>BSY</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SIRI</t>
+          <t>BUUU</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BLLN</t>
+          <t>BVC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SMBC</t>
+          <t>BVFL</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BMRC</t>
+          <t>BWFG</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>SNES</t>
+          <t>BZ</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BOBS</t>
+          <t>CARL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SYBT</t>
+          <t>CATY</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BOW</t>
+          <t>CBC</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>TCBK</t>
+          <t>CBK</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>CBU</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>TCBS</t>
+          <t>CCEP</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>BRLT</t>
+          <t>CCID</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>TOWN</t>
+          <t>CCNE</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BSET</t>
+          <t>CDLR</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>TREE</t>
+          <t>CENT</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>BSP</t>
+          <t>CENTA</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>XFOR</t>
+          <t>CERT</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BSVN</t>
+          <t>CGNT</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>XLAB</t>
+          <t>CHCO</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>BUUU</t>
+          <t>CHKP</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>YORW</t>
+          <t>CHRD</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BVS</t>
+          <t>CIGI</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BWFG</t>
+          <t>CINF</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>BWIN</t>
+          <t>CING</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>CAC</t>
+          <t>CIVB</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CAI</t>
+          <t>CLGN</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CARL</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CATY</t>
+          <t>COAG</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CBC</t>
+          <t>COFS</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CBK</t>
+          <t>COLM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CBNK</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CBRL</t>
+          <t>CPB</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>CBU</t>
+          <t>CPRT</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CCBG</t>
+          <t>CRAI</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CCNE</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CD</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>CTAS</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CDZI</t>
+          <t>CVBF</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CFBK</t>
+          <t>CZFS</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CFFI</t>
+          <t>CZNC</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>CFR</t>
+          <t>CZWI</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CGNT</t>
+          <t>DCBO</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CHCO</t>
+          <t>DCOM</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CHKP</t>
+          <t>DGII</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>CHMG</t>
+          <t>DLTR</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CHRD</t>
+          <t>DMAA</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CINF</t>
+          <t>DMII</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CING</t>
+          <t>DORM</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>CIVB</t>
+          <t>DOX</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CLAR</t>
+          <t>DSP</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CLMB</t>
+          <t>DUKU</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>EBAY</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>COFS</t>
+          <t>EFSC</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>COKE</t>
+          <t>ENGS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>COLB</t>
+          <t>EPSN</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>COLM</t>
+          <t>ERIC</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>CRAI</t>
+          <t>ERIE</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>ESQ</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CSX</t>
+          <t>EVRG</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>EWBC</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>CTKB</t>
+          <t>EXC</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CV</t>
+          <t>EXEL</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CYPH</t>
+          <t>EXLS</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CZFS</t>
+          <t>EXPO</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>CZNC</t>
+          <t>FA</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CZWI</t>
+          <t>FANG</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>FBNC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>DGICA</t>
+          <t>FCBM</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>DHCNL</t>
+          <t>FCCO</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DLTR</t>
+          <t>FCNCA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DOO</t>
+          <t>FDBC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>DOX</t>
+          <t>FGBI</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>DTIL</t>
+          <t>FIZZ</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DUKU</t>
+          <t>FMAO</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DYOR</t>
+          <t>FNLC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>FRAF</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>EBC</t>
+          <t>FRBA</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>EDHL</t>
+          <t>FRD</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>EFSI</t>
+          <t>FRHC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>EGBN</t>
+          <t>FRME</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>EGHT</t>
+          <t>FSBC</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ELMT</t>
+          <t>FSSL</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>EMBC</t>
+          <t>FTDR</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ENTX</t>
+          <t>FULT</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ENVX</t>
+          <t>FUNC</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>EPSN</t>
+          <t>GAING</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ERIC</t>
+          <t>GCBC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ERIE</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ESLT</t>
+          <t>GCT</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ESQ</t>
+          <t>GEHC</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>EWBC</t>
+          <t>GIBO</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>GMAB</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FA</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FANG</t>
+          <t>GRFS</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>GSAT</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>FBIZ</t>
+          <t>GSBC</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FBLA</t>
+          <t>GTLB</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>FCAP</t>
+          <t>HAFC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FCBM</t>
+          <t>HALO</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>FCCO</t>
+          <t>HAS</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>FCNCA</t>
+          <t>HBIO</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>FDBC</t>
+          <t>HBNC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FFBC</t>
+          <t>HCKT</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>FGBI</t>
+          <t>HELE</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FIBK</t>
+          <t>HFWA</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>FISI</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FITB</t>
+          <t>HTHT</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>FIVE</t>
+          <t>HURN</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FLYW</t>
+          <t>HWBK</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>FMAO</t>
+          <t>HWKN</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>FMBH</t>
+          <t>ICFI</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>FMNB</t>
+          <t>IDXX</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FNKO</t>
+          <t>III</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>FNLC</t>
+          <t>IIIV</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>FNWD</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>FRBA</t>
+          <t>INVA</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FRD</t>
+          <t>IOSP</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>FRHC</t>
+          <t>IPAR</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FRME</t>
+          <t>IRON</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>FRMEP</t>
+          <t>ISBA</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FSBC</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FSSL</t>
+          <t>ITRI</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>FSV</t>
+          <t>JAKK</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>FTDR</t>
+          <t>JANX</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FULT</t>
+          <t>JJSF</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FUNC</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>FVN</t>
+          <t>JOUT</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>JVA</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>GDRX</t>
+          <t>KARO</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>GEHC</t>
+          <t>KDP</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>GH</t>
+          <t>KELYA</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>KGEI</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>GLBE</t>
+          <t>KHC</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GRAL</t>
+          <t>KINS</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>GSBC</t>
+          <t>KMRK</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>HAFC</t>
+          <t>KROS</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>HALO</t>
+          <t>LBRX</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>HBIO</t>
+          <t>LCNB</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>HBNC</t>
+          <t>LEGH</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>HBT</t>
+          <t>LEGN</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>HCSG</t>
+          <t>LGND</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>HELE</t>
+          <t>LIFE</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>HIFS</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>HON</t>
+          <t>LKFN</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>HOWL</t>
+          <t>LKFT</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>HQY</t>
+          <t>LLYVA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>HTFL</t>
+          <t>LLYVK</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>HTHT</t>
+          <t>LMRI</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>HURN</t>
+          <t>LNT</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>HWBK</t>
+          <t>LOVE</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>HYNE</t>
+          <t>LSBK</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>LYEL</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>IBCP</t>
+          <t>LZ</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>MANH</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ICUI</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>IDXX</t>
+          <t>MASS</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>IMC</t>
+          <t>MAZE</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>INDB</t>
+          <t>MBWM</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>INDP</t>
+          <t>MCHX</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>INGN</t>
+          <t>MGPI</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>INTG</t>
+          <t>MGYR</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>IOSP</t>
+          <t>MICC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>IRON</t>
+          <t>MKTX</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>IRTC</t>
+          <t>MNST</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ISBA</t>
+          <t>MORN</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>MRSH</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>JAKK</t>
+          <t>MRVI</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>JJSF</t>
+          <t>MSBI</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>MSEX</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>JVA</t>
+          <t>MTEX</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>KARO</t>
+          <t>MYFW</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>KDP</t>
+          <t>MZTI</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>KIDS</t>
+          <t>NBTB</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>KINS</t>
+          <t>NBTX</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>KLTR</t>
+          <t>NDAQ</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>KMTS</t>
+          <t>NRC</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>KNSA</t>
+          <t>NRDS</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>KOD</t>
+          <t>NRIX</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>KPLT</t>
+          <t>NTLA</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>KRNT</t>
+          <t>NTSK</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>KROS</t>
+          <t>NWBI</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>KRRO</t>
+          <t>NWE</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>NWFL</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>KVHI</t>
+          <t>OBT</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>KYIV</t>
+          <t>OCTV</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>LARK</t>
+          <t>OIO</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>LBRX</t>
+          <t>OKTA</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LECO</t>
+          <t>OLED</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>LFST</t>
+          <t>OPK</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>LIFE</t>
+          <t>OPLN</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>LIND</t>
+          <t>ORRF</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LIVN</t>
+          <t>OSW</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>LKFN</t>
+          <t>OVLY</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>LKFT</t>
+          <t>OZK</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>LLYVA</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LLYVK</t>
+          <t>PCB</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>LMRI</t>
+          <t>PCTY</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>LNT</t>
+          <t>PDLB</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>LOVE</t>
+          <t>PEBO</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LQDT</t>
+          <t>PFIS</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>LSBK</t>
+          <t>PFXNZ</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>PGC</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>PGNY</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>MANE</t>
+          <t>PLBC</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MANH</t>
+          <t>PLGO</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>PLMR</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>MAZE</t>
+          <t>PNFP</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>MBWM</t>
+          <t>PNTG</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>MCBS</t>
+          <t>PODD</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>MEOH</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MGPI</t>
+          <t>PRGS</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>MGRC</t>
+          <t>PTC</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>MGRT</t>
+          <t>PTEN</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>MIDD</t>
+          <t>PTLE</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>MNST</t>
+          <t>PTLO</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>MORN</t>
+          <t>PWRL</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>MRSH</t>
+          <t>PYPD</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>MSBI</t>
+          <t>QCRH</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MSEX</t>
+          <t>QNBC</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>MTEX</t>
+          <t>RCBC</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MXCT</t>
+          <t>RDWR</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>MYFW</t>
+          <t>REAL</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>MZTI</t>
+          <t>REF</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NAVN</t>
+          <t>RELL</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>NBBK</t>
+          <t>REYN</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>NBN</t>
+          <t>RIGL</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>NBTX</t>
+          <t>RMBI</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>ROOT</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>NECB</t>
+          <t>ROP</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>NICE</t>
+          <t>RPRX</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>NMIH</t>
+          <t>RRBI</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NOVT</t>
+          <t>RXRX</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>NPAC</t>
+          <t>RYZ</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>NRC</t>
+          <t>SAFT</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>NRDS</t>
+          <t>SAGT</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NRIX</t>
+          <t>SAIC</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>NSIT</t>
+          <t>SBAC</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>NSSC</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>NTCT</t>
+          <t>SCAG</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NTGR</t>
+          <t>SCHL</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>NTNX</t>
+          <t>SDGR</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>NTRA</t>
+          <t>SFNC</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>NUTX</t>
+          <t>SGP</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NWBI</t>
+          <t>SHPH</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>NXPI</t>
+          <t>SIGI</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>OBT</t>
+          <t>SNES</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>OFIX</t>
+          <t>SNFCA</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>OFS</t>
+          <t>SOMN</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>SRCE</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>OMAB</t>
+          <t>SRPT</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>OMCL</t>
+          <t>SRZN</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ONC</t>
+          <t>SYNA</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>OPK</t>
+          <t>SYRE</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>OPLN</t>
+          <t>TACT</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>OPRT</t>
+          <t>TCMD</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>OPRX</t>
+          <t>TGTX</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ORKA</t>
+          <t>THFF</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ORRF</t>
+          <t>TILE</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>OSG</t>
+          <t>TLS</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>OSPN</t>
+          <t>TRI</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>OSUR</t>
+          <t>TRMB</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>OSW</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>OTAI</t>
+          <t>UTHR</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>OTTR</t>
+          <t>VIR</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>OVBC</t>
+          <t>WCCB</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>OVLY</t>
+          <t>WHK</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>OXLCO</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>OXLCZ</t>
+          <t>YSWY</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>OZK</t>
+          <t>DMRC</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PAA</t>
+          <t>EFOI</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>PACB</t>
+          <t>STAA</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>PAGP</t>
+          <t>BETR</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>CLAR</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PDLB</t>
+          <t>RIBBU</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>PDSB</t>
+          <t>FIVE</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>PEBO</t>
+          <t>KPLT</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>PFBC</t>
+          <t>DIBS</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PFIS</t>
+          <t>GNSS</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>PGNY</t>
+          <t>SWIM</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>PGY</t>
+          <t>HLP</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>PLBC</t>
+          <t>OPRT</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PLBY</t>
+          <t>DOO</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>PLGO</t>
+          <t>APOG</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>PLMR</t>
+          <t>ATEX</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>PLSE</t>
+          <t>SGRY</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PLUS</t>
+          <t>PRPL</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>PNFP</t>
+          <t>AIOK</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>PNTG</t>
+          <t>ORKA</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>PODD</t>
+          <t>IBG</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>TMCI</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>POWW</t>
+          <t>ATGL</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>PPLC</t>
+          <t>ICON</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>PRCT</t>
+          <t>GLSI</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PRME</t>
+          <t>CTKB</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>PRVA</t>
+          <t>LUNG</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>PSIG</t>
+          <t>KRRO</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>PTON</t>
+          <t>CHSN</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>QDEL</t>
+          <t>LVO</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>QLYS</t>
+          <t>TENB</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>QSI</t>
+          <t>SGHT</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>RCBC</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>RCEL</t>
+          <t>REPL</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>REAL</t>
+          <t>AVPT</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>REF</t>
+          <t>KXIN</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>ATER</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>RELY</t>
+          <t>PHAR</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>REYN</t>
+          <t>ALRM</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>RGCO</t>
+          <t>TRMD</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>RIGL</t>
+          <t>BRCB</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>RLAY</t>
+          <t>NXPI</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>RMBI</t>
+          <t>RJET</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>ROIV</t>
+          <t>KVHI</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ROOT</t>
+          <t>PNRG</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>RPAY</t>
+          <t>HYNE</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>RPC</t>
+          <t>SEPN</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>RRBI</t>
+          <t>MLTX</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>RYZ</t>
+          <t>CHMG</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>SBAC</t>
+          <t>IMC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>SBFG</t>
+          <t>KOD</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>RCEL</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SCHL</t>
+          <t>MOBI</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>SEPN</t>
+          <t>LFST</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>SEZL</t>
+          <t>ADMA</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>SFNC</t>
+          <t>FFTT</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SFST</t>
+          <t>XNCR</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>SGHT</t>
+          <t>JLHL</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>SGP</t>
+          <t>STFS</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>SHOE</t>
+          <t>MYGN</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SHPH</t>
+          <t>MANE</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SIBN</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>SIGI</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>SLAB</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>SNFCA</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>SNY</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>SOMN</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>SPFI</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>SPTX</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>SRCE</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>SRZN</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>SSTI</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>STAA</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>STBA</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>STLD</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>STRC</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>SUNB</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>SWIM</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>SWRD</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>TACO</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>TACT</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>TBCH</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>TCMD</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>TENB</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>TFSL</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>TGTX</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>THFF</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>TILE</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>TMCI</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>TNDM</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>TRAX</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>TRMB</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>TRMD</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>TW</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>UTHR</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>VSXY</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>WCCB</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>YMAT</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>ATGL</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>BMGL</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>GIBO</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>NTSK</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>MEDP</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>BRCB</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>DIBS</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>MOBI</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>CERT</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>ENGS</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>MRVI</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>PNRG</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>PHAR</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>JLHL</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>BSIN</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>PYPD</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>BOLT</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>JYD</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>EFOI</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>NOVTU</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>ANIX</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>GMAB</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>AIOK</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>PTEN</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>HLP</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>SAIC</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>RENT</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>RIBBU</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>ATER</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>SWKS</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>TLS</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>DGII</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>SGRY</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>INM</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>HAS</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>MYGN</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>NTWK</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
           <t>SLN</t>
         </is>
       </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>AVPT</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>SAGT</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>RDWR</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>ITRI</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>LEGN</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>BRZE</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>AMRX</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>RICK</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>GNSS</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>AIFA</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>BVC</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>BSRR</t>
-        </is>
-      </c>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_merged_latest.xlsx
+++ b/results/momentum_merged_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D113"/>
+  <dimension ref="A1:D111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,122 +441,122 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>ABCL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ABCL</t>
+          <t>ACIW</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BRKRP</t>
+          <t>AHRT</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AHRT</t>
+          <t>BBSI</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CHOW</t>
+          <t>ABLV</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ABLV</t>
+          <t>ACU</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>HBNB</t>
+          <t>BANR</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>BANR</t>
+          <t>BOKF</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FBIZ</t>
+          <t>ACGL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ACGL</t>
+          <t>AFRI</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BBSI</t>
+          <t>BCBP</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>GDYN</t>
+          <t>CLRO</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ACIC</t>
+          <t>ACNB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BCBP</t>
+          <t>AMRX</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MEOH</t>
+          <t>BGSI</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ACIW</t>
+          <t>CRNT</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BGSI</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NSLRL</t>
+          <t>ANIK</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ACNB</t>
+          <t>BRKRP</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>BOKF</t>
+          <t>CWST</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OSPN</t>
+          <t>ADPT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ACU</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -566,129 +566,129 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>FCAP</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>ARQT</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>CHDN</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>SHOE</t>
-        </is>
-      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ADPT</t>
+          <t>FRME</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CLRO</t>
+          <t>ADUS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SNY</t>
+          <t>ASBH</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>COO</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>COLL</t>
+          <t>HBAN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TOMZ</t>
+          <t>AEP</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ADUS</t>
+          <t>ASO</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>COO</t>
+          <t>DGII</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>IBG</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CRNT</t>
+          <t>ALRS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AFRI</t>
+          <t>AUDC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CWST</t>
+          <t>DPZ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AGYS</t>
+          <t>IMCR</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DPZ</t>
+          <t>AMCR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ALKS</t>
+          <t>AVAH</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>EJH</t>
+          <t>ESTA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ALLT</t>
+          <t>JRVR</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ESTA</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ALRS</t>
+          <t>AWR</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -698,447 +698,447 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>NYAX</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>ANDG</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>AXGN</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>EXTR</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>AMRX</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>FISV</t>
-        </is>
-      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ANIK</t>
+          <t>PECO</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HBAN</t>
+          <t>API</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>AXIN</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>IDN</t>
+          <t>FISV</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>PLUR</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IMCR</t>
+          <t>AROW</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>BHRB</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>INSG</t>
+          <t>GAUZ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>AROW</t>
+          <t>PRTA</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>KWY</t>
+          <t>ATLCL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ARQT</t>
+          <t>BIIB</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>LMAT</t>
+          <t>INSG</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ARX</t>
+          <t>RARE</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LWAY</t>
+          <t>ATLCZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ASBH</t>
+          <t>BL</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MGEE</t>
+          <t>INTJ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ASND</t>
+          <t>RDCM</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NBIX</t>
+          <t>ATR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ATLCL</t>
+          <t>BLKB</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NBN</t>
+          <t>JLHL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ATLCZ</t>
+          <t>SBCF</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NXST</t>
+          <t>AUPH</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ATR</t>
+          <t>BMBL</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NYAX</t>
+          <t>KWY</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>AUDC</t>
+          <t>SOLS</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>OFIX</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AUPH</t>
+          <t>BMRC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PATK</t>
+          <t>NBIX</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>AVBC</t>
+          <t>TCBK</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>BANF</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AVBH</t>
+          <t>BOLT</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>PECO</t>
+          <t>NBTX</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>AWR</t>
+          <t>TCX</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>BBCP</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AXGN</t>
+          <t>BOW</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PLUR</t>
+          <t>NXST</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>YORW</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PRTA</t>
+          <t>BBIO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BBCP</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>QQQX</t>
+          <t>PATK</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>BBIO</t>
+          <t>BFST</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>RARE</t>
+          <t>BSP</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BFST</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>RDCM</t>
+          <t>BIII</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>BHRB</t>
+          <t>BUUU</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SIRI</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>BMGL</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SMBC</t>
+          <t>CARL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>BL</t>
+          <t>PRPL</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SOLS</t>
+          <t>BOBS</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BLKB</t>
+          <t>CATY</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>TCBK</t>
+          <t>PWRL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>BMGL</t>
+          <t>BOOM</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TCX</t>
+          <t>CBRL</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BMRC</t>
+          <t>QNST</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>VMRK</t>
+          <t>BSIN</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>BOOM</t>
+          <t>CENT</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>YORW</t>
+          <t>SIRI</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BOW</t>
+          <t>BSY</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>CEPO</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>BSBK</t>
+          <t>SMBC</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BSIN</t>
+          <t>BWFG</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BSP</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BSY</t>
+          <t>TCMD</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>BUUU</t>
+          <t>BZ</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BVC</t>
+          <t>CHRD</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BVFL</t>
+          <t>VMRK</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BWFG</t>
+          <t>CBC</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>BZ</t>
+          <t>CING</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CARL</t>
+          <t>CBU</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CATY</t>
+          <t>CIVB</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CBC</t>
+          <t>CCEP</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CBK</t>
+          <t>CME</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CBU</t>
+          <t>CCID</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CCEP</t>
+          <t>COFS</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CCID</t>
+          <t>CCNE</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CCNE</t>
+          <t>CPRT</t>
         </is>
       </c>
     </row>
@@ -1150,1300 +1150,1300 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CENT</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CENTA</t>
+          <t>CDNA</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>CVBF</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>CENTA</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>CZNC</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
           <t>CGNT</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>CHCO</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>CHKP</t>
-        </is>
-      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>CHRD</t>
+          <t>DCOM</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CIGI</t>
+          <t>CHCO</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CINF</t>
+          <t>DMAA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CING</t>
+          <t>CHKP</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>CIVB</t>
+          <t>DORM</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CLGN</t>
+          <t>CHOW</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>ECBK</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>COAG</t>
+          <t>CHPGU</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>COFS</t>
+          <t>EFSC</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>COLM</t>
+          <t>CIGI</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>EML</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CPB</t>
+          <t>CINF</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>CPRT</t>
+          <t>ENGS</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CRAI</t>
+          <t>COAG</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>ENTX</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>COLM</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>EPSN</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CVBF</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CZFS</t>
+          <t>ESQ</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CZNC</t>
+          <t>CPB</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>CZWI</t>
+          <t>EWBC</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>CPSS</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>DCOM</t>
+          <t>EXLS</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>DGII</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>DLTR</t>
+          <t>FA</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DMAA</t>
+          <t>CTAS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DMII</t>
+          <t>FBLA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>DORM</t>
+          <t>CZFS</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>DOX</t>
+          <t>FBNC</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DSP</t>
+          <t>CZWI</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DUKU</t>
+          <t>FCCO</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>DLTR</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>EFSC</t>
+          <t>FCNCA</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>DMRC</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>EPSN</t>
+          <t>FFTT</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ERIC</t>
+          <t>DOX</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ERIE</t>
+          <t>FGCPP</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ESQ</t>
+          <t>DUKU</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>EVRG</t>
+          <t>FIZZ</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>EWBC</t>
+          <t>EBAY</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>FNLC</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>EDHL</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>EXLS</t>
+          <t>FSSL</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>ERIC</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>FA</t>
+          <t>FTDR</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FANG</t>
+          <t>ERIE</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FBNC</t>
+          <t>FULT</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FCBM</t>
+          <t>EVRG</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>FCCO</t>
+          <t>GAINI</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FCNCA</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FDBC</t>
+          <t>GIBO</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>FGBI</t>
+          <t>EXEL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>FIZZ</t>
+          <t>GSBC</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>FMAO</t>
+          <t>EXPO</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>FNLC</t>
+          <t>HALO</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>FRAF</t>
+          <t>FANG</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>FRBA</t>
+          <t>HAS</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>FRD</t>
+          <t>FBIZ</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>FRHC</t>
+          <t>HBT</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FRME</t>
+          <t>FLYW</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>FSBC</t>
+          <t>HCKT</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FSSL</t>
+          <t>FMNB</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FTDR</t>
+          <t>HELE</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>FULT</t>
+          <t>FRAF</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>FUNC</t>
+          <t>HFWA</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>GAING</t>
+          <t>FRHC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GCBC</t>
+          <t>HQY</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>FSBC</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>HUIZ</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>GEHC</t>
+          <t>FSV</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>GIBO</t>
+          <t>HURN</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>FWRD</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>HWBK</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>GAING</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>GRFS</t>
+          <t>HWKN</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GSAT</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>GSBC</t>
+          <t>IIIV</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>GTLB</t>
+          <t>GDYN</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>HAFC</t>
+          <t>INDB</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>HALO</t>
+          <t>GEHC</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>INVE</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>HBIO</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>HBNC</t>
+          <t>IOSP</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>HCKT</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>HELE</t>
+          <t>IRON</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>HFWA</t>
+          <t>GTLB</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>HON</t>
+          <t>ITRI</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>HTHT</t>
+          <t>HAFC</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>HURN</t>
+          <t>JAKK</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>HWBK</t>
+          <t>HBIO</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>HWKN</t>
+          <t>JANX</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ICFI</t>
+          <t>HBNC</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>IDXX</t>
+          <t>JJSF</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>HOFT</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>IIIV</t>
+          <t>JVA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>INVA</t>
+          <t>KBON</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>IOSP</t>
+          <t>HTHT</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>IPAR</t>
+          <t>KELYA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>IRON</t>
+          <t>ICON</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ISBA</t>
+          <t>KFII</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>ICUI</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ITRI</t>
+          <t>KGEI</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>JAKK</t>
+          <t>IDXX</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>JANX</t>
+          <t>KINS</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>JJSF</t>
+          <t>III</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>KMTS</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>JOUT</t>
+          <t>INTG</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>JVA</t>
+          <t>KRRO</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>KARO</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>KDP</t>
+          <t>LCNB</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>KELYA</t>
+          <t>INVA</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>KGEI</t>
+          <t>LFST</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>KHC</t>
+          <t>IPAR</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>KINS</t>
+          <t>LKFN</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>KMRK</t>
+          <t>IRTC</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>KROS</t>
+          <t>LLYVA</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>LBRX</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>LCNB</t>
+          <t>LLYVK</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>LEGH</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LEGN</t>
+          <t>LMRI</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>LGND</t>
+          <t>KDP</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>LIFE</t>
+          <t>LSBK</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>KHC</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LKFN</t>
+          <t>LZ</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>LKFT</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>LLYVA</t>
+          <t>MIDD</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>LLYVK</t>
+          <t>KYMR</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LMRI</t>
+          <t>MKTW</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>LNT</t>
+          <t>LEGH</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>LOVE</t>
+          <t>MOBI</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>LSBK</t>
+          <t>LEGN</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LYEL</t>
+          <t>MORN</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>LZ</t>
+          <t>LGND</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>MANH</t>
+          <t>MRVI</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>MASS</t>
+          <t>MSBI</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MAZE</t>
+          <t>LNT</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MBWM</t>
+          <t>MYFW</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MCHX</t>
+          <t>MANH</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>MGPI</t>
+          <t>NBTB</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MGYR</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MICC</t>
+          <t>NCNO</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MKTX</t>
+          <t>MASS</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>MNST</t>
+          <t>NPAC</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MORN</t>
+          <t>MAYS</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>MRSH</t>
+          <t>NRC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MRVI</t>
+          <t>MEOH</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>MSBI</t>
+          <t>NRIX</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MSEX</t>
+          <t>MGYR</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>MTEX</t>
+          <t>NTSK</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MYFW</t>
+          <t>MICC</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>MZTI</t>
+          <t>NWBI</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>NBTB</t>
+          <t>MKTX</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NBTX</t>
+          <t>NWFL</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>MNST</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NRC</t>
+          <t>OCTV</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>NRDS</t>
+          <t>MRSH</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>NRIX</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>NTLA</t>
+          <t>MSEX</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NTSK</t>
+          <t>OMAB</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>NWBI</t>
+          <t>MZTI</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>NWE</t>
+          <t>OPLN</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>NWFL</t>
+          <t>NDAQ</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>OBT</t>
+          <t>ORKA</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>OCTV</t>
+          <t>NMFCZ</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>OIO</t>
+          <t>OVLY</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>NOVTU</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>OZK</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>OPK</t>
+          <t>NSLRL</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>OPLN</t>
+          <t>PBFS</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ORRF</t>
+          <t>NTLA</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>OSW</t>
+          <t>PCB</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>OVLY</t>
+          <t>NWE</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>OZK</t>
+          <t>PFXNZ</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>OBT</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>PLGO</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>PCTY</t>
+          <t>OKTA</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>PDLB</t>
+          <t>PLMR</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>PEBO</t>
+          <t>ORRF</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>PFIS</t>
+          <t>PMTR</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>PFXNZ</t>
+          <t>OSG</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>PGC</t>
+          <t>PNRG</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>PGNY</t>
+          <t>OSPN</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>PLBC</t>
+          <t>PODD</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>PLGO</t>
+          <t>OSW</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>PLMR</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>PNFP</t>
+          <t>PAA</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>PNTG</t>
+          <t>PRGS</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>PODD</t>
+          <t>PACH</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>PRGS</t>
+          <t>PAHC</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>PYPD</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>PTEN</t>
+          <t>PCTY</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>PTLE</t>
+          <t>QCRH</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>PTLO</t>
+          <t>PDLB</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>PWRL</t>
+          <t>QNBC</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>PYPD</t>
+          <t>PEBO</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>QCRH</t>
+          <t>RCBC</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>QNBC</t>
+          <t>PGC</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>RCBC</t>
+          <t>REF</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>RDWR</t>
+          <t>PGNY</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>REAL</t>
+          <t>RELL</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>REF</t>
+          <t>PLBY</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>RELL</t>
+          <t>REYN</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>REYN</t>
+          <t>PNTG</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>RIGL</t>
+          <t>SAGT</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>RMBI</t>
+          <t>PPLC</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ROOT</t>
+          <t>SBAC</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ROP</t>
+          <t>PTEN</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>RPRX</t>
+          <t>SFNC</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>RRBI</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>RXRX</t>
+          <t>SGP</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>RYZ</t>
+          <t>RDWR</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SAFT</t>
+          <t>SHPH</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>SAGT</t>
+          <t>REAL</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>SAIC</t>
+          <t>SIGI</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>SBAC</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>SKYA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>SCAG</t>
+          <t>REPL</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>SCHL</t>
+          <t>SLDE</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>SDGR</t>
+          <t>RGCO</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SFNC</t>
+          <t>SNES</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SGP</t>
+          <t>ROOT</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>SHPH</t>
+          <t>SOMN</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SIGI</t>
+          <t>ROP</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SNES</t>
+          <t>SORA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>SNFCA</t>
+          <t>RPRX</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>SOMN</t>
+          <t>SRCE</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SRCE</t>
+          <t>RRBI</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2453,293 +2453,293 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
+          <t>RXRX</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
           <t>SRZN</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>SYNA</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
+          <t>RYZ</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
           <t>SYRE</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>TACT</t>
-        </is>
-      </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>TCMD</t>
+          <t>SAIC</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>TGTX</t>
+          <t>UTHR</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>THFF</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>TILE</t>
+          <t>VIR</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>TLS</t>
+          <t>SCHL</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>TRI</t>
+          <t>WHK</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>TRMB</t>
+          <t>SDGR</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>YSWY</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>UTHR</t>
+          <t>SEZL</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VIR</t>
+          <t>SHOE</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>WCCB</t>
+          <t>SLAB</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>WHK</t>
+          <t>SNFCA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>SNY</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>YSWY</t>
+          <t>SWIM</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>DMRC</t>
+          <t>SYNA</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>EFOI</t>
+          <t>TGTX</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>STAA</t>
+          <t>TLS</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>BETR</t>
+          <t>TOMZ</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>CLAR</t>
+          <t>TRGSU</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>RIBBU</t>
+          <t>TRI</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>FIVE</t>
+          <t>TVACU</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>KPLT</t>
+          <t>TW</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>DIBS</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>GNSS</t>
+          <t>XZO</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>SWIM</t>
+          <t>SUNB</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>INM</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>OPRT</t>
+          <t>TENB</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>DOO</t>
+          <t>SPCB</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>APOG</t>
+          <t>NXPI</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>ATEX</t>
+          <t>AVBC</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>SGRY</t>
+          <t>STFS</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PRPL</t>
+          <t>NORD</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
+          <t>BETR</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
           <t>AIOK</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>ORKA</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>IBG</t>
+          <t>RIBBU</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>TMCI</t>
+          <t>DOO</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>ATGL</t>
+          <t>EFOI</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>ICON</t>
+          <t>BRCB</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>GLSI</t>
+          <t>FIVE</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>CTKB</t>
+          <t>OPRT</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>LUNG</t>
+          <t>RICK</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>KRRO</t>
+          <t>ATEX</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>CHSN</t>
+          <t>HYNE</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>LVO</t>
+          <t>RIGL</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>TENB</t>
+          <t>ATGL</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>SGHT</t>
+          <t>STAA</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>XFOR</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>REPL</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>AVPT</t>
+          <t>PHAR</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -2751,148 +2751,108 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ATER</t>
+          <t>CHSN</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>PHAR</t>
+          <t>CLAR</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>ALRM</t>
+          <t>RJET</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>AVPT</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>BRCB</t>
+          <t>FGBI</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>NXPI</t>
+          <t>GRFS</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>RJET</t>
+          <t>CTKB</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>KVHI</t>
+          <t>XNCR</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>PNRG</t>
+          <t>IMC</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>HYNE</t>
+          <t>DHCNL</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>SEPN</t>
+          <t>GMAB</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>MLTX</t>
+          <t>SGRY</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>CHMG</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>IMC</t>
+          <t>HLP</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>KOD</t>
+          <t>KPLT</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>RCEL</t>
+          <t>DIBS</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>MOBI</t>
+          <t>ATER</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>LFST</t>
+          <t>KOD</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>ADMA</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>FFTT</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>XNCR</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>JLHL</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>STFS</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>MYGN</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>MANE</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>SLN</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr"/>
-      <c r="D113" t="inlineStr"/>
+          <t>LUNG</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
